--- a/downloads/Merit_2026_Employee_Bulk_Calculator_350_exact.xlsx
+++ b/downloads/Merit_2026_Employee_Bulk_Calculator_350_exact.xlsx
@@ -1011,13 +1011,13 @@
       <x:c r="B5" s="30"/>
       <x:c r="C5" s="58"/>
       <x:c r="D5" s="49" t="str">
-        <x:f>IF($B5="","",IFERROR(VLOOKUP($B5,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B5="","",IFERROR(VLOOKUP($B5,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E5" s="61" t="str">
         <x:f>IF($D5="","",IF($D5="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F5" s="50" t="str">
-        <x:f>IF($B5="","",IFERROR(VLOOKUP($B5,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B5="","",IFERROR(VLOOKUP($B5,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B5),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G5" s="64" t="str">
         <x:f>IF($F5="","",IFERROR(VLOOKUP($F5,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1067,13 +1067,13 @@
       <x:c r="B6" s="33"/>
       <x:c r="C6" s="59"/>
       <x:c r="D6" s="52" t="str">
-        <x:f>IF($B6="","",IFERROR(VLOOKUP($B6,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B6="","",IFERROR(VLOOKUP($B6,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E6" s="62" t="str">
         <x:f>IF($D6="","",IF($D6="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F6" s="53" t="str">
-        <x:f>IF($B6="","",IFERROR(VLOOKUP($B6,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B6="","",IFERROR(VLOOKUP($B6,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B6),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G6" s="65" t="str">
         <x:f>IF($F6="","",IFERROR(VLOOKUP($F6,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1123,13 +1123,13 @@
       <x:c r="B7" s="33"/>
       <x:c r="C7" s="59"/>
       <x:c r="D7" s="52" t="str">
-        <x:f>IF($B7="","",IFERROR(VLOOKUP($B7,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B7="","",IFERROR(VLOOKUP($B7,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E7" s="62" t="str">
         <x:f>IF($D7="","",IF($D7="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F7" s="53" t="str">
-        <x:f>IF($B7="","",IFERROR(VLOOKUP($B7,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B7="","",IFERROR(VLOOKUP($B7,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B7),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G7" s="65" t="str">
         <x:f>IF($F7="","",IFERROR(VLOOKUP($F7,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1179,13 +1179,13 @@
       <x:c r="B8" s="33"/>
       <x:c r="C8" s="59"/>
       <x:c r="D8" s="52" t="str">
-        <x:f>IF($B8="","",IFERROR(VLOOKUP($B8,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B8="","",IFERROR(VLOOKUP($B8,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E8" s="62" t="str">
         <x:f>IF($D8="","",IF($D8="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F8" s="53" t="str">
-        <x:f>IF($B8="","",IFERROR(VLOOKUP($B8,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B8="","",IFERROR(VLOOKUP($B8,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B8),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G8" s="65" t="str">
         <x:f>IF($F8="","",IFERROR(VLOOKUP($F8,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1235,13 +1235,13 @@
       <x:c r="B9" s="33"/>
       <x:c r="C9" s="59"/>
       <x:c r="D9" s="52" t="str">
-        <x:f>IF($B9="","",IFERROR(VLOOKUP($B9,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B9="","",IFERROR(VLOOKUP($B9,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E9" s="62" t="str">
         <x:f>IF($D9="","",IF($D9="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F9" s="53" t="str">
-        <x:f>IF($B9="","",IFERROR(VLOOKUP($B9,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B9="","",IFERROR(VLOOKUP($B9,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B9),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G9" s="65" t="str">
         <x:f>IF($F9="","",IFERROR(VLOOKUP($F9,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1291,13 +1291,13 @@
       <x:c r="B10" s="33"/>
       <x:c r="C10" s="59"/>
       <x:c r="D10" s="52" t="str">
-        <x:f>IF($B10="","",IFERROR(VLOOKUP($B10,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B10="","",IFERROR(VLOOKUP($B10,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E10" s="62" t="str">
         <x:f>IF($D10="","",IF($D10="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F10" s="53" t="str">
-        <x:f>IF($B10="","",IFERROR(VLOOKUP($B10,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B10="","",IFERROR(VLOOKUP($B10,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B10),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G10" s="65" t="str">
         <x:f>IF($F10="","",IFERROR(VLOOKUP($F10,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1347,13 +1347,13 @@
       <x:c r="B11" s="33"/>
       <x:c r="C11" s="59"/>
       <x:c r="D11" s="52" t="str">
-        <x:f>IF($B11="","",IFERROR(VLOOKUP($B11,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B11="","",IFERROR(VLOOKUP($B11,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E11" s="62" t="str">
         <x:f>IF($D11="","",IF($D11="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F11" s="53" t="str">
-        <x:f>IF($B11="","",IFERROR(VLOOKUP($B11,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B11="","",IFERROR(VLOOKUP($B11,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B11),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G11" s="65" t="str">
         <x:f>IF($F11="","",IFERROR(VLOOKUP($F11,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1403,13 +1403,13 @@
       <x:c r="B12" s="33"/>
       <x:c r="C12" s="59"/>
       <x:c r="D12" s="52" t="str">
-        <x:f>IF($B12="","",IFERROR(VLOOKUP($B12,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B12="","",IFERROR(VLOOKUP($B12,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E12" s="62" t="str">
         <x:f>IF($D12="","",IF($D12="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F12" s="53" t="str">
-        <x:f>IF($B12="","",IFERROR(VLOOKUP($B12,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B12="","",IFERROR(VLOOKUP($B12,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B12),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G12" s="65" t="str">
         <x:f>IF($F12="","",IFERROR(VLOOKUP($F12,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1459,13 +1459,13 @@
       <x:c r="B13" s="33"/>
       <x:c r="C13" s="59"/>
       <x:c r="D13" s="52" t="str">
-        <x:f>IF($B13="","",IFERROR(VLOOKUP($B13,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B13="","",IFERROR(VLOOKUP($B13,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E13" s="62" t="str">
         <x:f>IF($D13="","",IF($D13="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F13" s="53" t="str">
-        <x:f>IF($B13="","",IFERROR(VLOOKUP($B13,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B13="","",IFERROR(VLOOKUP($B13,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B13),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G13" s="65" t="str">
         <x:f>IF($F13="","",IFERROR(VLOOKUP($F13,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1515,13 +1515,13 @@
       <x:c r="B14" s="33"/>
       <x:c r="C14" s="59"/>
       <x:c r="D14" s="52" t="str">
-        <x:f>IF($B14="","",IFERROR(VLOOKUP($B14,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B14="","",IFERROR(VLOOKUP($B14,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E14" s="62" t="str">
         <x:f>IF($D14="","",IF($D14="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F14" s="53" t="str">
-        <x:f>IF($B14="","",IFERROR(VLOOKUP($B14,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B14="","",IFERROR(VLOOKUP($B14,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B14),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G14" s="65" t="str">
         <x:f>IF($F14="","",IFERROR(VLOOKUP($F14,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1571,13 +1571,13 @@
       <x:c r="B15" s="33"/>
       <x:c r="C15" s="59"/>
       <x:c r="D15" s="52" t="str">
-        <x:f>IF($B15="","",IFERROR(VLOOKUP($B15,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B15="","",IFERROR(VLOOKUP($B15,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E15" s="62" t="str">
         <x:f>IF($D15="","",IF($D15="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F15" s="53" t="str">
-        <x:f>IF($B15="","",IFERROR(VLOOKUP($B15,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B15="","",IFERROR(VLOOKUP($B15,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B15),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G15" s="65" t="str">
         <x:f>IF($F15="","",IFERROR(VLOOKUP($F15,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1627,13 +1627,13 @@
       <x:c r="B16" s="33"/>
       <x:c r="C16" s="59"/>
       <x:c r="D16" s="52" t="str">
-        <x:f>IF($B16="","",IFERROR(VLOOKUP($B16,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B16="","",IFERROR(VLOOKUP($B16,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E16" s="62" t="str">
         <x:f>IF($D16="","",IF($D16="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F16" s="53" t="str">
-        <x:f>IF($B16="","",IFERROR(VLOOKUP($B16,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B16="","",IFERROR(VLOOKUP($B16,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B16),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G16" s="65" t="str">
         <x:f>IF($F16="","",IFERROR(VLOOKUP($F16,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1683,13 +1683,13 @@
       <x:c r="B17" s="33"/>
       <x:c r="C17" s="59"/>
       <x:c r="D17" s="52" t="str">
-        <x:f>IF($B17="","",IFERROR(VLOOKUP($B17,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B17="","",IFERROR(VLOOKUP($B17,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E17" s="62" t="str">
         <x:f>IF($D17="","",IF($D17="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F17" s="53" t="str">
-        <x:f>IF($B17="","",IFERROR(VLOOKUP($B17,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B17="","",IFERROR(VLOOKUP($B17,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B17),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G17" s="65" t="str">
         <x:f>IF($F17="","",IFERROR(VLOOKUP($F17,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1739,13 +1739,13 @@
       <x:c r="B18" s="33"/>
       <x:c r="C18" s="59"/>
       <x:c r="D18" s="52" t="str">
-        <x:f>IF($B18="","",IFERROR(VLOOKUP($B18,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B18="","",IFERROR(VLOOKUP($B18,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E18" s="62" t="str">
         <x:f>IF($D18="","",IF($D18="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F18" s="53" t="str">
-        <x:f>IF($B18="","",IFERROR(VLOOKUP($B18,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B18="","",IFERROR(VLOOKUP($B18,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B18),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G18" s="65" t="str">
         <x:f>IF($F18="","",IFERROR(VLOOKUP($F18,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1795,13 +1795,13 @@
       <x:c r="B19" s="33"/>
       <x:c r="C19" s="59"/>
       <x:c r="D19" s="52" t="str">
-        <x:f>IF($B19="","",IFERROR(VLOOKUP($B19,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B19="","",IFERROR(VLOOKUP($B19,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E19" s="62" t="str">
         <x:f>IF($D19="","",IF($D19="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F19" s="53" t="str">
-        <x:f>IF($B19="","",IFERROR(VLOOKUP($B19,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B19="","",IFERROR(VLOOKUP($B19,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B19),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G19" s="65" t="str">
         <x:f>IF($F19="","",IFERROR(VLOOKUP($F19,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1851,13 +1851,13 @@
       <x:c r="B20" s="33"/>
       <x:c r="C20" s="59"/>
       <x:c r="D20" s="52" t="str">
-        <x:f>IF($B20="","",IFERROR(VLOOKUP($B20,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B20="","",IFERROR(VLOOKUP($B20,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E20" s="62" t="str">
         <x:f>IF($D20="","",IF($D20="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F20" s="53" t="str">
-        <x:f>IF($B20="","",IFERROR(VLOOKUP($B20,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B20="","",IFERROR(VLOOKUP($B20,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B20),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G20" s="65" t="str">
         <x:f>IF($F20="","",IFERROR(VLOOKUP($F20,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1907,13 +1907,13 @@
       <x:c r="B21" s="33"/>
       <x:c r="C21" s="59"/>
       <x:c r="D21" s="52" t="str">
-        <x:f>IF($B21="","",IFERROR(VLOOKUP($B21,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B21="","",IFERROR(VLOOKUP($B21,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E21" s="62" t="str">
         <x:f>IF($D21="","",IF($D21="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F21" s="53" t="str">
-        <x:f>IF($B21="","",IFERROR(VLOOKUP($B21,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B21="","",IFERROR(VLOOKUP($B21,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B21),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G21" s="65" t="str">
         <x:f>IF($F21="","",IFERROR(VLOOKUP($F21,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -1963,13 +1963,13 @@
       <x:c r="B22" s="33"/>
       <x:c r="C22" s="59"/>
       <x:c r="D22" s="52" t="str">
-        <x:f>IF($B22="","",IFERROR(VLOOKUP($B22,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B22="","",IFERROR(VLOOKUP($B22,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E22" s="62" t="str">
         <x:f>IF($D22="","",IF($D22="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F22" s="53" t="str">
-        <x:f>IF($B22="","",IFERROR(VLOOKUP($B22,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B22="","",IFERROR(VLOOKUP($B22,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B22),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G22" s="65" t="str">
         <x:f>IF($F22="","",IFERROR(VLOOKUP($F22,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2019,13 +2019,13 @@
       <x:c r="B23" s="33"/>
       <x:c r="C23" s="59"/>
       <x:c r="D23" s="52" t="str">
-        <x:f>IF($B23="","",IFERROR(VLOOKUP($B23,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B23="","",IFERROR(VLOOKUP($B23,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E23" s="62" t="str">
         <x:f>IF($D23="","",IF($D23="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F23" s="53" t="str">
-        <x:f>IF($B23="","",IFERROR(VLOOKUP($B23,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B23="","",IFERROR(VLOOKUP($B23,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B23),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G23" s="65" t="str">
         <x:f>IF($F23="","",IFERROR(VLOOKUP($F23,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2075,13 +2075,13 @@
       <x:c r="B24" s="33"/>
       <x:c r="C24" s="59"/>
       <x:c r="D24" s="52" t="str">
-        <x:f>IF($B24="","",IFERROR(VLOOKUP($B24,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B24="","",IFERROR(VLOOKUP($B24,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E24" s="62" t="str">
         <x:f>IF($D24="","",IF($D24="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F24" s="53" t="str">
-        <x:f>IF($B24="","",IFERROR(VLOOKUP($B24,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B24="","",IFERROR(VLOOKUP($B24,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B24),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G24" s="65" t="str">
         <x:f>IF($F24="","",IFERROR(VLOOKUP($F24,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2131,13 +2131,13 @@
       <x:c r="B25" s="33"/>
       <x:c r="C25" s="59"/>
       <x:c r="D25" s="52" t="str">
-        <x:f>IF($B25="","",IFERROR(VLOOKUP($B25,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B25="","",IFERROR(VLOOKUP($B25,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E25" s="62" t="str">
         <x:f>IF($D25="","",IF($D25="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F25" s="53" t="str">
-        <x:f>IF($B25="","",IFERROR(VLOOKUP($B25,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B25="","",IFERROR(VLOOKUP($B25,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B25),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G25" s="65" t="str">
         <x:f>IF($F25="","",IFERROR(VLOOKUP($F25,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2187,13 +2187,13 @@
       <x:c r="B26" s="33"/>
       <x:c r="C26" s="59"/>
       <x:c r="D26" s="52" t="str">
-        <x:f>IF($B26="","",IFERROR(VLOOKUP($B26,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B26="","",IFERROR(VLOOKUP($B26,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E26" s="62" t="str">
         <x:f>IF($D26="","",IF($D26="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F26" s="53" t="str">
-        <x:f>IF($B26="","",IFERROR(VLOOKUP($B26,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B26="","",IFERROR(VLOOKUP($B26,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B26),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G26" s="65" t="str">
         <x:f>IF($F26="","",IFERROR(VLOOKUP($F26,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2243,13 +2243,13 @@
       <x:c r="B27" s="33"/>
       <x:c r="C27" s="59"/>
       <x:c r="D27" s="52" t="str">
-        <x:f>IF($B27="","",IFERROR(VLOOKUP($B27,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B27="","",IFERROR(VLOOKUP($B27,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E27" s="62" t="str">
         <x:f>IF($D27="","",IF($D27="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F27" s="53" t="str">
-        <x:f>IF($B27="","",IFERROR(VLOOKUP($B27,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B27="","",IFERROR(VLOOKUP($B27,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B27),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G27" s="65" t="str">
         <x:f>IF($F27="","",IFERROR(VLOOKUP($F27,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2299,13 +2299,13 @@
       <x:c r="B28" s="33"/>
       <x:c r="C28" s="59"/>
       <x:c r="D28" s="52" t="str">
-        <x:f>IF($B28="","",IFERROR(VLOOKUP($B28,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B28="","",IFERROR(VLOOKUP($B28,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E28" s="62" t="str">
         <x:f>IF($D28="","",IF($D28="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F28" s="53" t="str">
-        <x:f>IF($B28="","",IFERROR(VLOOKUP($B28,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B28="","",IFERROR(VLOOKUP($B28,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B28),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G28" s="65" t="str">
         <x:f>IF($F28="","",IFERROR(VLOOKUP($F28,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2355,13 +2355,13 @@
       <x:c r="B29" s="33"/>
       <x:c r="C29" s="59"/>
       <x:c r="D29" s="52" t="str">
-        <x:f>IF($B29="","",IFERROR(VLOOKUP($B29,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B29="","",IFERROR(VLOOKUP($B29,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E29" s="62" t="str">
         <x:f>IF($D29="","",IF($D29="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F29" s="53" t="str">
-        <x:f>IF($B29="","",IFERROR(VLOOKUP($B29,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B29="","",IFERROR(VLOOKUP($B29,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B29),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G29" s="65" t="str">
         <x:f>IF($F29="","",IFERROR(VLOOKUP($F29,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2411,13 +2411,13 @@
       <x:c r="B30" s="33"/>
       <x:c r="C30" s="59"/>
       <x:c r="D30" s="52" t="str">
-        <x:f>IF($B30="","",IFERROR(VLOOKUP($B30,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B30="","",IFERROR(VLOOKUP($B30,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E30" s="62" t="str">
         <x:f>IF($D30="","",IF($D30="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F30" s="53" t="str">
-        <x:f>IF($B30="","",IFERROR(VLOOKUP($B30,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B30="","",IFERROR(VLOOKUP($B30,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B30),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G30" s="65" t="str">
         <x:f>IF($F30="","",IFERROR(VLOOKUP($F30,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2467,13 +2467,13 @@
       <x:c r="B31" s="33"/>
       <x:c r="C31" s="59"/>
       <x:c r="D31" s="52" t="str">
-        <x:f>IF($B31="","",IFERROR(VLOOKUP($B31,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B31="","",IFERROR(VLOOKUP($B31,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E31" s="62" t="str">
         <x:f>IF($D31="","",IF($D31="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F31" s="53" t="str">
-        <x:f>IF($B31="","",IFERROR(VLOOKUP($B31,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B31="","",IFERROR(VLOOKUP($B31,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B31),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G31" s="65" t="str">
         <x:f>IF($F31="","",IFERROR(VLOOKUP($F31,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2523,13 +2523,13 @@
       <x:c r="B32" s="33"/>
       <x:c r="C32" s="59"/>
       <x:c r="D32" s="52" t="str">
-        <x:f>IF($B32="","",IFERROR(VLOOKUP($B32,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B32="","",IFERROR(VLOOKUP($B32,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E32" s="62" t="str">
         <x:f>IF($D32="","",IF($D32="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F32" s="53" t="str">
-        <x:f>IF($B32="","",IFERROR(VLOOKUP($B32,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B32="","",IFERROR(VLOOKUP($B32,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B32),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G32" s="65" t="str">
         <x:f>IF($F32="","",IFERROR(VLOOKUP($F32,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2579,13 +2579,13 @@
       <x:c r="B33" s="33"/>
       <x:c r="C33" s="59"/>
       <x:c r="D33" s="52" t="str">
-        <x:f>IF($B33="","",IFERROR(VLOOKUP($B33,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B33="","",IFERROR(VLOOKUP($B33,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E33" s="62" t="str">
         <x:f>IF($D33="","",IF($D33="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F33" s="53" t="str">
-        <x:f>IF($B33="","",IFERROR(VLOOKUP($B33,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B33="","",IFERROR(VLOOKUP($B33,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B33),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G33" s="65" t="str">
         <x:f>IF($F33="","",IFERROR(VLOOKUP($F33,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2635,13 +2635,13 @@
       <x:c r="B34" s="33"/>
       <x:c r="C34" s="59"/>
       <x:c r="D34" s="52" t="str">
-        <x:f>IF($B34="","",IFERROR(VLOOKUP($B34,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B34="","",IFERROR(VLOOKUP($B34,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E34" s="62" t="str">
         <x:f>IF($D34="","",IF($D34="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F34" s="53" t="str">
-        <x:f>IF($B34="","",IFERROR(VLOOKUP($B34,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B34="","",IFERROR(VLOOKUP($B34,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B34),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G34" s="65" t="str">
         <x:f>IF($F34="","",IFERROR(VLOOKUP($F34,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2691,13 +2691,13 @@
       <x:c r="B35" s="33"/>
       <x:c r="C35" s="59"/>
       <x:c r="D35" s="52" t="str">
-        <x:f>IF($B35="","",IFERROR(VLOOKUP($B35,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B35="","",IFERROR(VLOOKUP($B35,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E35" s="62" t="str">
         <x:f>IF($D35="","",IF($D35="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F35" s="53" t="str">
-        <x:f>IF($B35="","",IFERROR(VLOOKUP($B35,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B35="","",IFERROR(VLOOKUP($B35,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B35),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G35" s="65" t="str">
         <x:f>IF($F35="","",IFERROR(VLOOKUP($F35,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2747,13 +2747,13 @@
       <x:c r="B36" s="33"/>
       <x:c r="C36" s="59"/>
       <x:c r="D36" s="52" t="str">
-        <x:f>IF($B36="","",IFERROR(VLOOKUP($B36,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B36="","",IFERROR(VLOOKUP($B36,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E36" s="62" t="str">
         <x:f>IF($D36="","",IF($D36="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F36" s="53" t="str">
-        <x:f>IF($B36="","",IFERROR(VLOOKUP($B36,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B36="","",IFERROR(VLOOKUP($B36,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B36),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G36" s="65" t="str">
         <x:f>IF($F36="","",IFERROR(VLOOKUP($F36,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2803,13 +2803,13 @@
       <x:c r="B37" s="33"/>
       <x:c r="C37" s="59"/>
       <x:c r="D37" s="52" t="str">
-        <x:f>IF($B37="","",IFERROR(VLOOKUP($B37,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B37="","",IFERROR(VLOOKUP($B37,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E37" s="62" t="str">
         <x:f>IF($D37="","",IF($D37="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F37" s="53" t="str">
-        <x:f>IF($B37="","",IFERROR(VLOOKUP($B37,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B37="","",IFERROR(VLOOKUP($B37,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B37),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G37" s="65" t="str">
         <x:f>IF($F37="","",IFERROR(VLOOKUP($F37,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2859,13 +2859,13 @@
       <x:c r="B38" s="33"/>
       <x:c r="C38" s="59"/>
       <x:c r="D38" s="52" t="str">
-        <x:f>IF($B38="","",IFERROR(VLOOKUP($B38,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B38="","",IFERROR(VLOOKUP($B38,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E38" s="62" t="str">
         <x:f>IF($D38="","",IF($D38="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F38" s="53" t="str">
-        <x:f>IF($B38="","",IFERROR(VLOOKUP($B38,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B38="","",IFERROR(VLOOKUP($B38,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B38),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G38" s="65" t="str">
         <x:f>IF($F38="","",IFERROR(VLOOKUP($F38,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2915,13 +2915,13 @@
       <x:c r="B39" s="33"/>
       <x:c r="C39" s="59"/>
       <x:c r="D39" s="52" t="str">
-        <x:f>IF($B39="","",IFERROR(VLOOKUP($B39,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B39="","",IFERROR(VLOOKUP($B39,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E39" s="62" t="str">
         <x:f>IF($D39="","",IF($D39="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F39" s="53" t="str">
-        <x:f>IF($B39="","",IFERROR(VLOOKUP($B39,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B39="","",IFERROR(VLOOKUP($B39,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B39),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G39" s="65" t="str">
         <x:f>IF($F39="","",IFERROR(VLOOKUP($F39,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -2971,13 +2971,13 @@
       <x:c r="B40" s="33"/>
       <x:c r="C40" s="59"/>
       <x:c r="D40" s="52" t="str">
-        <x:f>IF($B40="","",IFERROR(VLOOKUP($B40,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B40="","",IFERROR(VLOOKUP($B40,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E40" s="62" t="str">
         <x:f>IF($D40="","",IF($D40="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F40" s="53" t="str">
-        <x:f>IF($B40="","",IFERROR(VLOOKUP($B40,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B40="","",IFERROR(VLOOKUP($B40,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B40),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G40" s="65" t="str">
         <x:f>IF($F40="","",IFERROR(VLOOKUP($F40,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3027,13 +3027,13 @@
       <x:c r="B41" s="33"/>
       <x:c r="C41" s="59"/>
       <x:c r="D41" s="52" t="str">
-        <x:f>IF($B41="","",IFERROR(VLOOKUP($B41,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B41="","",IFERROR(VLOOKUP($B41,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E41" s="62" t="str">
         <x:f>IF($D41="","",IF($D41="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F41" s="53" t="str">
-        <x:f>IF($B41="","",IFERROR(VLOOKUP($B41,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B41="","",IFERROR(VLOOKUP($B41,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B41),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G41" s="65" t="str">
         <x:f>IF($F41="","",IFERROR(VLOOKUP($F41,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3083,13 +3083,13 @@
       <x:c r="B42" s="33"/>
       <x:c r="C42" s="59"/>
       <x:c r="D42" s="52" t="str">
-        <x:f>IF($B42="","",IFERROR(VLOOKUP($B42,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B42="","",IFERROR(VLOOKUP($B42,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E42" s="62" t="str">
         <x:f>IF($D42="","",IF($D42="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F42" s="53" t="str">
-        <x:f>IF($B42="","",IFERROR(VLOOKUP($B42,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B42="","",IFERROR(VLOOKUP($B42,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B42),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G42" s="65" t="str">
         <x:f>IF($F42="","",IFERROR(VLOOKUP($F42,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3139,13 +3139,13 @@
       <x:c r="B43" s="33"/>
       <x:c r="C43" s="59"/>
       <x:c r="D43" s="52" t="str">
-        <x:f>IF($B43="","",IFERROR(VLOOKUP($B43,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B43="","",IFERROR(VLOOKUP($B43,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E43" s="62" t="str">
         <x:f>IF($D43="","",IF($D43="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F43" s="53" t="str">
-        <x:f>IF($B43="","",IFERROR(VLOOKUP($B43,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B43="","",IFERROR(VLOOKUP($B43,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B43),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G43" s="65" t="str">
         <x:f>IF($F43="","",IFERROR(VLOOKUP($F43,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3195,13 +3195,13 @@
       <x:c r="B44" s="33"/>
       <x:c r="C44" s="59"/>
       <x:c r="D44" s="52" t="str">
-        <x:f>IF($B44="","",IFERROR(VLOOKUP($B44,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B44="","",IFERROR(VLOOKUP($B44,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E44" s="62" t="str">
         <x:f>IF($D44="","",IF($D44="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F44" s="53" t="str">
-        <x:f>IF($B44="","",IFERROR(VLOOKUP($B44,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B44="","",IFERROR(VLOOKUP($B44,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B44),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G44" s="65" t="str">
         <x:f>IF($F44="","",IFERROR(VLOOKUP($F44,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3251,13 +3251,13 @@
       <x:c r="B45" s="33"/>
       <x:c r="C45" s="59"/>
       <x:c r="D45" s="52" t="str">
-        <x:f>IF($B45="","",IFERROR(VLOOKUP($B45,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B45="","",IFERROR(VLOOKUP($B45,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E45" s="62" t="str">
         <x:f>IF($D45="","",IF($D45="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F45" s="53" t="str">
-        <x:f>IF($B45="","",IFERROR(VLOOKUP($B45,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B45="","",IFERROR(VLOOKUP($B45,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B45),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G45" s="65" t="str">
         <x:f>IF($F45="","",IFERROR(VLOOKUP($F45,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3307,13 +3307,13 @@
       <x:c r="B46" s="33"/>
       <x:c r="C46" s="59"/>
       <x:c r="D46" s="52" t="str">
-        <x:f>IF($B46="","",IFERROR(VLOOKUP($B46,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B46="","",IFERROR(VLOOKUP($B46,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E46" s="62" t="str">
         <x:f>IF($D46="","",IF($D46="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F46" s="53" t="str">
-        <x:f>IF($B46="","",IFERROR(VLOOKUP($B46,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B46="","",IFERROR(VLOOKUP($B46,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B46),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G46" s="65" t="str">
         <x:f>IF($F46="","",IFERROR(VLOOKUP($F46,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3363,13 +3363,13 @@
       <x:c r="B47" s="33"/>
       <x:c r="C47" s="59"/>
       <x:c r="D47" s="52" t="str">
-        <x:f>IF($B47="","",IFERROR(VLOOKUP($B47,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B47="","",IFERROR(VLOOKUP($B47,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E47" s="62" t="str">
         <x:f>IF($D47="","",IF($D47="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F47" s="53" t="str">
-        <x:f>IF($B47="","",IFERROR(VLOOKUP($B47,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B47="","",IFERROR(VLOOKUP($B47,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B47),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G47" s="65" t="str">
         <x:f>IF($F47="","",IFERROR(VLOOKUP($F47,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3419,13 +3419,13 @@
       <x:c r="B48" s="33"/>
       <x:c r="C48" s="59"/>
       <x:c r="D48" s="52" t="str">
-        <x:f>IF($B48="","",IFERROR(VLOOKUP($B48,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B48="","",IFERROR(VLOOKUP($B48,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E48" s="62" t="str">
         <x:f>IF($D48="","",IF($D48="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F48" s="53" t="str">
-        <x:f>IF($B48="","",IFERROR(VLOOKUP($B48,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B48="","",IFERROR(VLOOKUP($B48,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B48),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G48" s="65" t="str">
         <x:f>IF($F48="","",IFERROR(VLOOKUP($F48,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3475,13 +3475,13 @@
       <x:c r="B49" s="33"/>
       <x:c r="C49" s="59"/>
       <x:c r="D49" s="52" t="str">
-        <x:f>IF($B49="","",IFERROR(VLOOKUP($B49,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B49="","",IFERROR(VLOOKUP($B49,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E49" s="62" t="str">
         <x:f>IF($D49="","",IF($D49="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F49" s="53" t="str">
-        <x:f>IF($B49="","",IFERROR(VLOOKUP($B49,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B49="","",IFERROR(VLOOKUP($B49,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B49),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G49" s="65" t="str">
         <x:f>IF($F49="","",IFERROR(VLOOKUP($F49,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3531,13 +3531,13 @@
       <x:c r="B50" s="33"/>
       <x:c r="C50" s="59"/>
       <x:c r="D50" s="52" t="str">
-        <x:f>IF($B50="","",IFERROR(VLOOKUP($B50,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B50="","",IFERROR(VLOOKUP($B50,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E50" s="62" t="str">
         <x:f>IF($D50="","",IF($D50="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F50" s="53" t="str">
-        <x:f>IF($B50="","",IFERROR(VLOOKUP($B50,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B50="","",IFERROR(VLOOKUP($B50,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B50),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G50" s="65" t="str">
         <x:f>IF($F50="","",IFERROR(VLOOKUP($F50,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3587,13 +3587,13 @@
       <x:c r="B51" s="33"/>
       <x:c r="C51" s="59"/>
       <x:c r="D51" s="52" t="str">
-        <x:f>IF($B51="","",IFERROR(VLOOKUP($B51,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B51="","",IFERROR(VLOOKUP($B51,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E51" s="62" t="str">
         <x:f>IF($D51="","",IF($D51="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F51" s="53" t="str">
-        <x:f>IF($B51="","",IFERROR(VLOOKUP($B51,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B51="","",IFERROR(VLOOKUP($B51,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B51),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G51" s="65" t="str">
         <x:f>IF($F51="","",IFERROR(VLOOKUP($F51,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3643,13 +3643,13 @@
       <x:c r="B52" s="33"/>
       <x:c r="C52" s="59"/>
       <x:c r="D52" s="52" t="str">
-        <x:f>IF($B52="","",IFERROR(VLOOKUP($B52,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B52="","",IFERROR(VLOOKUP($B52,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E52" s="62" t="str">
         <x:f>IF($D52="","",IF($D52="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F52" s="53" t="str">
-        <x:f>IF($B52="","",IFERROR(VLOOKUP($B52,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B52="","",IFERROR(VLOOKUP($B52,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B52),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G52" s="65" t="str">
         <x:f>IF($F52="","",IFERROR(VLOOKUP($F52,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3699,13 +3699,13 @@
       <x:c r="B53" s="33"/>
       <x:c r="C53" s="59"/>
       <x:c r="D53" s="52" t="str">
-        <x:f>IF($B53="","",IFERROR(VLOOKUP($B53,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B53="","",IFERROR(VLOOKUP($B53,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E53" s="62" t="str">
         <x:f>IF($D53="","",IF($D53="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F53" s="53" t="str">
-        <x:f>IF($B53="","",IFERROR(VLOOKUP($B53,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B53="","",IFERROR(VLOOKUP($B53,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B53),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G53" s="65" t="str">
         <x:f>IF($F53="","",IFERROR(VLOOKUP($F53,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3755,13 +3755,13 @@
       <x:c r="B54" s="33"/>
       <x:c r="C54" s="59"/>
       <x:c r="D54" s="52" t="str">
-        <x:f>IF($B54="","",IFERROR(VLOOKUP($B54,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B54="","",IFERROR(VLOOKUP($B54,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E54" s="62" t="str">
         <x:f>IF($D54="","",IF($D54="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F54" s="53" t="str">
-        <x:f>IF($B54="","",IFERROR(VLOOKUP($B54,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B54="","",IFERROR(VLOOKUP($B54,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B54),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G54" s="65" t="str">
         <x:f>IF($F54="","",IFERROR(VLOOKUP($F54,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3811,13 +3811,13 @@
       <x:c r="B55" s="33"/>
       <x:c r="C55" s="59"/>
       <x:c r="D55" s="52" t="str">
-        <x:f>IF($B55="","",IFERROR(VLOOKUP($B55,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B55="","",IFERROR(VLOOKUP($B55,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E55" s="62" t="str">
         <x:f>IF($D55="","",IF($D55="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F55" s="53" t="str">
-        <x:f>IF($B55="","",IFERROR(VLOOKUP($B55,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B55="","",IFERROR(VLOOKUP($B55,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B55),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G55" s="65" t="str">
         <x:f>IF($F55="","",IFERROR(VLOOKUP($F55,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3867,13 +3867,13 @@
       <x:c r="B56" s="33"/>
       <x:c r="C56" s="59"/>
       <x:c r="D56" s="52" t="str">
-        <x:f>IF($B56="","",IFERROR(VLOOKUP($B56,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B56="","",IFERROR(VLOOKUP($B56,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E56" s="62" t="str">
         <x:f>IF($D56="","",IF($D56="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F56" s="53" t="str">
-        <x:f>IF($B56="","",IFERROR(VLOOKUP($B56,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B56="","",IFERROR(VLOOKUP($B56,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B56),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G56" s="65" t="str">
         <x:f>IF($F56="","",IFERROR(VLOOKUP($F56,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3923,13 +3923,13 @@
       <x:c r="B57" s="33"/>
       <x:c r="C57" s="59"/>
       <x:c r="D57" s="52" t="str">
-        <x:f>IF($B57="","",IFERROR(VLOOKUP($B57,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B57="","",IFERROR(VLOOKUP($B57,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E57" s="62" t="str">
         <x:f>IF($D57="","",IF($D57="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F57" s="53" t="str">
-        <x:f>IF($B57="","",IFERROR(VLOOKUP($B57,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B57="","",IFERROR(VLOOKUP($B57,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B57),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G57" s="65" t="str">
         <x:f>IF($F57="","",IFERROR(VLOOKUP($F57,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -3979,13 +3979,13 @@
       <x:c r="B58" s="33"/>
       <x:c r="C58" s="59"/>
       <x:c r="D58" s="52" t="str">
-        <x:f>IF($B58="","",IFERROR(VLOOKUP($B58,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B58="","",IFERROR(VLOOKUP($B58,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E58" s="62" t="str">
         <x:f>IF($D58="","",IF($D58="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F58" s="53" t="str">
-        <x:f>IF($B58="","",IFERROR(VLOOKUP($B58,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B58="","",IFERROR(VLOOKUP($B58,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B58),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G58" s="65" t="str">
         <x:f>IF($F58="","",IFERROR(VLOOKUP($F58,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4035,13 +4035,13 @@
       <x:c r="B59" s="33"/>
       <x:c r="C59" s="59"/>
       <x:c r="D59" s="52" t="str">
-        <x:f>IF($B59="","",IFERROR(VLOOKUP($B59,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B59="","",IFERROR(VLOOKUP($B59,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E59" s="62" t="str">
         <x:f>IF($D59="","",IF($D59="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F59" s="53" t="str">
-        <x:f>IF($B59="","",IFERROR(VLOOKUP($B59,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B59="","",IFERROR(VLOOKUP($B59,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B59),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G59" s="65" t="str">
         <x:f>IF($F59="","",IFERROR(VLOOKUP($F59,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4091,13 +4091,13 @@
       <x:c r="B60" s="33"/>
       <x:c r="C60" s="59"/>
       <x:c r="D60" s="52" t="str">
-        <x:f>IF($B60="","",IFERROR(VLOOKUP($B60,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B60="","",IFERROR(VLOOKUP($B60,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E60" s="62" t="str">
         <x:f>IF($D60="","",IF($D60="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F60" s="53" t="str">
-        <x:f>IF($B60="","",IFERROR(VLOOKUP($B60,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B60="","",IFERROR(VLOOKUP($B60,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B60),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G60" s="65" t="str">
         <x:f>IF($F60="","",IFERROR(VLOOKUP($F60,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4147,13 +4147,13 @@
       <x:c r="B61" s="33"/>
       <x:c r="C61" s="59"/>
       <x:c r="D61" s="52" t="str">
-        <x:f>IF($B61="","",IFERROR(VLOOKUP($B61,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B61="","",IFERROR(VLOOKUP($B61,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E61" s="62" t="str">
         <x:f>IF($D61="","",IF($D61="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F61" s="53" t="str">
-        <x:f>IF($B61="","",IFERROR(VLOOKUP($B61,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B61="","",IFERROR(VLOOKUP($B61,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B61),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G61" s="65" t="str">
         <x:f>IF($F61="","",IFERROR(VLOOKUP($F61,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4203,13 +4203,13 @@
       <x:c r="B62" s="33"/>
       <x:c r="C62" s="59"/>
       <x:c r="D62" s="52" t="str">
-        <x:f>IF($B62="","",IFERROR(VLOOKUP($B62,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B62="","",IFERROR(VLOOKUP($B62,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E62" s="62" t="str">
         <x:f>IF($D62="","",IF($D62="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F62" s="53" t="str">
-        <x:f>IF($B62="","",IFERROR(VLOOKUP($B62,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B62="","",IFERROR(VLOOKUP($B62,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B62),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G62" s="65" t="str">
         <x:f>IF($F62="","",IFERROR(VLOOKUP($F62,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4259,13 +4259,13 @@
       <x:c r="B63" s="33"/>
       <x:c r="C63" s="59"/>
       <x:c r="D63" s="52" t="str">
-        <x:f>IF($B63="","",IFERROR(VLOOKUP($B63,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B63="","",IFERROR(VLOOKUP($B63,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E63" s="62" t="str">
         <x:f>IF($D63="","",IF($D63="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F63" s="53" t="str">
-        <x:f>IF($B63="","",IFERROR(VLOOKUP($B63,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B63="","",IFERROR(VLOOKUP($B63,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B63),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G63" s="65" t="str">
         <x:f>IF($F63="","",IFERROR(VLOOKUP($F63,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4315,13 +4315,13 @@
       <x:c r="B64" s="33"/>
       <x:c r="C64" s="59"/>
       <x:c r="D64" s="52" t="str">
-        <x:f>IF($B64="","",IFERROR(VLOOKUP($B64,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B64="","",IFERROR(VLOOKUP($B64,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E64" s="62" t="str">
         <x:f>IF($D64="","",IF($D64="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F64" s="53" t="str">
-        <x:f>IF($B64="","",IFERROR(VLOOKUP($B64,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B64="","",IFERROR(VLOOKUP($B64,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B64),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G64" s="65" t="str">
         <x:f>IF($F64="","",IFERROR(VLOOKUP($F64,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4371,13 +4371,13 @@
       <x:c r="B65" s="33"/>
       <x:c r="C65" s="59"/>
       <x:c r="D65" s="52" t="str">
-        <x:f>IF($B65="","",IFERROR(VLOOKUP($B65,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B65="","",IFERROR(VLOOKUP($B65,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E65" s="62" t="str">
         <x:f>IF($D65="","",IF($D65="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F65" s="53" t="str">
-        <x:f>IF($B65="","",IFERROR(VLOOKUP($B65,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B65="","",IFERROR(VLOOKUP($B65,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B65),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G65" s="65" t="str">
         <x:f>IF($F65="","",IFERROR(VLOOKUP($F65,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4427,13 +4427,13 @@
       <x:c r="B66" s="33"/>
       <x:c r="C66" s="59"/>
       <x:c r="D66" s="52" t="str">
-        <x:f>IF($B66="","",IFERROR(VLOOKUP($B66,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B66="","",IFERROR(VLOOKUP($B66,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E66" s="62" t="str">
         <x:f>IF($D66="","",IF($D66="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F66" s="53" t="str">
-        <x:f>IF($B66="","",IFERROR(VLOOKUP($B66,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B66="","",IFERROR(VLOOKUP($B66,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B66),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G66" s="65" t="str">
         <x:f>IF($F66="","",IFERROR(VLOOKUP($F66,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4483,13 +4483,13 @@
       <x:c r="B67" s="33"/>
       <x:c r="C67" s="59"/>
       <x:c r="D67" s="52" t="str">
-        <x:f>IF($B67="","",IFERROR(VLOOKUP($B67,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B67="","",IFERROR(VLOOKUP($B67,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E67" s="62" t="str">
         <x:f>IF($D67="","",IF($D67="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F67" s="53" t="str">
-        <x:f>IF($B67="","",IFERROR(VLOOKUP($B67,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B67="","",IFERROR(VLOOKUP($B67,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B67),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G67" s="65" t="str">
         <x:f>IF($F67="","",IFERROR(VLOOKUP($F67,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4539,13 +4539,13 @@
       <x:c r="B68" s="33"/>
       <x:c r="C68" s="59"/>
       <x:c r="D68" s="52" t="str">
-        <x:f>IF($B68="","",IFERROR(VLOOKUP($B68,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B68="","",IFERROR(VLOOKUP($B68,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E68" s="62" t="str">
         <x:f>IF($D68="","",IF($D68="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F68" s="53" t="str">
-        <x:f>IF($B68="","",IFERROR(VLOOKUP($B68,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B68="","",IFERROR(VLOOKUP($B68,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B68),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G68" s="65" t="str">
         <x:f>IF($F68="","",IFERROR(VLOOKUP($F68,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4595,13 +4595,13 @@
       <x:c r="B69" s="33"/>
       <x:c r="C69" s="59"/>
       <x:c r="D69" s="52" t="str">
-        <x:f>IF($B69="","",IFERROR(VLOOKUP($B69,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B69="","",IFERROR(VLOOKUP($B69,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E69" s="62" t="str">
         <x:f>IF($D69="","",IF($D69="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F69" s="53" t="str">
-        <x:f>IF($B69="","",IFERROR(VLOOKUP($B69,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B69="","",IFERROR(VLOOKUP($B69,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B69),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G69" s="65" t="str">
         <x:f>IF($F69="","",IFERROR(VLOOKUP($F69,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4651,13 +4651,13 @@
       <x:c r="B70" s="33"/>
       <x:c r="C70" s="59"/>
       <x:c r="D70" s="52" t="str">
-        <x:f>IF($B70="","",IFERROR(VLOOKUP($B70,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B70="","",IFERROR(VLOOKUP($B70,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E70" s="62" t="str">
         <x:f>IF($D70="","",IF($D70="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F70" s="53" t="str">
-        <x:f>IF($B70="","",IFERROR(VLOOKUP($B70,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B70="","",IFERROR(VLOOKUP($B70,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B70),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G70" s="65" t="str">
         <x:f>IF($F70="","",IFERROR(VLOOKUP($F70,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4707,13 +4707,13 @@
       <x:c r="B71" s="33"/>
       <x:c r="C71" s="59"/>
       <x:c r="D71" s="52" t="str">
-        <x:f>IF($B71="","",IFERROR(VLOOKUP($B71,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B71="","",IFERROR(VLOOKUP($B71,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E71" s="62" t="str">
         <x:f>IF($D71="","",IF($D71="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F71" s="53" t="str">
-        <x:f>IF($B71="","",IFERROR(VLOOKUP($B71,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B71="","",IFERROR(VLOOKUP($B71,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B71),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G71" s="65" t="str">
         <x:f>IF($F71="","",IFERROR(VLOOKUP($F71,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4763,13 +4763,13 @@
       <x:c r="B72" s="33"/>
       <x:c r="C72" s="59"/>
       <x:c r="D72" s="52" t="str">
-        <x:f>IF($B72="","",IFERROR(VLOOKUP($B72,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B72="","",IFERROR(VLOOKUP($B72,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E72" s="62" t="str">
         <x:f>IF($D72="","",IF($D72="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F72" s="53" t="str">
-        <x:f>IF($B72="","",IFERROR(VLOOKUP($B72,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B72="","",IFERROR(VLOOKUP($B72,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B72),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G72" s="65" t="str">
         <x:f>IF($F72="","",IFERROR(VLOOKUP($F72,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4819,13 +4819,13 @@
       <x:c r="B73" s="33"/>
       <x:c r="C73" s="59"/>
       <x:c r="D73" s="52" t="str">
-        <x:f>IF($B73="","",IFERROR(VLOOKUP($B73,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B73="","",IFERROR(VLOOKUP($B73,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E73" s="62" t="str">
         <x:f>IF($D73="","",IF($D73="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F73" s="53" t="str">
-        <x:f>IF($B73="","",IFERROR(VLOOKUP($B73,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B73="","",IFERROR(VLOOKUP($B73,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B73),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G73" s="65" t="str">
         <x:f>IF($F73="","",IFERROR(VLOOKUP($F73,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4875,13 +4875,13 @@
       <x:c r="B74" s="33"/>
       <x:c r="C74" s="59"/>
       <x:c r="D74" s="52" t="str">
-        <x:f>IF($B74="","",IFERROR(VLOOKUP($B74,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B74="","",IFERROR(VLOOKUP($B74,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E74" s="62" t="str">
         <x:f>IF($D74="","",IF($D74="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F74" s="53" t="str">
-        <x:f>IF($B74="","",IFERROR(VLOOKUP($B74,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B74="","",IFERROR(VLOOKUP($B74,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B74),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G74" s="65" t="str">
         <x:f>IF($F74="","",IFERROR(VLOOKUP($F74,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4931,13 +4931,13 @@
       <x:c r="B75" s="33"/>
       <x:c r="C75" s="59"/>
       <x:c r="D75" s="52" t="str">
-        <x:f>IF($B75="","",IFERROR(VLOOKUP($B75,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B75="","",IFERROR(VLOOKUP($B75,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E75" s="62" t="str">
         <x:f>IF($D75="","",IF($D75="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F75" s="53" t="str">
-        <x:f>IF($B75="","",IFERROR(VLOOKUP($B75,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B75="","",IFERROR(VLOOKUP($B75,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B75),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G75" s="65" t="str">
         <x:f>IF($F75="","",IFERROR(VLOOKUP($F75,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -4987,13 +4987,13 @@
       <x:c r="B76" s="33"/>
       <x:c r="C76" s="59"/>
       <x:c r="D76" s="52" t="str">
-        <x:f>IF($B76="","",IFERROR(VLOOKUP($B76,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B76="","",IFERROR(VLOOKUP($B76,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E76" s="62" t="str">
         <x:f>IF($D76="","",IF($D76="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F76" s="53" t="str">
-        <x:f>IF($B76="","",IFERROR(VLOOKUP($B76,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B76="","",IFERROR(VLOOKUP($B76,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B76),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G76" s="65" t="str">
         <x:f>IF($F76="","",IFERROR(VLOOKUP($F76,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5043,13 +5043,13 @@
       <x:c r="B77" s="33"/>
       <x:c r="C77" s="59"/>
       <x:c r="D77" s="52" t="str">
-        <x:f>IF($B77="","",IFERROR(VLOOKUP($B77,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B77="","",IFERROR(VLOOKUP($B77,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E77" s="62" t="str">
         <x:f>IF($D77="","",IF($D77="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F77" s="53" t="str">
-        <x:f>IF($B77="","",IFERROR(VLOOKUP($B77,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B77="","",IFERROR(VLOOKUP($B77,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B77),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G77" s="65" t="str">
         <x:f>IF($F77="","",IFERROR(VLOOKUP($F77,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5099,13 +5099,13 @@
       <x:c r="B78" s="33"/>
       <x:c r="C78" s="59"/>
       <x:c r="D78" s="52" t="str">
-        <x:f>IF($B78="","",IFERROR(VLOOKUP($B78,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B78="","",IFERROR(VLOOKUP($B78,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E78" s="62" t="str">
         <x:f>IF($D78="","",IF($D78="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F78" s="53" t="str">
-        <x:f>IF($B78="","",IFERROR(VLOOKUP($B78,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B78="","",IFERROR(VLOOKUP($B78,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B78),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G78" s="65" t="str">
         <x:f>IF($F78="","",IFERROR(VLOOKUP($F78,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5155,13 +5155,13 @@
       <x:c r="B79" s="33"/>
       <x:c r="C79" s="59"/>
       <x:c r="D79" s="52" t="str">
-        <x:f>IF($B79="","",IFERROR(VLOOKUP($B79,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B79="","",IFERROR(VLOOKUP($B79,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E79" s="62" t="str">
         <x:f>IF($D79="","",IF($D79="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F79" s="53" t="str">
-        <x:f>IF($B79="","",IFERROR(VLOOKUP($B79,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B79="","",IFERROR(VLOOKUP($B79,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B79),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G79" s="65" t="str">
         <x:f>IF($F79="","",IFERROR(VLOOKUP($F79,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5211,13 +5211,13 @@
       <x:c r="B80" s="33"/>
       <x:c r="C80" s="59"/>
       <x:c r="D80" s="52" t="str">
-        <x:f>IF($B80="","",IFERROR(VLOOKUP($B80,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B80="","",IFERROR(VLOOKUP($B80,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E80" s="62" t="str">
         <x:f>IF($D80="","",IF($D80="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F80" s="53" t="str">
-        <x:f>IF($B80="","",IFERROR(VLOOKUP($B80,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B80="","",IFERROR(VLOOKUP($B80,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B80),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G80" s="65" t="str">
         <x:f>IF($F80="","",IFERROR(VLOOKUP($F80,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5267,13 +5267,13 @@
       <x:c r="B81" s="33"/>
       <x:c r="C81" s="59"/>
       <x:c r="D81" s="52" t="str">
-        <x:f>IF($B81="","",IFERROR(VLOOKUP($B81,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B81="","",IFERROR(VLOOKUP($B81,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E81" s="62" t="str">
         <x:f>IF($D81="","",IF($D81="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F81" s="53" t="str">
-        <x:f>IF($B81="","",IFERROR(VLOOKUP($B81,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B81="","",IFERROR(VLOOKUP($B81,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B81),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G81" s="65" t="str">
         <x:f>IF($F81="","",IFERROR(VLOOKUP($F81,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5323,13 +5323,13 @@
       <x:c r="B82" s="33"/>
       <x:c r="C82" s="59"/>
       <x:c r="D82" s="52" t="str">
-        <x:f>IF($B82="","",IFERROR(VLOOKUP($B82,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B82="","",IFERROR(VLOOKUP($B82,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E82" s="62" t="str">
         <x:f>IF($D82="","",IF($D82="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F82" s="53" t="str">
-        <x:f>IF($B82="","",IFERROR(VLOOKUP($B82,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B82="","",IFERROR(VLOOKUP($B82,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B82),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G82" s="65" t="str">
         <x:f>IF($F82="","",IFERROR(VLOOKUP($F82,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5379,13 +5379,13 @@
       <x:c r="B83" s="33"/>
       <x:c r="C83" s="59"/>
       <x:c r="D83" s="52" t="str">
-        <x:f>IF($B83="","",IFERROR(VLOOKUP($B83,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B83="","",IFERROR(VLOOKUP($B83,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E83" s="62" t="str">
         <x:f>IF($D83="","",IF($D83="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F83" s="53" t="str">
-        <x:f>IF($B83="","",IFERROR(VLOOKUP($B83,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B83="","",IFERROR(VLOOKUP($B83,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B83),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G83" s="65" t="str">
         <x:f>IF($F83="","",IFERROR(VLOOKUP($F83,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5435,13 +5435,13 @@
       <x:c r="B84" s="33"/>
       <x:c r="C84" s="59"/>
       <x:c r="D84" s="52" t="str">
-        <x:f>IF($B84="","",IFERROR(VLOOKUP($B84,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B84="","",IFERROR(VLOOKUP($B84,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E84" s="62" t="str">
         <x:f>IF($D84="","",IF($D84="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F84" s="53" t="str">
-        <x:f>IF($B84="","",IFERROR(VLOOKUP($B84,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B84="","",IFERROR(VLOOKUP($B84,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B84),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G84" s="65" t="str">
         <x:f>IF($F84="","",IFERROR(VLOOKUP($F84,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5491,13 +5491,13 @@
       <x:c r="B85" s="33"/>
       <x:c r="C85" s="59"/>
       <x:c r="D85" s="52" t="str">
-        <x:f>IF($B85="","",IFERROR(VLOOKUP($B85,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B85="","",IFERROR(VLOOKUP($B85,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E85" s="62" t="str">
         <x:f>IF($D85="","",IF($D85="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F85" s="53" t="str">
-        <x:f>IF($B85="","",IFERROR(VLOOKUP($B85,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B85="","",IFERROR(VLOOKUP($B85,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B85),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G85" s="65" t="str">
         <x:f>IF($F85="","",IFERROR(VLOOKUP($F85,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5547,13 +5547,13 @@
       <x:c r="B86" s="33"/>
       <x:c r="C86" s="59"/>
       <x:c r="D86" s="52" t="str">
-        <x:f>IF($B86="","",IFERROR(VLOOKUP($B86,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B86="","",IFERROR(VLOOKUP($B86,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E86" s="62" t="str">
         <x:f>IF($D86="","",IF($D86="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F86" s="53" t="str">
-        <x:f>IF($B86="","",IFERROR(VLOOKUP($B86,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B86="","",IFERROR(VLOOKUP($B86,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B86),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G86" s="65" t="str">
         <x:f>IF($F86="","",IFERROR(VLOOKUP($F86,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5603,13 +5603,13 @@
       <x:c r="B87" s="33"/>
       <x:c r="C87" s="59"/>
       <x:c r="D87" s="52" t="str">
-        <x:f>IF($B87="","",IFERROR(VLOOKUP($B87,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B87="","",IFERROR(VLOOKUP($B87,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E87" s="62" t="str">
         <x:f>IF($D87="","",IF($D87="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F87" s="53" t="str">
-        <x:f>IF($B87="","",IFERROR(VLOOKUP($B87,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B87="","",IFERROR(VLOOKUP($B87,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B87),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G87" s="65" t="str">
         <x:f>IF($F87="","",IFERROR(VLOOKUP($F87,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5659,13 +5659,13 @@
       <x:c r="B88" s="33"/>
       <x:c r="C88" s="59"/>
       <x:c r="D88" s="52" t="str">
-        <x:f>IF($B88="","",IFERROR(VLOOKUP($B88,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B88="","",IFERROR(VLOOKUP($B88,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E88" s="62" t="str">
         <x:f>IF($D88="","",IF($D88="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F88" s="53" t="str">
-        <x:f>IF($B88="","",IFERROR(VLOOKUP($B88,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B88="","",IFERROR(VLOOKUP($B88,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B88),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G88" s="65" t="str">
         <x:f>IF($F88="","",IFERROR(VLOOKUP($F88,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5715,13 +5715,13 @@
       <x:c r="B89" s="33"/>
       <x:c r="C89" s="59"/>
       <x:c r="D89" s="52" t="str">
-        <x:f>IF($B89="","",IFERROR(VLOOKUP($B89,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B89="","",IFERROR(VLOOKUP($B89,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E89" s="62" t="str">
         <x:f>IF($D89="","",IF($D89="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F89" s="53" t="str">
-        <x:f>IF($B89="","",IFERROR(VLOOKUP($B89,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B89="","",IFERROR(VLOOKUP($B89,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B89),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G89" s="65" t="str">
         <x:f>IF($F89="","",IFERROR(VLOOKUP($F89,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5771,13 +5771,13 @@
       <x:c r="B90" s="33"/>
       <x:c r="C90" s="59"/>
       <x:c r="D90" s="52" t="str">
-        <x:f>IF($B90="","",IFERROR(VLOOKUP($B90,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B90="","",IFERROR(VLOOKUP($B90,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E90" s="62" t="str">
         <x:f>IF($D90="","",IF($D90="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F90" s="53" t="str">
-        <x:f>IF($B90="","",IFERROR(VLOOKUP($B90,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B90="","",IFERROR(VLOOKUP($B90,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B90),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G90" s="65" t="str">
         <x:f>IF($F90="","",IFERROR(VLOOKUP($F90,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5827,13 +5827,13 @@
       <x:c r="B91" s="33"/>
       <x:c r="C91" s="59"/>
       <x:c r="D91" s="52" t="str">
-        <x:f>IF($B91="","",IFERROR(VLOOKUP($B91,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B91="","",IFERROR(VLOOKUP($B91,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E91" s="62" t="str">
         <x:f>IF($D91="","",IF($D91="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F91" s="53" t="str">
-        <x:f>IF($B91="","",IFERROR(VLOOKUP($B91,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B91="","",IFERROR(VLOOKUP($B91,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B91),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G91" s="65" t="str">
         <x:f>IF($F91="","",IFERROR(VLOOKUP($F91,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5883,13 +5883,13 @@
       <x:c r="B92" s="33"/>
       <x:c r="C92" s="59"/>
       <x:c r="D92" s="52" t="str">
-        <x:f>IF($B92="","",IFERROR(VLOOKUP($B92,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B92="","",IFERROR(VLOOKUP($B92,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E92" s="62" t="str">
         <x:f>IF($D92="","",IF($D92="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F92" s="53" t="str">
-        <x:f>IF($B92="","",IFERROR(VLOOKUP($B92,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B92="","",IFERROR(VLOOKUP($B92,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B92),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G92" s="65" t="str">
         <x:f>IF($F92="","",IFERROR(VLOOKUP($F92,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5939,13 +5939,13 @@
       <x:c r="B93" s="33"/>
       <x:c r="C93" s="59"/>
       <x:c r="D93" s="52" t="str">
-        <x:f>IF($B93="","",IFERROR(VLOOKUP($B93,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B93="","",IFERROR(VLOOKUP($B93,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E93" s="62" t="str">
         <x:f>IF($D93="","",IF($D93="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F93" s="53" t="str">
-        <x:f>IF($B93="","",IFERROR(VLOOKUP($B93,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B93="","",IFERROR(VLOOKUP($B93,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B93),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G93" s="65" t="str">
         <x:f>IF($F93="","",IFERROR(VLOOKUP($F93,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -5995,13 +5995,13 @@
       <x:c r="B94" s="33"/>
       <x:c r="C94" s="59"/>
       <x:c r="D94" s="52" t="str">
-        <x:f>IF($B94="","",IFERROR(VLOOKUP($B94,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B94="","",IFERROR(VLOOKUP($B94,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E94" s="62" t="str">
         <x:f>IF($D94="","",IF($D94="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F94" s="53" t="str">
-        <x:f>IF($B94="","",IFERROR(VLOOKUP($B94,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B94="","",IFERROR(VLOOKUP($B94,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B94),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G94" s="65" t="str">
         <x:f>IF($F94="","",IFERROR(VLOOKUP($F94,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6051,13 +6051,13 @@
       <x:c r="B95" s="33"/>
       <x:c r="C95" s="59"/>
       <x:c r="D95" s="52" t="str">
-        <x:f>IF($B95="","",IFERROR(VLOOKUP($B95,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B95="","",IFERROR(VLOOKUP($B95,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E95" s="62" t="str">
         <x:f>IF($D95="","",IF($D95="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F95" s="53" t="str">
-        <x:f>IF($B95="","",IFERROR(VLOOKUP($B95,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B95="","",IFERROR(VLOOKUP($B95,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B95),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G95" s="65" t="str">
         <x:f>IF($F95="","",IFERROR(VLOOKUP($F95,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6107,13 +6107,13 @@
       <x:c r="B96" s="33"/>
       <x:c r="C96" s="59"/>
       <x:c r="D96" s="52" t="str">
-        <x:f>IF($B96="","",IFERROR(VLOOKUP($B96,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B96="","",IFERROR(VLOOKUP($B96,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E96" s="62" t="str">
         <x:f>IF($D96="","",IF($D96="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F96" s="53" t="str">
-        <x:f>IF($B96="","",IFERROR(VLOOKUP($B96,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B96="","",IFERROR(VLOOKUP($B96,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B96),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G96" s="65" t="str">
         <x:f>IF($F96="","",IFERROR(VLOOKUP($F96,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6163,13 +6163,13 @@
       <x:c r="B97" s="33"/>
       <x:c r="C97" s="59"/>
       <x:c r="D97" s="52" t="str">
-        <x:f>IF($B97="","",IFERROR(VLOOKUP($B97,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B97="","",IFERROR(VLOOKUP($B97,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E97" s="62" t="str">
         <x:f>IF($D97="","",IF($D97="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F97" s="53" t="str">
-        <x:f>IF($B97="","",IFERROR(VLOOKUP($B97,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B97="","",IFERROR(VLOOKUP($B97,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B97),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G97" s="65" t="str">
         <x:f>IF($F97="","",IFERROR(VLOOKUP($F97,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6219,13 +6219,13 @@
       <x:c r="B98" s="33"/>
       <x:c r="C98" s="59"/>
       <x:c r="D98" s="52" t="str">
-        <x:f>IF($B98="","",IFERROR(VLOOKUP($B98,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B98="","",IFERROR(VLOOKUP($B98,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E98" s="62" t="str">
         <x:f>IF($D98="","",IF($D98="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F98" s="53" t="str">
-        <x:f>IF($B98="","",IFERROR(VLOOKUP($B98,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B98="","",IFERROR(VLOOKUP($B98,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B98),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G98" s="65" t="str">
         <x:f>IF($F98="","",IFERROR(VLOOKUP($F98,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6275,13 +6275,13 @@
       <x:c r="B99" s="33"/>
       <x:c r="C99" s="59"/>
       <x:c r="D99" s="52" t="str">
-        <x:f>IF($B99="","",IFERROR(VLOOKUP($B99,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B99="","",IFERROR(VLOOKUP($B99,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E99" s="62" t="str">
         <x:f>IF($D99="","",IF($D99="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F99" s="53" t="str">
-        <x:f>IF($B99="","",IFERROR(VLOOKUP($B99,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B99="","",IFERROR(VLOOKUP($B99,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B99),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G99" s="65" t="str">
         <x:f>IF($F99="","",IFERROR(VLOOKUP($F99,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6331,13 +6331,13 @@
       <x:c r="B100" s="33"/>
       <x:c r="C100" s="59"/>
       <x:c r="D100" s="52" t="str">
-        <x:f>IF($B100="","",IFERROR(VLOOKUP($B100,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B100="","",IFERROR(VLOOKUP($B100,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E100" s="62" t="str">
         <x:f>IF($D100="","",IF($D100="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F100" s="53" t="str">
-        <x:f>IF($B100="","",IFERROR(VLOOKUP($B100,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B100="","",IFERROR(VLOOKUP($B100,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B100),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G100" s="65" t="str">
         <x:f>IF($F100="","",IFERROR(VLOOKUP($F100,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6387,13 +6387,13 @@
       <x:c r="B101" s="33"/>
       <x:c r="C101" s="59"/>
       <x:c r="D101" s="52" t="str">
-        <x:f>IF($B101="","",IFERROR(VLOOKUP($B101,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B101="","",IFERROR(VLOOKUP($B101,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E101" s="62" t="str">
         <x:f>IF($D101="","",IF($D101="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F101" s="53" t="str">
-        <x:f>IF($B101="","",IFERROR(VLOOKUP($B101,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B101="","",IFERROR(VLOOKUP($B101,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B101),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G101" s="65" t="str">
         <x:f>IF($F101="","",IFERROR(VLOOKUP($F101,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6443,13 +6443,13 @@
       <x:c r="B102" s="33"/>
       <x:c r="C102" s="59"/>
       <x:c r="D102" s="52" t="str">
-        <x:f>IF($B102="","",IFERROR(VLOOKUP($B102,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B102="","",IFERROR(VLOOKUP($B102,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E102" s="62" t="str">
         <x:f>IF($D102="","",IF($D102="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F102" s="53" t="str">
-        <x:f>IF($B102="","",IFERROR(VLOOKUP($B102,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B102="","",IFERROR(VLOOKUP($B102,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B102),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G102" s="65" t="str">
         <x:f>IF($F102="","",IFERROR(VLOOKUP($F102,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6499,13 +6499,13 @@
       <x:c r="B103" s="33"/>
       <x:c r="C103" s="59"/>
       <x:c r="D103" s="52" t="str">
-        <x:f>IF($B103="","",IFERROR(VLOOKUP($B103,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B103="","",IFERROR(VLOOKUP($B103,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E103" s="62" t="str">
         <x:f>IF($D103="","",IF($D103="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F103" s="53" t="str">
-        <x:f>IF($B103="","",IFERROR(VLOOKUP($B103,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B103="","",IFERROR(VLOOKUP($B103,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B103),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G103" s="65" t="str">
         <x:f>IF($F103="","",IFERROR(VLOOKUP($F103,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6555,13 +6555,13 @@
       <x:c r="B104" s="33"/>
       <x:c r="C104" s="59"/>
       <x:c r="D104" s="52" t="str">
-        <x:f>IF($B104="","",IFERROR(VLOOKUP($B104,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B104="","",IFERROR(VLOOKUP($B104,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E104" s="62" t="str">
         <x:f>IF($D104="","",IF($D104="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F104" s="53" t="str">
-        <x:f>IF($B104="","",IFERROR(VLOOKUP($B104,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B104="","",IFERROR(VLOOKUP($B104,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B104),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G104" s="65" t="str">
         <x:f>IF($F104="","",IFERROR(VLOOKUP($F104,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6611,13 +6611,13 @@
       <x:c r="B105" s="33"/>
       <x:c r="C105" s="59"/>
       <x:c r="D105" s="52" t="str">
-        <x:f>IF($B105="","",IFERROR(VLOOKUP($B105,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B105="","",IFERROR(VLOOKUP($B105,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E105" s="62" t="str">
         <x:f>IF($D105="","",IF($D105="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F105" s="53" t="str">
-        <x:f>IF($B105="","",IFERROR(VLOOKUP($B105,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B105="","",IFERROR(VLOOKUP($B105,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B105),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G105" s="65" t="str">
         <x:f>IF($F105="","",IFERROR(VLOOKUP($F105,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6667,13 +6667,13 @@
       <x:c r="B106" s="33"/>
       <x:c r="C106" s="59"/>
       <x:c r="D106" s="52" t="str">
-        <x:f>IF($B106="","",IFERROR(VLOOKUP($B106,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B106="","",IFERROR(VLOOKUP($B106,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E106" s="62" t="str">
         <x:f>IF($D106="","",IF($D106="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F106" s="53" t="str">
-        <x:f>IF($B106="","",IFERROR(VLOOKUP($B106,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B106="","",IFERROR(VLOOKUP($B106,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B106),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G106" s="65" t="str">
         <x:f>IF($F106="","",IFERROR(VLOOKUP($F106,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6723,13 +6723,13 @@
       <x:c r="B107" s="33"/>
       <x:c r="C107" s="59"/>
       <x:c r="D107" s="52" t="str">
-        <x:f>IF($B107="","",IFERROR(VLOOKUP($B107,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B107="","",IFERROR(VLOOKUP($B107,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E107" s="62" t="str">
         <x:f>IF($D107="","",IF($D107="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F107" s="53" t="str">
-        <x:f>IF($B107="","",IFERROR(VLOOKUP($B107,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B107="","",IFERROR(VLOOKUP($B107,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B107),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G107" s="65" t="str">
         <x:f>IF($F107="","",IFERROR(VLOOKUP($F107,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6779,13 +6779,13 @@
       <x:c r="B108" s="33"/>
       <x:c r="C108" s="59"/>
       <x:c r="D108" s="52" t="str">
-        <x:f>IF($B108="","",IFERROR(VLOOKUP($B108,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B108="","",IFERROR(VLOOKUP($B108,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E108" s="62" t="str">
         <x:f>IF($D108="","",IF($D108="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F108" s="53" t="str">
-        <x:f>IF($B108="","",IFERROR(VLOOKUP($B108,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B108="","",IFERROR(VLOOKUP($B108,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B108),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G108" s="65" t="str">
         <x:f>IF($F108="","",IFERROR(VLOOKUP($F108,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6835,13 +6835,13 @@
       <x:c r="B109" s="33"/>
       <x:c r="C109" s="59"/>
       <x:c r="D109" s="52" t="str">
-        <x:f>IF($B109="","",IFERROR(VLOOKUP($B109,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B109="","",IFERROR(VLOOKUP($B109,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E109" s="62" t="str">
         <x:f>IF($D109="","",IF($D109="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F109" s="53" t="str">
-        <x:f>IF($B109="","",IFERROR(VLOOKUP($B109,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B109="","",IFERROR(VLOOKUP($B109,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B109),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G109" s="65" t="str">
         <x:f>IF($F109="","",IFERROR(VLOOKUP($F109,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6891,13 +6891,13 @@
       <x:c r="B110" s="33"/>
       <x:c r="C110" s="59"/>
       <x:c r="D110" s="52" t="str">
-        <x:f>IF($B110="","",IFERROR(VLOOKUP($B110,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B110="","",IFERROR(VLOOKUP($B110,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E110" s="62" t="str">
         <x:f>IF($D110="","",IF($D110="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F110" s="53" t="str">
-        <x:f>IF($B110="","",IFERROR(VLOOKUP($B110,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B110="","",IFERROR(VLOOKUP($B110,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B110),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G110" s="65" t="str">
         <x:f>IF($F110="","",IFERROR(VLOOKUP($F110,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -6947,13 +6947,13 @@
       <x:c r="B111" s="33"/>
       <x:c r="C111" s="59"/>
       <x:c r="D111" s="52" t="str">
-        <x:f>IF($B111="","",IFERROR(VLOOKUP($B111,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B111="","",IFERROR(VLOOKUP($B111,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E111" s="62" t="str">
         <x:f>IF($D111="","",IF($D111="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F111" s="53" t="str">
-        <x:f>IF($B111="","",IFERROR(VLOOKUP($B111,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B111="","",IFERROR(VLOOKUP($B111,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B111),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G111" s="65" t="str">
         <x:f>IF($F111="","",IFERROR(VLOOKUP($F111,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7003,13 +7003,13 @@
       <x:c r="B112" s="33"/>
       <x:c r="C112" s="59"/>
       <x:c r="D112" s="52" t="str">
-        <x:f>IF($B112="","",IFERROR(VLOOKUP($B112,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B112="","",IFERROR(VLOOKUP($B112,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E112" s="62" t="str">
         <x:f>IF($D112="","",IF($D112="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F112" s="53" t="str">
-        <x:f>IF($B112="","",IFERROR(VLOOKUP($B112,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B112="","",IFERROR(VLOOKUP($B112,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B112),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G112" s="65" t="str">
         <x:f>IF($F112="","",IFERROR(VLOOKUP($F112,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7059,13 +7059,13 @@
       <x:c r="B113" s="33"/>
       <x:c r="C113" s="59"/>
       <x:c r="D113" s="52" t="str">
-        <x:f>IF($B113="","",IFERROR(VLOOKUP($B113,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B113="","",IFERROR(VLOOKUP($B113,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E113" s="62" t="str">
         <x:f>IF($D113="","",IF($D113="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F113" s="53" t="str">
-        <x:f>IF($B113="","",IFERROR(VLOOKUP($B113,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B113="","",IFERROR(VLOOKUP($B113,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B113),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G113" s="65" t="str">
         <x:f>IF($F113="","",IFERROR(VLOOKUP($F113,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7115,13 +7115,13 @@
       <x:c r="B114" s="33"/>
       <x:c r="C114" s="59"/>
       <x:c r="D114" s="52" t="str">
-        <x:f>IF($B114="","",IFERROR(VLOOKUP($B114,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B114="","",IFERROR(VLOOKUP($B114,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E114" s="62" t="str">
         <x:f>IF($D114="","",IF($D114="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F114" s="53" t="str">
-        <x:f>IF($B114="","",IFERROR(VLOOKUP($B114,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B114="","",IFERROR(VLOOKUP($B114,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B114),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G114" s="65" t="str">
         <x:f>IF($F114="","",IFERROR(VLOOKUP($F114,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7162,20 +7162,23 @@
       <x:c r="S114" s="54" t="str">
         <x:f>IF(AND($A114="",$B114="",$C114=""),"",IF($A114="","Missing Assignment Number",IF($B114="","Select Job Title",IF($C114="","Enter Pay Rate",IF($F114="","Job Title not found","Ready")))))</x:f>
       </x:c>
-      <x:c r="U114"/>
+      <x:c r="U114" t="str">
+        <x:v>CQ engineer  Site Engineering P1-G midpoint   (CQ=Commissioning&amp;Qualification)
+1 stap boven mid</x:v>
+      </x:c>
     </x:row>
     <x:row r="115" ht="22" customHeight="1">
       <x:c r="A115" s="32"/>
       <x:c r="B115" s="33"/>
       <x:c r="C115" s="59"/>
       <x:c r="D115" s="52" t="str">
-        <x:f>IF($B115="","",IFERROR(VLOOKUP($B115,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B115="","",IFERROR(VLOOKUP($B115,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E115" s="62" t="str">
         <x:f>IF($D115="","",IF($D115="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F115" s="53" t="str">
-        <x:f>IF($B115="","",IFERROR(VLOOKUP($B115,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B115="","",IFERROR(VLOOKUP($B115,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B115),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G115" s="65" t="str">
         <x:f>IF($F115="","",IFERROR(VLOOKUP($F115,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7216,20 +7219,22 @@
       <x:c r="S115" s="54" t="str">
         <x:f>IF(AND($A115="",$B115="",$C115=""),"",IF($A115="","Missing Assignment Number",IF($B115="","Select Job Title",IF($C115="","Enter Pay Rate",IF($F115="","Job Title not found","Ready")))))</x:f>
       </x:c>
-      <x:c r="U115"/>
+      <x:c r="U115" t="str">
+        <x:v>CQ engineer Site Engineering P1-F midpoint   (CQ=Commissioning&amp;Qualification)</x:v>
+      </x:c>
     </x:row>
     <x:row r="116" ht="22" customHeight="1">
       <x:c r="A116" s="32"/>
       <x:c r="B116" s="33"/>
       <x:c r="C116" s="59"/>
       <x:c r="D116" s="52" t="str">
-        <x:f>IF($B116="","",IFERROR(VLOOKUP($B116,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B116="","",IFERROR(VLOOKUP($B116,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E116" s="62" t="str">
         <x:f>IF($D116="","",IF($D116="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F116" s="53" t="str">
-        <x:f>IF($B116="","",IFERROR(VLOOKUP($B116,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B116="","",IFERROR(VLOOKUP($B116,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B116),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G116" s="65" t="str">
         <x:f>IF($F116="","",IFERROR(VLOOKUP($F116,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7270,20 +7275,22 @@
       <x:c r="S116" s="54" t="str">
         <x:f>IF(AND($A116="",$B116="",$C116=""),"",IF($A116="","Missing Assignment Number",IF($B116="","Select Job Title",IF($C116="","Enter Pay Rate",IF($F116="","Job Title not found","Ready")))))</x:f>
       </x:c>
-      <x:c r="U116"/>
+      <x:c r="U116" t="str">
+        <x:v>CQ engineer Site Engineering P1-G Tussen midpoint en max.   (CQ=Commissioning&amp;Qualification)</x:v>
+      </x:c>
     </x:row>
     <x:row r="117" ht="22" customHeight="1">
       <x:c r="A117" s="32"/>
       <x:c r="B117" s="33"/>
       <x:c r="C117" s="59"/>
       <x:c r="D117" s="52" t="str">
-        <x:f>IF($B117="","",IFERROR(VLOOKUP($B117,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B117="","",IFERROR(VLOOKUP($B117,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E117" s="62" t="str">
         <x:f>IF($D117="","",IF($D117="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F117" s="53" t="str">
-        <x:f>IF($B117="","",IFERROR(VLOOKUP($B117,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B117="","",IFERROR(VLOOKUP($B117,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B117),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G117" s="65" t="str">
         <x:f>IF($F117="","",IFERROR(VLOOKUP($F117,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7324,20 +7331,23 @@
       <x:c r="S117" s="54" t="str">
         <x:f>IF(AND($A117="",$B117="",$C117=""),"",IF($A117="","Missing Assignment Number",IF($B117="","Select Job Title",IF($C117="","Enter Pay Rate",IF($F117="","Job Title not found","Ready")))))</x:f>
       </x:c>
-      <x:c r="U117"/>
+      <x:c r="U117" t="str">
+        <x:v>SPOC=Programma-manager Site Engineering  P3-J  Tussen midpoint en max.
+2 stappen boven mid 1 stap  onder max</x:v>
+      </x:c>
     </x:row>
     <x:row r="118" ht="22" customHeight="1">
       <x:c r="A118" s="32"/>
       <x:c r="B118" s="33"/>
       <x:c r="C118" s="59"/>
       <x:c r="D118" s="52" t="str">
-        <x:f>IF($B118="","",IFERROR(VLOOKUP($B118,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B118="","",IFERROR(VLOOKUP($B118,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E118" s="62" t="str">
         <x:f>IF($D118="","",IF($D118="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F118" s="53" t="str">
-        <x:f>IF($B118="","",IFERROR(VLOOKUP($B118,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B118="","",IFERROR(VLOOKUP($B118,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B118),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G118" s="65" t="str">
         <x:f>IF($F118="","",IFERROR(VLOOKUP($F118,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7378,20 +7388,23 @@
       <x:c r="S118" s="54" t="str">
         <x:f>IF(AND($A118="",$B118="",$C118=""),"",IF($A118="","Missing Assignment Number",IF($B118="","Select Job Title",IF($C118="","Enter Pay Rate",IF($F118="","Job Title not found","Ready")))))</x:f>
       </x:c>
-      <x:c r="U118"/>
+      <x:c r="U118" t="str">
+        <x:v>Projectmanager Site Engineering P2-H Tussen midpoint en max.
+2 stappen boven mid 1 stap onder max</x:v>
+      </x:c>
     </x:row>
     <x:row r="119" ht="22" customHeight="1">
       <x:c r="A119" s="32"/>
       <x:c r="B119" s="33"/>
       <x:c r="C119" s="59"/>
       <x:c r="D119" s="52" t="str">
-        <x:f>IF($B119="","",IFERROR(VLOOKUP($B119,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B119="","",IFERROR(VLOOKUP($B119,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E119" s="62" t="str">
         <x:f>IF($D119="","",IF($D119="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F119" s="53" t="str">
-        <x:f>IF($B119="","",IFERROR(VLOOKUP($B119,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B119="","",IFERROR(VLOOKUP($B119,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B119),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G119" s="65" t="str">
         <x:f>IF($F119="","",IFERROR(VLOOKUP($F119,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7432,20 +7445,22 @@
       <x:c r="S119" s="54" t="str">
         <x:f>IF(AND($A119="",$B119="",$C119=""),"",IF($A119="","Missing Assignment Number",IF($B119="","Select Job Title",IF($C119="","Enter Pay Rate",IF($F119="","Job Title not found","Ready")))))</x:f>
       </x:c>
-      <x:c r="U119"/>
+      <x:c r="U119" t="str">
+        <x:v>Civil engineer Site Engineering P1-G midpoint 1 stap boven</x:v>
+      </x:c>
     </x:row>
     <x:row r="120" ht="22" customHeight="1">
       <x:c r="A120" s="32"/>
       <x:c r="B120" s="33"/>
       <x:c r="C120" s="59"/>
       <x:c r="D120" s="52" t="str">
-        <x:f>IF($B120="","",IFERROR(VLOOKUP($B120,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B120="","",IFERROR(VLOOKUP($B120,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E120" s="62" t="str">
         <x:f>IF($D120="","",IF($D120="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F120" s="53" t="str">
-        <x:f>IF($B120="","",IFERROR(VLOOKUP($B120,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B120="","",IFERROR(VLOOKUP($B120,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B120),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G120" s="65" t="str">
         <x:f>IF($F120="","",IFERROR(VLOOKUP($F120,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7493,13 +7508,13 @@
       <x:c r="B121" s="33"/>
       <x:c r="C121" s="59"/>
       <x:c r="D121" s="52" t="str">
-        <x:f>IF($B121="","",IFERROR(VLOOKUP($B121,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B121="","",IFERROR(VLOOKUP($B121,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E121" s="62" t="str">
         <x:f>IF($D121="","",IF($D121="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F121" s="53" t="str">
-        <x:f>IF($B121="","",IFERROR(VLOOKUP($B121,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B121="","",IFERROR(VLOOKUP($B121,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B121),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G121" s="65" t="str">
         <x:f>IF($F121="","",IFERROR(VLOOKUP($F121,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7547,13 +7562,13 @@
       <x:c r="B122" s="33"/>
       <x:c r="C122" s="59"/>
       <x:c r="D122" s="52" t="str">
-        <x:f>IF($B122="","",IFERROR(VLOOKUP($B122,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B122="","",IFERROR(VLOOKUP($B122,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E122" s="62" t="str">
         <x:f>IF($D122="","",IF($D122="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F122" s="53" t="str">
-        <x:f>IF($B122="","",IFERROR(VLOOKUP($B122,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B122="","",IFERROR(VLOOKUP($B122,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B122),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G122" s="65" t="str">
         <x:f>IF($F122="","",IFERROR(VLOOKUP($F122,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7601,13 +7616,13 @@
       <x:c r="B123" s="33"/>
       <x:c r="C123" s="59"/>
       <x:c r="D123" s="52" t="str">
-        <x:f>IF($B123="","",IFERROR(VLOOKUP($B123,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B123="","",IFERROR(VLOOKUP($B123,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E123" s="62" t="str">
         <x:f>IF($D123="","",IF($D123="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F123" s="53" t="str">
-        <x:f>IF($B123="","",IFERROR(VLOOKUP($B123,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B123="","",IFERROR(VLOOKUP($B123,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B123),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G123" s="65" t="str">
         <x:f>IF($F123="","",IFERROR(VLOOKUP($F123,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7655,13 +7670,13 @@
       <x:c r="B124" s="33"/>
       <x:c r="C124" s="59"/>
       <x:c r="D124" s="52" t="str">
-        <x:f>IF($B124="","",IFERROR(VLOOKUP($B124,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B124="","",IFERROR(VLOOKUP($B124,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E124" s="62" t="str">
         <x:f>IF($D124="","",IF($D124="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F124" s="53" t="str">
-        <x:f>IF($B124="","",IFERROR(VLOOKUP($B124,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B124="","",IFERROR(VLOOKUP($B124,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B124),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G124" s="65" t="str">
         <x:f>IF($F124="","",IFERROR(VLOOKUP($F124,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7709,13 +7724,13 @@
       <x:c r="B125" s="33"/>
       <x:c r="C125" s="59"/>
       <x:c r="D125" s="52" t="str">
-        <x:f>IF($B125="","",IFERROR(VLOOKUP($B125,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B125="","",IFERROR(VLOOKUP($B125,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E125" s="62" t="str">
         <x:f>IF($D125="","",IF($D125="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F125" s="53" t="str">
-        <x:f>IF($B125="","",IFERROR(VLOOKUP($B125,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B125="","",IFERROR(VLOOKUP($B125,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B125),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G125" s="65" t="str">
         <x:f>IF($F125="","",IFERROR(VLOOKUP($F125,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7763,13 +7778,13 @@
       <x:c r="B126" s="33"/>
       <x:c r="C126" s="59"/>
       <x:c r="D126" s="52" t="str">
-        <x:f>IF($B126="","",IFERROR(VLOOKUP($B126,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B126="","",IFERROR(VLOOKUP($B126,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E126" s="62" t="str">
         <x:f>IF($D126="","",IF($D126="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F126" s="53" t="str">
-        <x:f>IF($B126="","",IFERROR(VLOOKUP($B126,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B126="","",IFERROR(VLOOKUP($B126,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B126),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G126" s="65" t="str">
         <x:f>IF($F126="","",IFERROR(VLOOKUP($F126,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7817,13 +7832,13 @@
       <x:c r="B127" s="33"/>
       <x:c r="C127" s="59"/>
       <x:c r="D127" s="52" t="str">
-        <x:f>IF($B127="","",IFERROR(VLOOKUP($B127,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B127="","",IFERROR(VLOOKUP($B127,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E127" s="62" t="str">
         <x:f>IF($D127="","",IF($D127="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F127" s="53" t="str">
-        <x:f>IF($B127="","",IFERROR(VLOOKUP($B127,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B127="","",IFERROR(VLOOKUP($B127,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B127),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G127" s="65" t="str">
         <x:f>IF($F127="","",IFERROR(VLOOKUP($F127,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7871,13 +7886,13 @@
       <x:c r="B128" s="33"/>
       <x:c r="C128" s="59"/>
       <x:c r="D128" s="52" t="str">
-        <x:f>IF($B128="","",IFERROR(VLOOKUP($B128,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B128="","",IFERROR(VLOOKUP($B128,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E128" s="62" t="str">
         <x:f>IF($D128="","",IF($D128="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F128" s="53" t="str">
-        <x:f>IF($B128="","",IFERROR(VLOOKUP($B128,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B128="","",IFERROR(VLOOKUP($B128,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B128),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G128" s="65" t="str">
         <x:f>IF($F128="","",IFERROR(VLOOKUP($F128,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7925,13 +7940,13 @@
       <x:c r="B129" s="33"/>
       <x:c r="C129" s="59"/>
       <x:c r="D129" s="52" t="str">
-        <x:f>IF($B129="","",IFERROR(VLOOKUP($B129,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B129="","",IFERROR(VLOOKUP($B129,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E129" s="62" t="str">
         <x:f>IF($D129="","",IF($D129="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F129" s="53" t="str">
-        <x:f>IF($B129="","",IFERROR(VLOOKUP($B129,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B129="","",IFERROR(VLOOKUP($B129,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B129),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G129" s="65" t="str">
         <x:f>IF($F129="","",IFERROR(VLOOKUP($F129,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -7979,13 +7994,13 @@
       <x:c r="B130" s="33"/>
       <x:c r="C130" s="59"/>
       <x:c r="D130" s="52" t="str">
-        <x:f>IF($B130="","",IFERROR(VLOOKUP($B130,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B130="","",IFERROR(VLOOKUP($B130,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E130" s="62" t="str">
         <x:f>IF($D130="","",IF($D130="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F130" s="53" t="str">
-        <x:f>IF($B130="","",IFERROR(VLOOKUP($B130,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B130="","",IFERROR(VLOOKUP($B130,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B130),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G130" s="65" t="str">
         <x:f>IF($F130="","",IFERROR(VLOOKUP($F130,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8033,13 +8048,13 @@
       <x:c r="B131" s="33"/>
       <x:c r="C131" s="59"/>
       <x:c r="D131" s="52" t="str">
-        <x:f>IF($B131="","",IFERROR(VLOOKUP($B131,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B131="","",IFERROR(VLOOKUP($B131,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E131" s="62" t="str">
         <x:f>IF($D131="","",IF($D131="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F131" s="53" t="str">
-        <x:f>IF($B131="","",IFERROR(VLOOKUP($B131,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B131="","",IFERROR(VLOOKUP($B131,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B131),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G131" s="65" t="str">
         <x:f>IF($F131="","",IFERROR(VLOOKUP($F131,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8087,13 +8102,13 @@
       <x:c r="B132" s="33"/>
       <x:c r="C132" s="59"/>
       <x:c r="D132" s="52" t="str">
-        <x:f>IF($B132="","",IFERROR(VLOOKUP($B132,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B132="","",IFERROR(VLOOKUP($B132,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E132" s="62" t="str">
         <x:f>IF($D132="","",IF($D132="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F132" s="53" t="str">
-        <x:f>IF($B132="","",IFERROR(VLOOKUP($B132,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B132="","",IFERROR(VLOOKUP($B132,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B132),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G132" s="65" t="str">
         <x:f>IF($F132="","",IFERROR(VLOOKUP($F132,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8141,13 +8156,13 @@
       <x:c r="B133" s="33"/>
       <x:c r="C133" s="59"/>
       <x:c r="D133" s="52" t="str">
-        <x:f>IF($B133="","",IFERROR(VLOOKUP($B133,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B133="","",IFERROR(VLOOKUP($B133,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E133" s="62" t="str">
         <x:f>IF($D133="","",IF($D133="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F133" s="53" t="str">
-        <x:f>IF($B133="","",IFERROR(VLOOKUP($B133,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B133="","",IFERROR(VLOOKUP($B133,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B133),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G133" s="65" t="str">
         <x:f>IF($F133="","",IFERROR(VLOOKUP($F133,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8195,13 +8210,13 @@
       <x:c r="B134" s="33"/>
       <x:c r="C134" s="59"/>
       <x:c r="D134" s="52" t="str">
-        <x:f>IF($B134="","",IFERROR(VLOOKUP($B134,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B134="","",IFERROR(VLOOKUP($B134,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E134" s="62" t="str">
         <x:f>IF($D134="","",IF($D134="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F134" s="53" t="str">
-        <x:f>IF($B134="","",IFERROR(VLOOKUP($B134,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B134="","",IFERROR(VLOOKUP($B134,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B134),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G134" s="65" t="str">
         <x:f>IF($F134="","",IFERROR(VLOOKUP($F134,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8249,13 +8264,13 @@
       <x:c r="B135" s="33"/>
       <x:c r="C135" s="59"/>
       <x:c r="D135" s="52" t="str">
-        <x:f>IF($B135="","",IFERROR(VLOOKUP($B135,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B135="","",IFERROR(VLOOKUP($B135,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E135" s="62" t="str">
         <x:f>IF($D135="","",IF($D135="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F135" s="53" t="str">
-        <x:f>IF($B135="","",IFERROR(VLOOKUP($B135,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B135="","",IFERROR(VLOOKUP($B135,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B135),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G135" s="65" t="str">
         <x:f>IF($F135="","",IFERROR(VLOOKUP($F135,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8303,13 +8318,13 @@
       <x:c r="B136" s="33"/>
       <x:c r="C136" s="59"/>
       <x:c r="D136" s="52" t="str">
-        <x:f>IF($B136="","",IFERROR(VLOOKUP($B136,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B136="","",IFERROR(VLOOKUP($B136,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E136" s="62" t="str">
         <x:f>IF($D136="","",IF($D136="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F136" s="53" t="str">
-        <x:f>IF($B136="","",IFERROR(VLOOKUP($B136,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B136="","",IFERROR(VLOOKUP($B136,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B136),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G136" s="65" t="str">
         <x:f>IF($F136="","",IFERROR(VLOOKUP($F136,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8357,13 +8372,13 @@
       <x:c r="B137" s="33"/>
       <x:c r="C137" s="59"/>
       <x:c r="D137" s="52" t="str">
-        <x:f>IF($B137="","",IFERROR(VLOOKUP($B137,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B137="","",IFERROR(VLOOKUP($B137,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E137" s="62" t="str">
         <x:f>IF($D137="","",IF($D137="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F137" s="53" t="str">
-        <x:f>IF($B137="","",IFERROR(VLOOKUP($B137,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B137="","",IFERROR(VLOOKUP($B137,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B137),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G137" s="65" t="str">
         <x:f>IF($F137="","",IFERROR(VLOOKUP($F137,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8411,13 +8426,13 @@
       <x:c r="B138" s="33"/>
       <x:c r="C138" s="59"/>
       <x:c r="D138" s="52" t="str">
-        <x:f>IF($B138="","",IFERROR(VLOOKUP($B138,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B138="","",IFERROR(VLOOKUP($B138,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E138" s="62" t="str">
         <x:f>IF($D138="","",IF($D138="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F138" s="53" t="str">
-        <x:f>IF($B138="","",IFERROR(VLOOKUP($B138,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B138="","",IFERROR(VLOOKUP($B138,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B138),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G138" s="65" t="str">
         <x:f>IF($F138="","",IFERROR(VLOOKUP($F138,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8465,13 +8480,13 @@
       <x:c r="B139" s="33"/>
       <x:c r="C139" s="59"/>
       <x:c r="D139" s="52" t="str">
-        <x:f>IF($B139="","",IFERROR(VLOOKUP($B139,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B139="","",IFERROR(VLOOKUP($B139,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E139" s="62" t="str">
         <x:f>IF($D139="","",IF($D139="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F139" s="53" t="str">
-        <x:f>IF($B139="","",IFERROR(VLOOKUP($B139,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B139="","",IFERROR(VLOOKUP($B139,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B139),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G139" s="65" t="str">
         <x:f>IF($F139="","",IFERROR(VLOOKUP($F139,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8519,13 +8534,13 @@
       <x:c r="B140" s="33"/>
       <x:c r="C140" s="59"/>
       <x:c r="D140" s="52" t="str">
-        <x:f>IF($B140="","",IFERROR(VLOOKUP($B140,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B140="","",IFERROR(VLOOKUP($B140,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E140" s="62" t="str">
         <x:f>IF($D140="","",IF($D140="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F140" s="53" t="str">
-        <x:f>IF($B140="","",IFERROR(VLOOKUP($B140,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B140="","",IFERROR(VLOOKUP($B140,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B140),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G140" s="65" t="str">
         <x:f>IF($F140="","",IFERROR(VLOOKUP($F140,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8573,13 +8588,13 @@
       <x:c r="B141" s="33"/>
       <x:c r="C141" s="59"/>
       <x:c r="D141" s="52" t="str">
-        <x:f>IF($B141="","",IFERROR(VLOOKUP($B141,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B141="","",IFERROR(VLOOKUP($B141,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E141" s="62" t="str">
         <x:f>IF($D141="","",IF($D141="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F141" s="53" t="str">
-        <x:f>IF($B141="","",IFERROR(VLOOKUP($B141,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B141="","",IFERROR(VLOOKUP($B141,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B141),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G141" s="65" t="str">
         <x:f>IF($F141="","",IFERROR(VLOOKUP($F141,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8627,13 +8642,13 @@
       <x:c r="B142" s="33"/>
       <x:c r="C142" s="59"/>
       <x:c r="D142" s="52" t="str">
-        <x:f>IF($B142="","",IFERROR(VLOOKUP($B142,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B142="","",IFERROR(VLOOKUP($B142,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E142" s="62" t="str">
         <x:f>IF($D142="","",IF($D142="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F142" s="53" t="str">
-        <x:f>IF($B142="","",IFERROR(VLOOKUP($B142,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B142="","",IFERROR(VLOOKUP($B142,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B142),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G142" s="65" t="str">
         <x:f>IF($F142="","",IFERROR(VLOOKUP($F142,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8681,13 +8696,13 @@
       <x:c r="B143" s="33"/>
       <x:c r="C143" s="59"/>
       <x:c r="D143" s="52" t="str">
-        <x:f>IF($B143="","",IFERROR(VLOOKUP($B143,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B143="","",IFERROR(VLOOKUP($B143,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E143" s="62" t="str">
         <x:f>IF($D143="","",IF($D143="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F143" s="53" t="str">
-        <x:f>IF($B143="","",IFERROR(VLOOKUP($B143,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B143="","",IFERROR(VLOOKUP($B143,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B143),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G143" s="65" t="str">
         <x:f>IF($F143="","",IFERROR(VLOOKUP($F143,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8735,13 +8750,13 @@
       <x:c r="B144" s="33"/>
       <x:c r="C144" s="59"/>
       <x:c r="D144" s="52" t="str">
-        <x:f>IF($B144="","",IFERROR(VLOOKUP($B144,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B144="","",IFERROR(VLOOKUP($B144,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E144" s="62" t="str">
         <x:f>IF($D144="","",IF($D144="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F144" s="53" t="str">
-        <x:f>IF($B144="","",IFERROR(VLOOKUP($B144,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B144="","",IFERROR(VLOOKUP($B144,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B144),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G144" s="65" t="str">
         <x:f>IF($F144="","",IFERROR(VLOOKUP($F144,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8789,13 +8804,13 @@
       <x:c r="B145" s="33"/>
       <x:c r="C145" s="59"/>
       <x:c r="D145" s="52" t="str">
-        <x:f>IF($B145="","",IFERROR(VLOOKUP($B145,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B145="","",IFERROR(VLOOKUP($B145,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E145" s="62" t="str">
         <x:f>IF($D145="","",IF($D145="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F145" s="53" t="str">
-        <x:f>IF($B145="","",IFERROR(VLOOKUP($B145,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B145="","",IFERROR(VLOOKUP($B145,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B145),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G145" s="65" t="str">
         <x:f>IF($F145="","",IFERROR(VLOOKUP($F145,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8843,13 +8858,13 @@
       <x:c r="B146" s="33"/>
       <x:c r="C146" s="59"/>
       <x:c r="D146" s="52" t="str">
-        <x:f>IF($B146="","",IFERROR(VLOOKUP($B146,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B146="","",IFERROR(VLOOKUP($B146,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E146" s="62" t="str">
         <x:f>IF($D146="","",IF($D146="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F146" s="53" t="str">
-        <x:f>IF($B146="","",IFERROR(VLOOKUP($B146,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B146="","",IFERROR(VLOOKUP($B146,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B146),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G146" s="65" t="str">
         <x:f>IF($F146="","",IFERROR(VLOOKUP($F146,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8897,13 +8912,13 @@
       <x:c r="B147" s="33"/>
       <x:c r="C147" s="59"/>
       <x:c r="D147" s="52" t="str">
-        <x:f>IF($B147="","",IFERROR(VLOOKUP($B147,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B147="","",IFERROR(VLOOKUP($B147,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E147" s="62" t="str">
         <x:f>IF($D147="","",IF($D147="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F147" s="53" t="str">
-        <x:f>IF($B147="","",IFERROR(VLOOKUP($B147,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B147="","",IFERROR(VLOOKUP($B147,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B147),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G147" s="65" t="str">
         <x:f>IF($F147="","",IFERROR(VLOOKUP($F147,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -8951,13 +8966,13 @@
       <x:c r="B148" s="33"/>
       <x:c r="C148" s="59"/>
       <x:c r="D148" s="52" t="str">
-        <x:f>IF($B148="","",IFERROR(VLOOKUP($B148,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B148="","",IFERROR(VLOOKUP($B148,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E148" s="62" t="str">
         <x:f>IF($D148="","",IF($D148="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F148" s="53" t="str">
-        <x:f>IF($B148="","",IFERROR(VLOOKUP($B148,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B148="","",IFERROR(VLOOKUP($B148,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B148),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G148" s="65" t="str">
         <x:f>IF($F148="","",IFERROR(VLOOKUP($F148,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9005,13 +9020,13 @@
       <x:c r="B149" s="33"/>
       <x:c r="C149" s="59"/>
       <x:c r="D149" s="52" t="str">
-        <x:f>IF($B149="","",IFERROR(VLOOKUP($B149,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B149="","",IFERROR(VLOOKUP($B149,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E149" s="62" t="str">
         <x:f>IF($D149="","",IF($D149="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F149" s="53" t="str">
-        <x:f>IF($B149="","",IFERROR(VLOOKUP($B149,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B149="","",IFERROR(VLOOKUP($B149,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B149),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G149" s="65" t="str">
         <x:f>IF($F149="","",IFERROR(VLOOKUP($F149,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9059,13 +9074,13 @@
       <x:c r="B150" s="33"/>
       <x:c r="C150" s="59"/>
       <x:c r="D150" s="52" t="str">
-        <x:f>IF($B150="","",IFERROR(VLOOKUP($B150,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B150="","",IFERROR(VLOOKUP($B150,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E150" s="62" t="str">
         <x:f>IF($D150="","",IF($D150="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F150" s="53" t="str">
-        <x:f>IF($B150="","",IFERROR(VLOOKUP($B150,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B150="","",IFERROR(VLOOKUP($B150,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B150),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G150" s="65" t="str">
         <x:f>IF($F150="","",IFERROR(VLOOKUP($F150,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9113,13 +9128,13 @@
       <x:c r="B151" s="33"/>
       <x:c r="C151" s="59"/>
       <x:c r="D151" s="52" t="str">
-        <x:f>IF($B151="","",IFERROR(VLOOKUP($B151,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B151="","",IFERROR(VLOOKUP($B151,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E151" s="62" t="str">
         <x:f>IF($D151="","",IF($D151="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F151" s="53" t="str">
-        <x:f>IF($B151="","",IFERROR(VLOOKUP($B151,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B151="","",IFERROR(VLOOKUP($B151,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B151),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G151" s="65" t="str">
         <x:f>IF($F151="","",IFERROR(VLOOKUP($F151,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9167,13 +9182,13 @@
       <x:c r="B152" s="33"/>
       <x:c r="C152" s="59"/>
       <x:c r="D152" s="52" t="str">
-        <x:f>IF($B152="","",IFERROR(VLOOKUP($B152,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B152="","",IFERROR(VLOOKUP($B152,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E152" s="62" t="str">
         <x:f>IF($D152="","",IF($D152="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F152" s="53" t="str">
-        <x:f>IF($B152="","",IFERROR(VLOOKUP($B152,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B152="","",IFERROR(VLOOKUP($B152,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B152),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G152" s="65" t="str">
         <x:f>IF($F152="","",IFERROR(VLOOKUP($F152,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9221,13 +9236,13 @@
       <x:c r="B153" s="33"/>
       <x:c r="C153" s="59"/>
       <x:c r="D153" s="52" t="str">
-        <x:f>IF($B153="","",IFERROR(VLOOKUP($B153,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B153="","",IFERROR(VLOOKUP($B153,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E153" s="62" t="str">
         <x:f>IF($D153="","",IF($D153="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F153" s="53" t="str">
-        <x:f>IF($B153="","",IFERROR(VLOOKUP($B153,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B153="","",IFERROR(VLOOKUP($B153,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B153),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G153" s="65" t="str">
         <x:f>IF($F153="","",IFERROR(VLOOKUP($F153,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9275,13 +9290,13 @@
       <x:c r="B154" s="33"/>
       <x:c r="C154" s="59"/>
       <x:c r="D154" s="52" t="str">
-        <x:f>IF($B154="","",IFERROR(VLOOKUP($B154,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B154="","",IFERROR(VLOOKUP($B154,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E154" s="62" t="str">
         <x:f>IF($D154="","",IF($D154="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F154" s="53" t="str">
-        <x:f>IF($B154="","",IFERROR(VLOOKUP($B154,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B154="","",IFERROR(VLOOKUP($B154,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B154),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G154" s="65" t="str">
         <x:f>IF($F154="","",IFERROR(VLOOKUP($F154,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9329,13 +9344,13 @@
       <x:c r="B155" s="33"/>
       <x:c r="C155" s="59"/>
       <x:c r="D155" s="52" t="str">
-        <x:f>IF($B155="","",IFERROR(VLOOKUP($B155,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B155="","",IFERROR(VLOOKUP($B155,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E155" s="62" t="str">
         <x:f>IF($D155="","",IF($D155="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F155" s="53" t="str">
-        <x:f>IF($B155="","",IFERROR(VLOOKUP($B155,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B155="","",IFERROR(VLOOKUP($B155,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B155),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G155" s="65" t="str">
         <x:f>IF($F155="","",IFERROR(VLOOKUP($F155,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9383,13 +9398,13 @@
       <x:c r="B156" s="33"/>
       <x:c r="C156" s="59"/>
       <x:c r="D156" s="52" t="str">
-        <x:f>IF($B156="","",IFERROR(VLOOKUP($B156,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B156="","",IFERROR(VLOOKUP($B156,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E156" s="62" t="str">
         <x:f>IF($D156="","",IF($D156="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F156" s="53" t="str">
-        <x:f>IF($B156="","",IFERROR(VLOOKUP($B156,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B156="","",IFERROR(VLOOKUP($B156,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B156),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G156" s="65" t="str">
         <x:f>IF($F156="","",IFERROR(VLOOKUP($F156,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9437,13 +9452,13 @@
       <x:c r="B157" s="33"/>
       <x:c r="C157" s="59"/>
       <x:c r="D157" s="52" t="str">
-        <x:f>IF($B157="","",IFERROR(VLOOKUP($B157,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B157="","",IFERROR(VLOOKUP($B157,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E157" s="62" t="str">
         <x:f>IF($D157="","",IF($D157="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F157" s="53" t="str">
-        <x:f>IF($B157="","",IFERROR(VLOOKUP($B157,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B157="","",IFERROR(VLOOKUP($B157,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B157),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G157" s="65" t="str">
         <x:f>IF($F157="","",IFERROR(VLOOKUP($F157,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9491,13 +9506,13 @@
       <x:c r="B158" s="33"/>
       <x:c r="C158" s="59"/>
       <x:c r="D158" s="52" t="str">
-        <x:f>IF($B158="","",IFERROR(VLOOKUP($B158,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B158="","",IFERROR(VLOOKUP($B158,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E158" s="62" t="str">
         <x:f>IF($D158="","",IF($D158="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F158" s="53" t="str">
-        <x:f>IF($B158="","",IFERROR(VLOOKUP($B158,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B158="","",IFERROR(VLOOKUP($B158,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B158),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G158" s="65" t="str">
         <x:f>IF($F158="","",IFERROR(VLOOKUP($F158,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9545,13 +9560,13 @@
       <x:c r="B159" s="33"/>
       <x:c r="C159" s="59"/>
       <x:c r="D159" s="52" t="str">
-        <x:f>IF($B159="","",IFERROR(VLOOKUP($B159,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B159="","",IFERROR(VLOOKUP($B159,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E159" s="62" t="str">
         <x:f>IF($D159="","",IF($D159="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F159" s="53" t="str">
-        <x:f>IF($B159="","",IFERROR(VLOOKUP($B159,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B159="","",IFERROR(VLOOKUP($B159,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B159),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G159" s="65" t="str">
         <x:f>IF($F159="","",IFERROR(VLOOKUP($F159,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9599,13 +9614,13 @@
       <x:c r="B160" s="33"/>
       <x:c r="C160" s="59"/>
       <x:c r="D160" s="52" t="str">
-        <x:f>IF($B160="","",IFERROR(VLOOKUP($B160,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B160="","",IFERROR(VLOOKUP($B160,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E160" s="62" t="str">
         <x:f>IF($D160="","",IF($D160="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F160" s="53" t="str">
-        <x:f>IF($B160="","",IFERROR(VLOOKUP($B160,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B160="","",IFERROR(VLOOKUP($B160,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B160),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G160" s="65" t="str">
         <x:f>IF($F160="","",IFERROR(VLOOKUP($F160,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9653,13 +9668,13 @@
       <x:c r="B161" s="33"/>
       <x:c r="C161" s="59"/>
       <x:c r="D161" s="52" t="str">
-        <x:f>IF($B161="","",IFERROR(VLOOKUP($B161,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B161="","",IFERROR(VLOOKUP($B161,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E161" s="62" t="str">
         <x:f>IF($D161="","",IF($D161="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F161" s="53" t="str">
-        <x:f>IF($B161="","",IFERROR(VLOOKUP($B161,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B161="","",IFERROR(VLOOKUP($B161,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B161),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G161" s="65" t="str">
         <x:f>IF($F161="","",IFERROR(VLOOKUP($F161,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9707,13 +9722,13 @@
       <x:c r="B162" s="33"/>
       <x:c r="C162" s="59"/>
       <x:c r="D162" s="52" t="str">
-        <x:f>IF($B162="","",IFERROR(VLOOKUP($B162,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B162="","",IFERROR(VLOOKUP($B162,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E162" s="62" t="str">
         <x:f>IF($D162="","",IF($D162="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F162" s="53" t="str">
-        <x:f>IF($B162="","",IFERROR(VLOOKUP($B162,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B162="","",IFERROR(VLOOKUP($B162,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B162),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G162" s="65" t="str">
         <x:f>IF($F162="","",IFERROR(VLOOKUP($F162,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9761,13 +9776,13 @@
       <x:c r="B163" s="33"/>
       <x:c r="C163" s="59"/>
       <x:c r="D163" s="52" t="str">
-        <x:f>IF($B163="","",IFERROR(VLOOKUP($B163,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B163="","",IFERROR(VLOOKUP($B163,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E163" s="62" t="str">
         <x:f>IF($D163="","",IF($D163="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F163" s="53" t="str">
-        <x:f>IF($B163="","",IFERROR(VLOOKUP($B163,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B163="","",IFERROR(VLOOKUP($B163,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B163),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G163" s="65" t="str">
         <x:f>IF($F163="","",IFERROR(VLOOKUP($F163,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9815,13 +9830,13 @@
       <x:c r="B164" s="33"/>
       <x:c r="C164" s="59"/>
       <x:c r="D164" s="52" t="str">
-        <x:f>IF($B164="","",IFERROR(VLOOKUP($B164,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B164="","",IFERROR(VLOOKUP($B164,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E164" s="62" t="str">
         <x:f>IF($D164="","",IF($D164="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F164" s="53" t="str">
-        <x:f>IF($B164="","",IFERROR(VLOOKUP($B164,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B164="","",IFERROR(VLOOKUP($B164,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B164),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G164" s="65" t="str">
         <x:f>IF($F164="","",IFERROR(VLOOKUP($F164,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9869,13 +9884,13 @@
       <x:c r="B165" s="33"/>
       <x:c r="C165" s="59"/>
       <x:c r="D165" s="52" t="str">
-        <x:f>IF($B165="","",IFERROR(VLOOKUP($B165,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B165="","",IFERROR(VLOOKUP($B165,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E165" s="62" t="str">
         <x:f>IF($D165="","",IF($D165="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F165" s="53" t="str">
-        <x:f>IF($B165="","",IFERROR(VLOOKUP($B165,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B165="","",IFERROR(VLOOKUP($B165,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B165),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G165" s="65" t="str">
         <x:f>IF($F165="","",IFERROR(VLOOKUP($F165,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9923,13 +9938,13 @@
       <x:c r="B166" s="33"/>
       <x:c r="C166" s="59"/>
       <x:c r="D166" s="52" t="str">
-        <x:f>IF($B166="","",IFERROR(VLOOKUP($B166,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B166="","",IFERROR(VLOOKUP($B166,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E166" s="62" t="str">
         <x:f>IF($D166="","",IF($D166="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F166" s="53" t="str">
-        <x:f>IF($B166="","",IFERROR(VLOOKUP($B166,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B166="","",IFERROR(VLOOKUP($B166,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B166),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G166" s="65" t="str">
         <x:f>IF($F166="","",IFERROR(VLOOKUP($F166,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -9977,13 +9992,13 @@
       <x:c r="B167" s="33"/>
       <x:c r="C167" s="59"/>
       <x:c r="D167" s="52" t="str">
-        <x:f>IF($B167="","",IFERROR(VLOOKUP($B167,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B167="","",IFERROR(VLOOKUP($B167,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E167" s="62" t="str">
         <x:f>IF($D167="","",IF($D167="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F167" s="53" t="str">
-        <x:f>IF($B167="","",IFERROR(VLOOKUP($B167,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B167="","",IFERROR(VLOOKUP($B167,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B167),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G167" s="65" t="str">
         <x:f>IF($F167="","",IFERROR(VLOOKUP($F167,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10031,13 +10046,13 @@
       <x:c r="B168" s="33"/>
       <x:c r="C168" s="59"/>
       <x:c r="D168" s="52" t="str">
-        <x:f>IF($B168="","",IFERROR(VLOOKUP($B168,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B168="","",IFERROR(VLOOKUP($B168,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E168" s="62" t="str">
         <x:f>IF($D168="","",IF($D168="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F168" s="53" t="str">
-        <x:f>IF($B168="","",IFERROR(VLOOKUP($B168,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B168="","",IFERROR(VLOOKUP($B168,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B168),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G168" s="65" t="str">
         <x:f>IF($F168="","",IFERROR(VLOOKUP($F168,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10085,13 +10100,13 @@
       <x:c r="B169" s="33"/>
       <x:c r="C169" s="59"/>
       <x:c r="D169" s="52" t="str">
-        <x:f>IF($B169="","",IFERROR(VLOOKUP($B169,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B169="","",IFERROR(VLOOKUP($B169,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E169" s="62" t="str">
         <x:f>IF($D169="","",IF($D169="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F169" s="53" t="str">
-        <x:f>IF($B169="","",IFERROR(VLOOKUP($B169,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B169="","",IFERROR(VLOOKUP($B169,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B169),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G169" s="65" t="str">
         <x:f>IF($F169="","",IFERROR(VLOOKUP($F169,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10139,13 +10154,13 @@
       <x:c r="B170" s="33"/>
       <x:c r="C170" s="59"/>
       <x:c r="D170" s="52" t="str">
-        <x:f>IF($B170="","",IFERROR(VLOOKUP($B170,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B170="","",IFERROR(VLOOKUP($B170,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E170" s="62" t="str">
         <x:f>IF($D170="","",IF($D170="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F170" s="53" t="str">
-        <x:f>IF($B170="","",IFERROR(VLOOKUP($B170,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B170="","",IFERROR(VLOOKUP($B170,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B170),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G170" s="65" t="str">
         <x:f>IF($F170="","",IFERROR(VLOOKUP($F170,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10193,13 +10208,13 @@
       <x:c r="B171" s="33"/>
       <x:c r="C171" s="59"/>
       <x:c r="D171" s="52" t="str">
-        <x:f>IF($B171="","",IFERROR(VLOOKUP($B171,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B171="","",IFERROR(VLOOKUP($B171,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E171" s="62" t="str">
         <x:f>IF($D171="","",IF($D171="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F171" s="53" t="str">
-        <x:f>IF($B171="","",IFERROR(VLOOKUP($B171,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B171="","",IFERROR(VLOOKUP($B171,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B171),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G171" s="65" t="str">
         <x:f>IF($F171="","",IFERROR(VLOOKUP($F171,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10247,13 +10262,13 @@
       <x:c r="B172" s="33"/>
       <x:c r="C172" s="59"/>
       <x:c r="D172" s="52" t="str">
-        <x:f>IF($B172="","",IFERROR(VLOOKUP($B172,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B172="","",IFERROR(VLOOKUP($B172,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E172" s="62" t="str">
         <x:f>IF($D172="","",IF($D172="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F172" s="53" t="str">
-        <x:f>IF($B172="","",IFERROR(VLOOKUP($B172,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B172="","",IFERROR(VLOOKUP($B172,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B172),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G172" s="65" t="str">
         <x:f>IF($F172="","",IFERROR(VLOOKUP($F172,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10301,13 +10316,13 @@
       <x:c r="B173" s="33"/>
       <x:c r="C173" s="59"/>
       <x:c r="D173" s="52" t="str">
-        <x:f>IF($B173="","",IFERROR(VLOOKUP($B173,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B173="","",IFERROR(VLOOKUP($B173,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E173" s="62" t="str">
         <x:f>IF($D173="","",IF($D173="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F173" s="53" t="str">
-        <x:f>IF($B173="","",IFERROR(VLOOKUP($B173,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B173="","",IFERROR(VLOOKUP($B173,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B173),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G173" s="65" t="str">
         <x:f>IF($F173="","",IFERROR(VLOOKUP($F173,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10355,13 +10370,13 @@
       <x:c r="B174" s="33"/>
       <x:c r="C174" s="59"/>
       <x:c r="D174" s="52" t="str">
-        <x:f>IF($B174="","",IFERROR(VLOOKUP($B174,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B174="","",IFERROR(VLOOKUP($B174,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E174" s="62" t="str">
         <x:f>IF($D174="","",IF($D174="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F174" s="53" t="str">
-        <x:f>IF($B174="","",IFERROR(VLOOKUP($B174,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B174="","",IFERROR(VLOOKUP($B174,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B174),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G174" s="65" t="str">
         <x:f>IF($F174="","",IFERROR(VLOOKUP($F174,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10409,13 +10424,13 @@
       <x:c r="B175" s="33"/>
       <x:c r="C175" s="59"/>
       <x:c r="D175" s="52" t="str">
-        <x:f>IF($B175="","",IFERROR(VLOOKUP($B175,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B175="","",IFERROR(VLOOKUP($B175,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E175" s="62" t="str">
         <x:f>IF($D175="","",IF($D175="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F175" s="53" t="str">
-        <x:f>IF($B175="","",IFERROR(VLOOKUP($B175,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B175="","",IFERROR(VLOOKUP($B175,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B175),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G175" s="65" t="str">
         <x:f>IF($F175="","",IFERROR(VLOOKUP($F175,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10463,13 +10478,13 @@
       <x:c r="B176" s="33"/>
       <x:c r="C176" s="59"/>
       <x:c r="D176" s="52" t="str">
-        <x:f>IF($B176="","",IFERROR(VLOOKUP($B176,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B176="","",IFERROR(VLOOKUP($B176,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E176" s="62" t="str">
         <x:f>IF($D176="","",IF($D176="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F176" s="53" t="str">
-        <x:f>IF($B176="","",IFERROR(VLOOKUP($B176,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B176="","",IFERROR(VLOOKUP($B176,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B176),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G176" s="65" t="str">
         <x:f>IF($F176="","",IFERROR(VLOOKUP($F176,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10517,13 +10532,13 @@
       <x:c r="B177" s="33"/>
       <x:c r="C177" s="59"/>
       <x:c r="D177" s="52" t="str">
-        <x:f>IF($B177="","",IFERROR(VLOOKUP($B177,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B177="","",IFERROR(VLOOKUP($B177,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E177" s="62" t="str">
         <x:f>IF($D177="","",IF($D177="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F177" s="53" t="str">
-        <x:f>IF($B177="","",IFERROR(VLOOKUP($B177,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B177="","",IFERROR(VLOOKUP($B177,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B177),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G177" s="65" t="str">
         <x:f>IF($F177="","",IFERROR(VLOOKUP($F177,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10571,13 +10586,13 @@
       <x:c r="B178" s="33"/>
       <x:c r="C178" s="59"/>
       <x:c r="D178" s="52" t="str">
-        <x:f>IF($B178="","",IFERROR(VLOOKUP($B178,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B178="","",IFERROR(VLOOKUP($B178,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E178" s="62" t="str">
         <x:f>IF($D178="","",IF($D178="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F178" s="53" t="str">
-        <x:f>IF($B178="","",IFERROR(VLOOKUP($B178,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B178="","",IFERROR(VLOOKUP($B178,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B178),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G178" s="65" t="str">
         <x:f>IF($F178="","",IFERROR(VLOOKUP($F178,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10625,13 +10640,13 @@
       <x:c r="B179" s="33"/>
       <x:c r="C179" s="59"/>
       <x:c r="D179" s="52" t="str">
-        <x:f>IF($B179="","",IFERROR(VLOOKUP($B179,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B179="","",IFERROR(VLOOKUP($B179,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E179" s="62" t="str">
         <x:f>IF($D179="","",IF($D179="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F179" s="53" t="str">
-        <x:f>IF($B179="","",IFERROR(VLOOKUP($B179,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B179="","",IFERROR(VLOOKUP($B179,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B179),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G179" s="65" t="str">
         <x:f>IF($F179="","",IFERROR(VLOOKUP($F179,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10679,13 +10694,13 @@
       <x:c r="B180" s="33"/>
       <x:c r="C180" s="59"/>
       <x:c r="D180" s="52" t="str">
-        <x:f>IF($B180="","",IFERROR(VLOOKUP($B180,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B180="","",IFERROR(VLOOKUP($B180,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E180" s="62" t="str">
         <x:f>IF($D180="","",IF($D180="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F180" s="53" t="str">
-        <x:f>IF($B180="","",IFERROR(VLOOKUP($B180,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B180="","",IFERROR(VLOOKUP($B180,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B180),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G180" s="65" t="str">
         <x:f>IF($F180="","",IFERROR(VLOOKUP($F180,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10733,13 +10748,13 @@
       <x:c r="B181" s="33"/>
       <x:c r="C181" s="59"/>
       <x:c r="D181" s="52" t="str">
-        <x:f>IF($B181="","",IFERROR(VLOOKUP($B181,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B181="","",IFERROR(VLOOKUP($B181,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E181" s="62" t="str">
         <x:f>IF($D181="","",IF($D181="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F181" s="53" t="str">
-        <x:f>IF($B181="","",IFERROR(VLOOKUP($B181,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B181="","",IFERROR(VLOOKUP($B181,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B181),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G181" s="65" t="str">
         <x:f>IF($F181="","",IFERROR(VLOOKUP($F181,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10787,13 +10802,13 @@
       <x:c r="B182" s="33"/>
       <x:c r="C182" s="59"/>
       <x:c r="D182" s="52" t="str">
-        <x:f>IF($B182="","",IFERROR(VLOOKUP($B182,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B182="","",IFERROR(VLOOKUP($B182,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E182" s="62" t="str">
         <x:f>IF($D182="","",IF($D182="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F182" s="53" t="str">
-        <x:f>IF($B182="","",IFERROR(VLOOKUP($B182,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B182="","",IFERROR(VLOOKUP($B182,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B182),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G182" s="65" t="str">
         <x:f>IF($F182="","",IFERROR(VLOOKUP($F182,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10841,13 +10856,13 @@
       <x:c r="B183" s="33"/>
       <x:c r="C183" s="59"/>
       <x:c r="D183" s="52" t="str">
-        <x:f>IF($B183="","",IFERROR(VLOOKUP($B183,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B183="","",IFERROR(VLOOKUP($B183,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E183" s="62" t="str">
         <x:f>IF($D183="","",IF($D183="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F183" s="53" t="str">
-        <x:f>IF($B183="","",IFERROR(VLOOKUP($B183,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B183="","",IFERROR(VLOOKUP($B183,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B183),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G183" s="65" t="str">
         <x:f>IF($F183="","",IFERROR(VLOOKUP($F183,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10895,13 +10910,13 @@
       <x:c r="B184" s="33"/>
       <x:c r="C184" s="59"/>
       <x:c r="D184" s="52" t="str">
-        <x:f>IF($B184="","",IFERROR(VLOOKUP($B184,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B184="","",IFERROR(VLOOKUP($B184,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E184" s="62" t="str">
         <x:f>IF($D184="","",IF($D184="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F184" s="53" t="str">
-        <x:f>IF($B184="","",IFERROR(VLOOKUP($B184,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B184="","",IFERROR(VLOOKUP($B184,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B184),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G184" s="65" t="str">
         <x:f>IF($F184="","",IFERROR(VLOOKUP($F184,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -10949,13 +10964,13 @@
       <x:c r="B185" s="33"/>
       <x:c r="C185" s="59"/>
       <x:c r="D185" s="52" t="str">
-        <x:f>IF($B185="","",IFERROR(VLOOKUP($B185,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B185="","",IFERROR(VLOOKUP($B185,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E185" s="62" t="str">
         <x:f>IF($D185="","",IF($D185="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F185" s="53" t="str">
-        <x:f>IF($B185="","",IFERROR(VLOOKUP($B185,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B185="","",IFERROR(VLOOKUP($B185,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B185),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G185" s="65" t="str">
         <x:f>IF($F185="","",IFERROR(VLOOKUP($F185,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11003,13 +11018,13 @@
       <x:c r="B186" s="33"/>
       <x:c r="C186" s="59"/>
       <x:c r="D186" s="52" t="str">
-        <x:f>IF($B186="","",IFERROR(VLOOKUP($B186,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B186="","",IFERROR(VLOOKUP($B186,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E186" s="62" t="str">
         <x:f>IF($D186="","",IF($D186="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F186" s="53" t="str">
-        <x:f>IF($B186="","",IFERROR(VLOOKUP($B186,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B186="","",IFERROR(VLOOKUP($B186,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B186),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G186" s="65" t="str">
         <x:f>IF($F186="","",IFERROR(VLOOKUP($F186,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11057,13 +11072,13 @@
       <x:c r="B187" s="33"/>
       <x:c r="C187" s="59"/>
       <x:c r="D187" s="52" t="str">
-        <x:f>IF($B187="","",IFERROR(VLOOKUP($B187,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B187="","",IFERROR(VLOOKUP($B187,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E187" s="62" t="str">
         <x:f>IF($D187="","",IF($D187="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F187" s="53" t="str">
-        <x:f>IF($B187="","",IFERROR(VLOOKUP($B187,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B187="","",IFERROR(VLOOKUP($B187,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B187),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G187" s="65" t="str">
         <x:f>IF($F187="","",IFERROR(VLOOKUP($F187,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11111,13 +11126,13 @@
       <x:c r="B188" s="33"/>
       <x:c r="C188" s="59"/>
       <x:c r="D188" s="52" t="str">
-        <x:f>IF($B188="","",IFERROR(VLOOKUP($B188,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B188="","",IFERROR(VLOOKUP($B188,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E188" s="62" t="str">
         <x:f>IF($D188="","",IF($D188="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F188" s="53" t="str">
-        <x:f>IF($B188="","",IFERROR(VLOOKUP($B188,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B188="","",IFERROR(VLOOKUP($B188,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B188),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G188" s="65" t="str">
         <x:f>IF($F188="","",IFERROR(VLOOKUP($F188,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11165,13 +11180,13 @@
       <x:c r="B189" s="33"/>
       <x:c r="C189" s="59"/>
       <x:c r="D189" s="52" t="str">
-        <x:f>IF($B189="","",IFERROR(VLOOKUP($B189,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B189="","",IFERROR(VLOOKUP($B189,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E189" s="62" t="str">
         <x:f>IF($D189="","",IF($D189="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F189" s="53" t="str">
-        <x:f>IF($B189="","",IFERROR(VLOOKUP($B189,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B189="","",IFERROR(VLOOKUP($B189,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B189),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G189" s="65" t="str">
         <x:f>IF($F189="","",IFERROR(VLOOKUP($F189,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11219,13 +11234,13 @@
       <x:c r="B190" s="33"/>
       <x:c r="C190" s="59"/>
       <x:c r="D190" s="52" t="str">
-        <x:f>IF($B190="","",IFERROR(VLOOKUP($B190,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B190="","",IFERROR(VLOOKUP($B190,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E190" s="62" t="str">
         <x:f>IF($D190="","",IF($D190="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F190" s="53" t="str">
-        <x:f>IF($B190="","",IFERROR(VLOOKUP($B190,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B190="","",IFERROR(VLOOKUP($B190,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B190),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G190" s="65" t="str">
         <x:f>IF($F190="","",IFERROR(VLOOKUP($F190,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11273,13 +11288,13 @@
       <x:c r="B191" s="33"/>
       <x:c r="C191" s="59"/>
       <x:c r="D191" s="52" t="str">
-        <x:f>IF($B191="","",IFERROR(VLOOKUP($B191,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B191="","",IFERROR(VLOOKUP($B191,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E191" s="62" t="str">
         <x:f>IF($D191="","",IF($D191="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F191" s="53" t="str">
-        <x:f>IF($B191="","",IFERROR(VLOOKUP($B191,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B191="","",IFERROR(VLOOKUP($B191,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B191),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G191" s="65" t="str">
         <x:f>IF($F191="","",IFERROR(VLOOKUP($F191,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11327,13 +11342,13 @@
       <x:c r="B192" s="33"/>
       <x:c r="C192" s="59"/>
       <x:c r="D192" s="52" t="str">
-        <x:f>IF($B192="","",IFERROR(VLOOKUP($B192,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B192="","",IFERROR(VLOOKUP($B192,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E192" s="62" t="str">
         <x:f>IF($D192="","",IF($D192="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F192" s="53" t="str">
-        <x:f>IF($B192="","",IFERROR(VLOOKUP($B192,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B192="","",IFERROR(VLOOKUP($B192,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B192),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G192" s="65" t="str">
         <x:f>IF($F192="","",IFERROR(VLOOKUP($F192,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11381,13 +11396,13 @@
       <x:c r="B193" s="33"/>
       <x:c r="C193" s="59"/>
       <x:c r="D193" s="52" t="str">
-        <x:f>IF($B193="","",IFERROR(VLOOKUP($B193,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B193="","",IFERROR(VLOOKUP($B193,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E193" s="62" t="str">
         <x:f>IF($D193="","",IF($D193="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F193" s="53" t="str">
-        <x:f>IF($B193="","",IFERROR(VLOOKUP($B193,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B193="","",IFERROR(VLOOKUP($B193,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B193),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G193" s="65" t="str">
         <x:f>IF($F193="","",IFERROR(VLOOKUP($F193,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11435,13 +11450,13 @@
       <x:c r="B194" s="33"/>
       <x:c r="C194" s="59"/>
       <x:c r="D194" s="52" t="str">
-        <x:f>IF($B194="","",IFERROR(VLOOKUP($B194,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B194="","",IFERROR(VLOOKUP($B194,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E194" s="62" t="str">
         <x:f>IF($D194="","",IF($D194="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F194" s="53" t="str">
-        <x:f>IF($B194="","",IFERROR(VLOOKUP($B194,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B194="","",IFERROR(VLOOKUP($B194,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B194),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G194" s="65" t="str">
         <x:f>IF($F194="","",IFERROR(VLOOKUP($F194,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11489,13 +11504,13 @@
       <x:c r="B195" s="33"/>
       <x:c r="C195" s="59"/>
       <x:c r="D195" s="52" t="str">
-        <x:f>IF($B195="","",IFERROR(VLOOKUP($B195,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B195="","",IFERROR(VLOOKUP($B195,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E195" s="62" t="str">
         <x:f>IF($D195="","",IF($D195="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F195" s="53" t="str">
-        <x:f>IF($B195="","",IFERROR(VLOOKUP($B195,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B195="","",IFERROR(VLOOKUP($B195,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B195),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G195" s="65" t="str">
         <x:f>IF($F195="","",IFERROR(VLOOKUP($F195,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11543,13 +11558,13 @@
       <x:c r="B196" s="33"/>
       <x:c r="C196" s="59"/>
       <x:c r="D196" s="52" t="str">
-        <x:f>IF($B196="","",IFERROR(VLOOKUP($B196,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B196="","",IFERROR(VLOOKUP($B196,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E196" s="62" t="str">
         <x:f>IF($D196="","",IF($D196="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F196" s="53" t="str">
-        <x:f>IF($B196="","",IFERROR(VLOOKUP($B196,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B196="","",IFERROR(VLOOKUP($B196,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B196),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G196" s="65" t="str">
         <x:f>IF($F196="","",IFERROR(VLOOKUP($F196,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11597,13 +11612,13 @@
       <x:c r="B197" s="33"/>
       <x:c r="C197" s="59"/>
       <x:c r="D197" s="52" t="str">
-        <x:f>IF($B197="","",IFERROR(VLOOKUP($B197,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B197="","",IFERROR(VLOOKUP($B197,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E197" s="62" t="str">
         <x:f>IF($D197="","",IF($D197="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F197" s="53" t="str">
-        <x:f>IF($B197="","",IFERROR(VLOOKUP($B197,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B197="","",IFERROR(VLOOKUP($B197,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B197),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G197" s="65" t="str">
         <x:f>IF($F197="","",IFERROR(VLOOKUP($F197,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11651,13 +11666,13 @@
       <x:c r="B198" s="33"/>
       <x:c r="C198" s="59"/>
       <x:c r="D198" s="52" t="str">
-        <x:f>IF($B198="","",IFERROR(VLOOKUP($B198,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B198="","",IFERROR(VLOOKUP($B198,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E198" s="62" t="str">
         <x:f>IF($D198="","",IF($D198="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F198" s="53" t="str">
-        <x:f>IF($B198="","",IFERROR(VLOOKUP($B198,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B198="","",IFERROR(VLOOKUP($B198,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B198),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G198" s="65" t="str">
         <x:f>IF($F198="","",IFERROR(VLOOKUP($F198,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11705,13 +11720,13 @@
       <x:c r="B199" s="33"/>
       <x:c r="C199" s="59"/>
       <x:c r="D199" s="52" t="str">
-        <x:f>IF($B199="","",IFERROR(VLOOKUP($B199,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B199="","",IFERROR(VLOOKUP($B199,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E199" s="62" t="str">
         <x:f>IF($D199="","",IF($D199="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F199" s="53" t="str">
-        <x:f>IF($B199="","",IFERROR(VLOOKUP($B199,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B199="","",IFERROR(VLOOKUP($B199,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B199),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G199" s="65" t="str">
         <x:f>IF($F199="","",IFERROR(VLOOKUP($F199,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11759,13 +11774,13 @@
       <x:c r="B200" s="33"/>
       <x:c r="C200" s="59"/>
       <x:c r="D200" s="52" t="str">
-        <x:f>IF($B200="","",IFERROR(VLOOKUP($B200,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B200="","",IFERROR(VLOOKUP($B200,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E200" s="62" t="str">
         <x:f>IF($D200="","",IF($D200="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F200" s="53" t="str">
-        <x:f>IF($B200="","",IFERROR(VLOOKUP($B200,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B200="","",IFERROR(VLOOKUP($B200,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B200),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G200" s="65" t="str">
         <x:f>IF($F200="","",IFERROR(VLOOKUP($F200,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11813,13 +11828,13 @@
       <x:c r="B201" s="33"/>
       <x:c r="C201" s="59"/>
       <x:c r="D201" s="52" t="str">
-        <x:f>IF($B201="","",IFERROR(VLOOKUP($B201,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B201="","",IFERROR(VLOOKUP($B201,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E201" s="62" t="str">
         <x:f>IF($D201="","",IF($D201="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F201" s="53" t="str">
-        <x:f>IF($B201="","",IFERROR(VLOOKUP($B201,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B201="","",IFERROR(VLOOKUP($B201,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B201),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G201" s="65" t="str">
         <x:f>IF($F201="","",IFERROR(VLOOKUP($F201,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11867,13 +11882,13 @@
       <x:c r="B202" s="33"/>
       <x:c r="C202" s="59"/>
       <x:c r="D202" s="52" t="str">
-        <x:f>IF($B202="","",IFERROR(VLOOKUP($B202,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B202="","",IFERROR(VLOOKUP($B202,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E202" s="62" t="str">
         <x:f>IF($D202="","",IF($D202="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F202" s="53" t="str">
-        <x:f>IF($B202="","",IFERROR(VLOOKUP($B202,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B202="","",IFERROR(VLOOKUP($B202,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B202),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G202" s="65" t="str">
         <x:f>IF($F202="","",IFERROR(VLOOKUP($F202,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11921,13 +11936,13 @@
       <x:c r="B203" s="33"/>
       <x:c r="C203" s="59"/>
       <x:c r="D203" s="52" t="str">
-        <x:f>IF($B203="","",IFERROR(VLOOKUP($B203,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B203="","",IFERROR(VLOOKUP($B203,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E203" s="62" t="str">
         <x:f>IF($D203="","",IF($D203="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F203" s="53" t="str">
-        <x:f>IF($B203="","",IFERROR(VLOOKUP($B203,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B203="","",IFERROR(VLOOKUP($B203,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B203),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G203" s="65" t="str">
         <x:f>IF($F203="","",IFERROR(VLOOKUP($F203,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -11975,13 +11990,13 @@
       <x:c r="B204" s="33"/>
       <x:c r="C204" s="59"/>
       <x:c r="D204" s="52" t="str">
-        <x:f>IF($B204="","",IFERROR(VLOOKUP($B204,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B204="","",IFERROR(VLOOKUP($B204,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E204" s="62" t="str">
         <x:f>IF($D204="","",IF($D204="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F204" s="53" t="str">
-        <x:f>IF($B204="","",IFERROR(VLOOKUP($B204,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B204="","",IFERROR(VLOOKUP($B204,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B204),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G204" s="65" t="str">
         <x:f>IF($F204="","",IFERROR(VLOOKUP($F204,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12029,13 +12044,13 @@
       <x:c r="B205" s="33"/>
       <x:c r="C205" s="59"/>
       <x:c r="D205" s="52" t="str">
-        <x:f>IF($B205="","",IFERROR(VLOOKUP($B205,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B205="","",IFERROR(VLOOKUP($B205,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E205" s="62" t="str">
         <x:f>IF($D205="","",IF($D205="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F205" s="53" t="str">
-        <x:f>IF($B205="","",IFERROR(VLOOKUP($B205,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B205="","",IFERROR(VLOOKUP($B205,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B205),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G205" s="65" t="str">
         <x:f>IF($F205="","",IFERROR(VLOOKUP($F205,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12083,13 +12098,13 @@
       <x:c r="B206" s="33"/>
       <x:c r="C206" s="59"/>
       <x:c r="D206" s="52" t="str">
-        <x:f>IF($B206="","",IFERROR(VLOOKUP($B206,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B206="","",IFERROR(VLOOKUP($B206,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E206" s="62" t="str">
         <x:f>IF($D206="","",IF($D206="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F206" s="53" t="str">
-        <x:f>IF($B206="","",IFERROR(VLOOKUP($B206,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B206="","",IFERROR(VLOOKUP($B206,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B206),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G206" s="65" t="str">
         <x:f>IF($F206="","",IFERROR(VLOOKUP($F206,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12137,13 +12152,13 @@
       <x:c r="B207" s="33"/>
       <x:c r="C207" s="59"/>
       <x:c r="D207" s="52" t="str">
-        <x:f>IF($B207="","",IFERROR(VLOOKUP($B207,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B207="","",IFERROR(VLOOKUP($B207,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E207" s="62" t="str">
         <x:f>IF($D207="","",IF($D207="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F207" s="53" t="str">
-        <x:f>IF($B207="","",IFERROR(VLOOKUP($B207,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B207="","",IFERROR(VLOOKUP($B207,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B207),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G207" s="65" t="str">
         <x:f>IF($F207="","",IFERROR(VLOOKUP($F207,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12191,13 +12206,13 @@
       <x:c r="B208" s="33"/>
       <x:c r="C208" s="59"/>
       <x:c r="D208" s="52" t="str">
-        <x:f>IF($B208="","",IFERROR(VLOOKUP($B208,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B208="","",IFERROR(VLOOKUP($B208,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E208" s="62" t="str">
         <x:f>IF($D208="","",IF($D208="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F208" s="53" t="str">
-        <x:f>IF($B208="","",IFERROR(VLOOKUP($B208,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B208="","",IFERROR(VLOOKUP($B208,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B208),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G208" s="65" t="str">
         <x:f>IF($F208="","",IFERROR(VLOOKUP($F208,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12245,13 +12260,13 @@
       <x:c r="B209" s="33"/>
       <x:c r="C209" s="59"/>
       <x:c r="D209" s="52" t="str">
-        <x:f>IF($B209="","",IFERROR(VLOOKUP($B209,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B209="","",IFERROR(VLOOKUP($B209,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E209" s="62" t="str">
         <x:f>IF($D209="","",IF($D209="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F209" s="53" t="str">
-        <x:f>IF($B209="","",IFERROR(VLOOKUP($B209,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B209="","",IFERROR(VLOOKUP($B209,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B209),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G209" s="65" t="str">
         <x:f>IF($F209="","",IFERROR(VLOOKUP($F209,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12299,13 +12314,13 @@
       <x:c r="B210" s="33"/>
       <x:c r="C210" s="59"/>
       <x:c r="D210" s="52" t="str">
-        <x:f>IF($B210="","",IFERROR(VLOOKUP($B210,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B210="","",IFERROR(VLOOKUP($B210,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E210" s="62" t="str">
         <x:f>IF($D210="","",IF($D210="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F210" s="53" t="str">
-        <x:f>IF($B210="","",IFERROR(VLOOKUP($B210,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B210="","",IFERROR(VLOOKUP($B210,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B210),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G210" s="65" t="str">
         <x:f>IF($F210="","",IFERROR(VLOOKUP($F210,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12353,13 +12368,13 @@
       <x:c r="B211" s="33"/>
       <x:c r="C211" s="59"/>
       <x:c r="D211" s="52" t="str">
-        <x:f>IF($B211="","",IFERROR(VLOOKUP($B211,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B211="","",IFERROR(VLOOKUP($B211,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E211" s="62" t="str">
         <x:f>IF($D211="","",IF($D211="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F211" s="53" t="str">
-        <x:f>IF($B211="","",IFERROR(VLOOKUP($B211,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B211="","",IFERROR(VLOOKUP($B211,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B211),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G211" s="65" t="str">
         <x:f>IF($F211="","",IFERROR(VLOOKUP($F211,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12407,13 +12422,13 @@
       <x:c r="B212" s="33"/>
       <x:c r="C212" s="59"/>
       <x:c r="D212" s="52" t="str">
-        <x:f>IF($B212="","",IFERROR(VLOOKUP($B212,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B212="","",IFERROR(VLOOKUP($B212,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E212" s="62" t="str">
         <x:f>IF($D212="","",IF($D212="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F212" s="53" t="str">
-        <x:f>IF($B212="","",IFERROR(VLOOKUP($B212,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B212="","",IFERROR(VLOOKUP($B212,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B212),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G212" s="65" t="str">
         <x:f>IF($F212="","",IFERROR(VLOOKUP($F212,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12461,13 +12476,13 @@
       <x:c r="B213" s="33"/>
       <x:c r="C213" s="59"/>
       <x:c r="D213" s="52" t="str">
-        <x:f>IF($B213="","",IFERROR(VLOOKUP($B213,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B213="","",IFERROR(VLOOKUP($B213,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E213" s="62" t="str">
         <x:f>IF($D213="","",IF($D213="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F213" s="53" t="str">
-        <x:f>IF($B213="","",IFERROR(VLOOKUP($B213,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B213="","",IFERROR(VLOOKUP($B213,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B213),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G213" s="65" t="str">
         <x:f>IF($F213="","",IFERROR(VLOOKUP($F213,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12515,13 +12530,13 @@
       <x:c r="B214" s="33"/>
       <x:c r="C214" s="59"/>
       <x:c r="D214" s="52" t="str">
-        <x:f>IF($B214="","",IFERROR(VLOOKUP($B214,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B214="","",IFERROR(VLOOKUP($B214,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E214" s="62" t="str">
         <x:f>IF($D214="","",IF($D214="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F214" s="53" t="str">
-        <x:f>IF($B214="","",IFERROR(VLOOKUP($B214,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B214="","",IFERROR(VLOOKUP($B214,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B214),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G214" s="65" t="str">
         <x:f>IF($F214="","",IFERROR(VLOOKUP($F214,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12569,13 +12584,13 @@
       <x:c r="B215" s="33"/>
       <x:c r="C215" s="59"/>
       <x:c r="D215" s="52" t="str">
-        <x:f>IF($B215="","",IFERROR(VLOOKUP($B215,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B215="","",IFERROR(VLOOKUP($B215,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E215" s="62" t="str">
         <x:f>IF($D215="","",IF($D215="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F215" s="53" t="str">
-        <x:f>IF($B215="","",IFERROR(VLOOKUP($B215,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B215="","",IFERROR(VLOOKUP($B215,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B215),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G215" s="65" t="str">
         <x:f>IF($F215="","",IFERROR(VLOOKUP($F215,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12623,13 +12638,13 @@
       <x:c r="B216" s="33"/>
       <x:c r="C216" s="59"/>
       <x:c r="D216" s="52" t="str">
-        <x:f>IF($B216="","",IFERROR(VLOOKUP($B216,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B216="","",IFERROR(VLOOKUP($B216,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E216" s="62" t="str">
         <x:f>IF($D216="","",IF($D216="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F216" s="53" t="str">
-        <x:f>IF($B216="","",IFERROR(VLOOKUP($B216,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B216="","",IFERROR(VLOOKUP($B216,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B216),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G216" s="65" t="str">
         <x:f>IF($F216="","",IFERROR(VLOOKUP($F216,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12677,13 +12692,13 @@
       <x:c r="B217" s="33"/>
       <x:c r="C217" s="59"/>
       <x:c r="D217" s="52" t="str">
-        <x:f>IF($B217="","",IFERROR(VLOOKUP($B217,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B217="","",IFERROR(VLOOKUP($B217,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E217" s="62" t="str">
         <x:f>IF($D217="","",IF($D217="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F217" s="53" t="str">
-        <x:f>IF($B217="","",IFERROR(VLOOKUP($B217,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B217="","",IFERROR(VLOOKUP($B217,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B217),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G217" s="65" t="str">
         <x:f>IF($F217="","",IFERROR(VLOOKUP($F217,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12731,13 +12746,13 @@
       <x:c r="B218" s="33"/>
       <x:c r="C218" s="59"/>
       <x:c r="D218" s="52" t="str">
-        <x:f>IF($B218="","",IFERROR(VLOOKUP($B218,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B218="","",IFERROR(VLOOKUP($B218,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E218" s="62" t="str">
         <x:f>IF($D218="","",IF($D218="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F218" s="53" t="str">
-        <x:f>IF($B218="","",IFERROR(VLOOKUP($B218,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B218="","",IFERROR(VLOOKUP($B218,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B218),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G218" s="65" t="str">
         <x:f>IF($F218="","",IFERROR(VLOOKUP($F218,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12785,13 +12800,13 @@
       <x:c r="B219" s="33"/>
       <x:c r="C219" s="59"/>
       <x:c r="D219" s="52" t="str">
-        <x:f>IF($B219="","",IFERROR(VLOOKUP($B219,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B219="","",IFERROR(VLOOKUP($B219,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E219" s="62" t="str">
         <x:f>IF($D219="","",IF($D219="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F219" s="53" t="str">
-        <x:f>IF($B219="","",IFERROR(VLOOKUP($B219,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B219="","",IFERROR(VLOOKUP($B219,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B219),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G219" s="65" t="str">
         <x:f>IF($F219="","",IFERROR(VLOOKUP($F219,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12839,13 +12854,13 @@
       <x:c r="B220" s="33"/>
       <x:c r="C220" s="59"/>
       <x:c r="D220" s="52" t="str">
-        <x:f>IF($B220="","",IFERROR(VLOOKUP($B220,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B220="","",IFERROR(VLOOKUP($B220,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E220" s="62" t="str">
         <x:f>IF($D220="","",IF($D220="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F220" s="53" t="str">
-        <x:f>IF($B220="","",IFERROR(VLOOKUP($B220,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B220="","",IFERROR(VLOOKUP($B220,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B220),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G220" s="65" t="str">
         <x:f>IF($F220="","",IFERROR(VLOOKUP($F220,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12893,13 +12908,13 @@
       <x:c r="B221" s="33"/>
       <x:c r="C221" s="59"/>
       <x:c r="D221" s="52" t="str">
-        <x:f>IF($B221="","",IFERROR(VLOOKUP($B221,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B221="","",IFERROR(VLOOKUP($B221,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E221" s="62" t="str">
         <x:f>IF($D221="","",IF($D221="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F221" s="53" t="str">
-        <x:f>IF($B221="","",IFERROR(VLOOKUP($B221,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B221="","",IFERROR(VLOOKUP($B221,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B221),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G221" s="65" t="str">
         <x:f>IF($F221="","",IFERROR(VLOOKUP($F221,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -12947,13 +12962,13 @@
       <x:c r="B222" s="33"/>
       <x:c r="C222" s="59"/>
       <x:c r="D222" s="52" t="str">
-        <x:f>IF($B222="","",IFERROR(VLOOKUP($B222,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B222="","",IFERROR(VLOOKUP($B222,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E222" s="62" t="str">
         <x:f>IF($D222="","",IF($D222="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F222" s="53" t="str">
-        <x:f>IF($B222="","",IFERROR(VLOOKUP($B222,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B222="","",IFERROR(VLOOKUP($B222,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B222),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G222" s="65" t="str">
         <x:f>IF($F222="","",IFERROR(VLOOKUP($F222,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13001,13 +13016,13 @@
       <x:c r="B223" s="33"/>
       <x:c r="C223" s="59"/>
       <x:c r="D223" s="52" t="str">
-        <x:f>IF($B223="","",IFERROR(VLOOKUP($B223,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B223="","",IFERROR(VLOOKUP($B223,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E223" s="62" t="str">
         <x:f>IF($D223="","",IF($D223="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F223" s="53" t="str">
-        <x:f>IF($B223="","",IFERROR(VLOOKUP($B223,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B223="","",IFERROR(VLOOKUP($B223,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B223),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G223" s="65" t="str">
         <x:f>IF($F223="","",IFERROR(VLOOKUP($F223,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13055,13 +13070,13 @@
       <x:c r="B224" s="33"/>
       <x:c r="C224" s="59"/>
       <x:c r="D224" s="52" t="str">
-        <x:f>IF($B224="","",IFERROR(VLOOKUP($B224,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B224="","",IFERROR(VLOOKUP($B224,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E224" s="62" t="str">
         <x:f>IF($D224="","",IF($D224="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F224" s="53" t="str">
-        <x:f>IF($B224="","",IFERROR(VLOOKUP($B224,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B224="","",IFERROR(VLOOKUP($B224,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B224),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G224" s="65" t="str">
         <x:f>IF($F224="","",IFERROR(VLOOKUP($F224,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13109,13 +13124,13 @@
       <x:c r="B225" s="33"/>
       <x:c r="C225" s="59"/>
       <x:c r="D225" s="52" t="str">
-        <x:f>IF($B225="","",IFERROR(VLOOKUP($B225,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B225="","",IFERROR(VLOOKUP($B225,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E225" s="62" t="str">
         <x:f>IF($D225="","",IF($D225="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F225" s="53" t="str">
-        <x:f>IF($B225="","",IFERROR(VLOOKUP($B225,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B225="","",IFERROR(VLOOKUP($B225,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B225),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G225" s="65" t="str">
         <x:f>IF($F225="","",IFERROR(VLOOKUP($F225,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13163,13 +13178,13 @@
       <x:c r="B226" s="33"/>
       <x:c r="C226" s="59"/>
       <x:c r="D226" s="52" t="str">
-        <x:f>IF($B226="","",IFERROR(VLOOKUP($B226,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B226="","",IFERROR(VLOOKUP($B226,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E226" s="62" t="str">
         <x:f>IF($D226="","",IF($D226="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F226" s="53" t="str">
-        <x:f>IF($B226="","",IFERROR(VLOOKUP($B226,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B226="","",IFERROR(VLOOKUP($B226,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B226),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G226" s="65" t="str">
         <x:f>IF($F226="","",IFERROR(VLOOKUP($F226,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13217,13 +13232,13 @@
       <x:c r="B227" s="33"/>
       <x:c r="C227" s="59"/>
       <x:c r="D227" s="52" t="str">
-        <x:f>IF($B227="","",IFERROR(VLOOKUP($B227,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B227="","",IFERROR(VLOOKUP($B227,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E227" s="62" t="str">
         <x:f>IF($D227="","",IF($D227="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F227" s="53" t="str">
-        <x:f>IF($B227="","",IFERROR(VLOOKUP($B227,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B227="","",IFERROR(VLOOKUP($B227,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B227),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G227" s="65" t="str">
         <x:f>IF($F227="","",IFERROR(VLOOKUP($F227,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13271,13 +13286,13 @@
       <x:c r="B228" s="33"/>
       <x:c r="C228" s="59"/>
       <x:c r="D228" s="52" t="str">
-        <x:f>IF($B228="","",IFERROR(VLOOKUP($B228,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B228="","",IFERROR(VLOOKUP($B228,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E228" s="62" t="str">
         <x:f>IF($D228="","",IF($D228="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F228" s="53" t="str">
-        <x:f>IF($B228="","",IFERROR(VLOOKUP($B228,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B228="","",IFERROR(VLOOKUP($B228,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B228),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G228" s="65" t="str">
         <x:f>IF($F228="","",IFERROR(VLOOKUP($F228,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13325,13 +13340,13 @@
       <x:c r="B229" s="33"/>
       <x:c r="C229" s="59"/>
       <x:c r="D229" s="52" t="str">
-        <x:f>IF($B229="","",IFERROR(VLOOKUP($B229,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B229="","",IFERROR(VLOOKUP($B229,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E229" s="62" t="str">
         <x:f>IF($D229="","",IF($D229="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F229" s="53" t="str">
-        <x:f>IF($B229="","",IFERROR(VLOOKUP($B229,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B229="","",IFERROR(VLOOKUP($B229,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B229),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G229" s="65" t="str">
         <x:f>IF($F229="","",IFERROR(VLOOKUP($F229,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13379,13 +13394,13 @@
       <x:c r="B230" s="33"/>
       <x:c r="C230" s="59"/>
       <x:c r="D230" s="52" t="str">
-        <x:f>IF($B230="","",IFERROR(VLOOKUP($B230,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B230="","",IFERROR(VLOOKUP($B230,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E230" s="62" t="str">
         <x:f>IF($D230="","",IF($D230="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F230" s="53" t="str">
-        <x:f>IF($B230="","",IFERROR(VLOOKUP($B230,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B230="","",IFERROR(VLOOKUP($B230,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B230),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G230" s="65" t="str">
         <x:f>IF($F230="","",IFERROR(VLOOKUP($F230,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13433,13 +13448,13 @@
       <x:c r="B231" s="33"/>
       <x:c r="C231" s="59"/>
       <x:c r="D231" s="52" t="str">
-        <x:f>IF($B231="","",IFERROR(VLOOKUP($B231,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B231="","",IFERROR(VLOOKUP($B231,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E231" s="62" t="str">
         <x:f>IF($D231="","",IF($D231="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F231" s="53" t="str">
-        <x:f>IF($B231="","",IFERROR(VLOOKUP($B231,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B231="","",IFERROR(VLOOKUP($B231,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B231),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G231" s="65" t="str">
         <x:f>IF($F231="","",IFERROR(VLOOKUP($F231,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13487,13 +13502,13 @@
       <x:c r="B232" s="33"/>
       <x:c r="C232" s="59"/>
       <x:c r="D232" s="52" t="str">
-        <x:f>IF($B232="","",IFERROR(VLOOKUP($B232,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B232="","",IFERROR(VLOOKUP($B232,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E232" s="62" t="str">
         <x:f>IF($D232="","",IF($D232="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F232" s="53" t="str">
-        <x:f>IF($B232="","",IFERROR(VLOOKUP($B232,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B232="","",IFERROR(VLOOKUP($B232,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B232),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G232" s="65" t="str">
         <x:f>IF($F232="","",IFERROR(VLOOKUP($F232,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13541,13 +13556,13 @@
       <x:c r="B233" s="33"/>
       <x:c r="C233" s="59"/>
       <x:c r="D233" s="52" t="str">
-        <x:f>IF($B233="","",IFERROR(VLOOKUP($B233,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B233="","",IFERROR(VLOOKUP($B233,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E233" s="62" t="str">
         <x:f>IF($D233="","",IF($D233="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F233" s="53" t="str">
-        <x:f>IF($B233="","",IFERROR(VLOOKUP($B233,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B233="","",IFERROR(VLOOKUP($B233,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B233),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G233" s="65" t="str">
         <x:f>IF($F233="","",IFERROR(VLOOKUP($F233,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13595,13 +13610,13 @@
       <x:c r="B234" s="33"/>
       <x:c r="C234" s="59"/>
       <x:c r="D234" s="52" t="str">
-        <x:f>IF($B234="","",IFERROR(VLOOKUP($B234,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B234="","",IFERROR(VLOOKUP($B234,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E234" s="62" t="str">
         <x:f>IF($D234="","",IF($D234="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F234" s="53" t="str">
-        <x:f>IF($B234="","",IFERROR(VLOOKUP($B234,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B234="","",IFERROR(VLOOKUP($B234,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B234),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G234" s="65" t="str">
         <x:f>IF($F234="","",IFERROR(VLOOKUP($F234,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13649,13 +13664,13 @@
       <x:c r="B235" s="33"/>
       <x:c r="C235" s="59"/>
       <x:c r="D235" s="52" t="str">
-        <x:f>IF($B235="","",IFERROR(VLOOKUP($B235,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B235="","",IFERROR(VLOOKUP($B235,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E235" s="62" t="str">
         <x:f>IF($D235="","",IF($D235="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F235" s="53" t="str">
-        <x:f>IF($B235="","",IFERROR(VLOOKUP($B235,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B235="","",IFERROR(VLOOKUP($B235,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B235),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G235" s="65" t="str">
         <x:f>IF($F235="","",IFERROR(VLOOKUP($F235,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13703,13 +13718,13 @@
       <x:c r="B236" s="33"/>
       <x:c r="C236" s="59"/>
       <x:c r="D236" s="52" t="str">
-        <x:f>IF($B236="","",IFERROR(VLOOKUP($B236,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B236="","",IFERROR(VLOOKUP($B236,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E236" s="62" t="str">
         <x:f>IF($D236="","",IF($D236="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F236" s="53" t="str">
-        <x:f>IF($B236="","",IFERROR(VLOOKUP($B236,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B236="","",IFERROR(VLOOKUP($B236,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B236),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G236" s="65" t="str">
         <x:f>IF($F236="","",IFERROR(VLOOKUP($F236,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13757,13 +13772,13 @@
       <x:c r="B237" s="33"/>
       <x:c r="C237" s="59"/>
       <x:c r="D237" s="52" t="str">
-        <x:f>IF($B237="","",IFERROR(VLOOKUP($B237,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B237="","",IFERROR(VLOOKUP($B237,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E237" s="62" t="str">
         <x:f>IF($D237="","",IF($D237="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F237" s="53" t="str">
-        <x:f>IF($B237="","",IFERROR(VLOOKUP($B237,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B237="","",IFERROR(VLOOKUP($B237,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B237),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G237" s="65" t="str">
         <x:f>IF($F237="","",IFERROR(VLOOKUP($F237,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13811,13 +13826,13 @@
       <x:c r="B238" s="33"/>
       <x:c r="C238" s="59"/>
       <x:c r="D238" s="52" t="str">
-        <x:f>IF($B238="","",IFERROR(VLOOKUP($B238,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B238="","",IFERROR(VLOOKUP($B238,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E238" s="62" t="str">
         <x:f>IF($D238="","",IF($D238="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F238" s="53" t="str">
-        <x:f>IF($B238="","",IFERROR(VLOOKUP($B238,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B238="","",IFERROR(VLOOKUP($B238,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B238),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G238" s="65" t="str">
         <x:f>IF($F238="","",IFERROR(VLOOKUP($F238,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13865,13 +13880,13 @@
       <x:c r="B239" s="33"/>
       <x:c r="C239" s="59"/>
       <x:c r="D239" s="52" t="str">
-        <x:f>IF($B239="","",IFERROR(VLOOKUP($B239,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B239="","",IFERROR(VLOOKUP($B239,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E239" s="62" t="str">
         <x:f>IF($D239="","",IF($D239="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F239" s="53" t="str">
-        <x:f>IF($B239="","",IFERROR(VLOOKUP($B239,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B239="","",IFERROR(VLOOKUP($B239,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B239),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G239" s="65" t="str">
         <x:f>IF($F239="","",IFERROR(VLOOKUP($F239,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13919,13 +13934,13 @@
       <x:c r="B240" s="33"/>
       <x:c r="C240" s="59"/>
       <x:c r="D240" s="52" t="str">
-        <x:f>IF($B240="","",IFERROR(VLOOKUP($B240,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B240="","",IFERROR(VLOOKUP($B240,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E240" s="62" t="str">
         <x:f>IF($D240="","",IF($D240="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F240" s="53" t="str">
-        <x:f>IF($B240="","",IFERROR(VLOOKUP($B240,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B240="","",IFERROR(VLOOKUP($B240,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B240),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G240" s="65" t="str">
         <x:f>IF($F240="","",IFERROR(VLOOKUP($F240,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -13973,13 +13988,13 @@
       <x:c r="B241" s="33"/>
       <x:c r="C241" s="59"/>
       <x:c r="D241" s="52" t="str">
-        <x:f>IF($B241="","",IFERROR(VLOOKUP($B241,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B241="","",IFERROR(VLOOKUP($B241,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E241" s="62" t="str">
         <x:f>IF($D241="","",IF($D241="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F241" s="53" t="str">
-        <x:f>IF($B241="","",IFERROR(VLOOKUP($B241,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B241="","",IFERROR(VLOOKUP($B241,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B241),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G241" s="65" t="str">
         <x:f>IF($F241="","",IFERROR(VLOOKUP($F241,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14027,13 +14042,13 @@
       <x:c r="B242" s="33"/>
       <x:c r="C242" s="59"/>
       <x:c r="D242" s="52" t="str">
-        <x:f>IF($B242="","",IFERROR(VLOOKUP($B242,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B242="","",IFERROR(VLOOKUP($B242,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E242" s="62" t="str">
         <x:f>IF($D242="","",IF($D242="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F242" s="53" t="str">
-        <x:f>IF($B242="","",IFERROR(VLOOKUP($B242,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B242="","",IFERROR(VLOOKUP($B242,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B242),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G242" s="65" t="str">
         <x:f>IF($F242="","",IFERROR(VLOOKUP($F242,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14081,13 +14096,13 @@
       <x:c r="B243" s="33"/>
       <x:c r="C243" s="59"/>
       <x:c r="D243" s="52" t="str">
-        <x:f>IF($B243="","",IFERROR(VLOOKUP($B243,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B243="","",IFERROR(VLOOKUP($B243,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E243" s="62" t="str">
         <x:f>IF($D243="","",IF($D243="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F243" s="53" t="str">
-        <x:f>IF($B243="","",IFERROR(VLOOKUP($B243,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B243="","",IFERROR(VLOOKUP($B243,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B243),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G243" s="65" t="str">
         <x:f>IF($F243="","",IFERROR(VLOOKUP($F243,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14135,13 +14150,13 @@
       <x:c r="B244" s="33"/>
       <x:c r="C244" s="59"/>
       <x:c r="D244" s="52" t="str">
-        <x:f>IF($B244="","",IFERROR(VLOOKUP($B244,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B244="","",IFERROR(VLOOKUP($B244,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E244" s="62" t="str">
         <x:f>IF($D244="","",IF($D244="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F244" s="53" t="str">
-        <x:f>IF($B244="","",IFERROR(VLOOKUP($B244,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B244="","",IFERROR(VLOOKUP($B244,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B244),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G244" s="65" t="str">
         <x:f>IF($F244="","",IFERROR(VLOOKUP($F244,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14189,13 +14204,13 @@
       <x:c r="B245" s="33"/>
       <x:c r="C245" s="59"/>
       <x:c r="D245" s="52" t="str">
-        <x:f>IF($B245="","",IFERROR(VLOOKUP($B245,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B245="","",IFERROR(VLOOKUP($B245,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E245" s="62" t="str">
         <x:f>IF($D245="","",IF($D245="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F245" s="53" t="str">
-        <x:f>IF($B245="","",IFERROR(VLOOKUP($B245,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B245="","",IFERROR(VLOOKUP($B245,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B245),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G245" s="65" t="str">
         <x:f>IF($F245="","",IFERROR(VLOOKUP($F245,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14243,13 +14258,13 @@
       <x:c r="B246" s="33"/>
       <x:c r="C246" s="59"/>
       <x:c r="D246" s="52" t="str">
-        <x:f>IF($B246="","",IFERROR(VLOOKUP($B246,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B246="","",IFERROR(VLOOKUP($B246,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E246" s="62" t="str">
         <x:f>IF($D246="","",IF($D246="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F246" s="53" t="str">
-        <x:f>IF($B246="","",IFERROR(VLOOKUP($B246,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B246="","",IFERROR(VLOOKUP($B246,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B246),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G246" s="65" t="str">
         <x:f>IF($F246="","",IFERROR(VLOOKUP($F246,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14297,13 +14312,13 @@
       <x:c r="B247" s="33"/>
       <x:c r="C247" s="59"/>
       <x:c r="D247" s="52" t="str">
-        <x:f>IF($B247="","",IFERROR(VLOOKUP($B247,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B247="","",IFERROR(VLOOKUP($B247,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E247" s="62" t="str">
         <x:f>IF($D247="","",IF($D247="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F247" s="53" t="str">
-        <x:f>IF($B247="","",IFERROR(VLOOKUP($B247,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B247="","",IFERROR(VLOOKUP($B247,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B247),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G247" s="65" t="str">
         <x:f>IF($F247="","",IFERROR(VLOOKUP($F247,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14351,13 +14366,13 @@
       <x:c r="B248" s="33"/>
       <x:c r="C248" s="59"/>
       <x:c r="D248" s="52" t="str">
-        <x:f>IF($B248="","",IFERROR(VLOOKUP($B248,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B248="","",IFERROR(VLOOKUP($B248,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E248" s="62" t="str">
         <x:f>IF($D248="","",IF($D248="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F248" s="53" t="str">
-        <x:f>IF($B248="","",IFERROR(VLOOKUP($B248,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B248="","",IFERROR(VLOOKUP($B248,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B248),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G248" s="65" t="str">
         <x:f>IF($F248="","",IFERROR(VLOOKUP($F248,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14405,13 +14420,13 @@
       <x:c r="B249" s="33"/>
       <x:c r="C249" s="59"/>
       <x:c r="D249" s="52" t="str">
-        <x:f>IF($B249="","",IFERROR(VLOOKUP($B249,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B249="","",IFERROR(VLOOKUP($B249,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E249" s="62" t="str">
         <x:f>IF($D249="","",IF($D249="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F249" s="53" t="str">
-        <x:f>IF($B249="","",IFERROR(VLOOKUP($B249,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B249="","",IFERROR(VLOOKUP($B249,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B249),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G249" s="65" t="str">
         <x:f>IF($F249="","",IFERROR(VLOOKUP($F249,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14459,13 +14474,13 @@
       <x:c r="B250" s="33"/>
       <x:c r="C250" s="59"/>
       <x:c r="D250" s="52" t="str">
-        <x:f>IF($B250="","",IFERROR(VLOOKUP($B250,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B250="","",IFERROR(VLOOKUP($B250,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E250" s="62" t="str">
         <x:f>IF($D250="","",IF($D250="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F250" s="53" t="str">
-        <x:f>IF($B250="","",IFERROR(VLOOKUP($B250,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B250="","",IFERROR(VLOOKUP($B250,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B250),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G250" s="65" t="str">
         <x:f>IF($F250="","",IFERROR(VLOOKUP($F250,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14513,13 +14528,13 @@
       <x:c r="B251" s="33"/>
       <x:c r="C251" s="59"/>
       <x:c r="D251" s="52" t="str">
-        <x:f>IF($B251="","",IFERROR(VLOOKUP($B251,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B251="","",IFERROR(VLOOKUP($B251,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E251" s="62" t="str">
         <x:f>IF($D251="","",IF($D251="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F251" s="53" t="str">
-        <x:f>IF($B251="","",IFERROR(VLOOKUP($B251,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B251="","",IFERROR(VLOOKUP($B251,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B251),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G251" s="65" t="str">
         <x:f>IF($F251="","",IFERROR(VLOOKUP($F251,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14567,13 +14582,13 @@
       <x:c r="B252" s="33"/>
       <x:c r="C252" s="59"/>
       <x:c r="D252" s="52" t="str">
-        <x:f>IF($B252="","",IFERROR(VLOOKUP($B252,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B252="","",IFERROR(VLOOKUP($B252,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E252" s="62" t="str">
         <x:f>IF($D252="","",IF($D252="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F252" s="53" t="str">
-        <x:f>IF($B252="","",IFERROR(VLOOKUP($B252,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B252="","",IFERROR(VLOOKUP($B252,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B252),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G252" s="65" t="str">
         <x:f>IF($F252="","",IFERROR(VLOOKUP($F252,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14621,13 +14636,13 @@
       <x:c r="B253" s="33"/>
       <x:c r="C253" s="59"/>
       <x:c r="D253" s="52" t="str">
-        <x:f>IF($B253="","",IFERROR(VLOOKUP($B253,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B253="","",IFERROR(VLOOKUP($B253,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E253" s="62" t="str">
         <x:f>IF($D253="","",IF($D253="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F253" s="53" t="str">
-        <x:f>IF($B253="","",IFERROR(VLOOKUP($B253,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B253="","",IFERROR(VLOOKUP($B253,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B253),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G253" s="65" t="str">
         <x:f>IF($F253="","",IFERROR(VLOOKUP($F253,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14675,13 +14690,13 @@
       <x:c r="B254" s="33"/>
       <x:c r="C254" s="59"/>
       <x:c r="D254" s="52" t="str">
-        <x:f>IF($B254="","",IFERROR(VLOOKUP($B254,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B254="","",IFERROR(VLOOKUP($B254,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E254" s="62" t="str">
         <x:f>IF($D254="","",IF($D254="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F254" s="53" t="str">
-        <x:f>IF($B254="","",IFERROR(VLOOKUP($B254,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B254="","",IFERROR(VLOOKUP($B254,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B254),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G254" s="65" t="str">
         <x:f>IF($F254="","",IFERROR(VLOOKUP($F254,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14729,13 +14744,13 @@
       <x:c r="B255" s="33"/>
       <x:c r="C255" s="59"/>
       <x:c r="D255" s="52" t="str">
-        <x:f>IF($B255="","",IFERROR(VLOOKUP($B255,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B255="","",IFERROR(VLOOKUP($B255,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E255" s="62" t="str">
         <x:f>IF($D255="","",IF($D255="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F255" s="53" t="str">
-        <x:f>IF($B255="","",IFERROR(VLOOKUP($B255,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B255="","",IFERROR(VLOOKUP($B255,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B255),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G255" s="65" t="str">
         <x:f>IF($F255="","",IFERROR(VLOOKUP($F255,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14783,13 +14798,13 @@
       <x:c r="B256" s="33"/>
       <x:c r="C256" s="59"/>
       <x:c r="D256" s="52" t="str">
-        <x:f>IF($B256="","",IFERROR(VLOOKUP($B256,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B256="","",IFERROR(VLOOKUP($B256,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E256" s="62" t="str">
         <x:f>IF($D256="","",IF($D256="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F256" s="53" t="str">
-        <x:f>IF($B256="","",IFERROR(VLOOKUP($B256,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B256="","",IFERROR(VLOOKUP($B256,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B256),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G256" s="65" t="str">
         <x:f>IF($F256="","",IFERROR(VLOOKUP($F256,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14837,13 +14852,13 @@
       <x:c r="B257" s="33"/>
       <x:c r="C257" s="59"/>
       <x:c r="D257" s="52" t="str">
-        <x:f>IF($B257="","",IFERROR(VLOOKUP($B257,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B257="","",IFERROR(VLOOKUP($B257,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E257" s="62" t="str">
         <x:f>IF($D257="","",IF($D257="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F257" s="53" t="str">
-        <x:f>IF($B257="","",IFERROR(VLOOKUP($B257,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B257="","",IFERROR(VLOOKUP($B257,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B257),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G257" s="65" t="str">
         <x:f>IF($F257="","",IFERROR(VLOOKUP($F257,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14891,13 +14906,13 @@
       <x:c r="B258" s="33"/>
       <x:c r="C258" s="59"/>
       <x:c r="D258" s="52" t="str">
-        <x:f>IF($B258="","",IFERROR(VLOOKUP($B258,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B258="","",IFERROR(VLOOKUP($B258,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E258" s="62" t="str">
         <x:f>IF($D258="","",IF($D258="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F258" s="53" t="str">
-        <x:f>IF($B258="","",IFERROR(VLOOKUP($B258,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B258="","",IFERROR(VLOOKUP($B258,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B258),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G258" s="65" t="str">
         <x:f>IF($F258="","",IFERROR(VLOOKUP($F258,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14945,13 +14960,13 @@
       <x:c r="B259" s="33"/>
       <x:c r="C259" s="59"/>
       <x:c r="D259" s="52" t="str">
-        <x:f>IF($B259="","",IFERROR(VLOOKUP($B259,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B259="","",IFERROR(VLOOKUP($B259,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E259" s="62" t="str">
         <x:f>IF($D259="","",IF($D259="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F259" s="53" t="str">
-        <x:f>IF($B259="","",IFERROR(VLOOKUP($B259,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B259="","",IFERROR(VLOOKUP($B259,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B259),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G259" s="65" t="str">
         <x:f>IF($F259="","",IFERROR(VLOOKUP($F259,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -14999,13 +15014,13 @@
       <x:c r="B260" s="33"/>
       <x:c r="C260" s="59"/>
       <x:c r="D260" s="52" t="str">
-        <x:f>IF($B260="","",IFERROR(VLOOKUP($B260,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B260="","",IFERROR(VLOOKUP($B260,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E260" s="62" t="str">
         <x:f>IF($D260="","",IF($D260="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F260" s="53" t="str">
-        <x:f>IF($B260="","",IFERROR(VLOOKUP($B260,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B260="","",IFERROR(VLOOKUP($B260,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B260),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G260" s="65" t="str">
         <x:f>IF($F260="","",IFERROR(VLOOKUP($F260,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15053,13 +15068,13 @@
       <x:c r="B261" s="33"/>
       <x:c r="C261" s="59"/>
       <x:c r="D261" s="52" t="str">
-        <x:f>IF($B261="","",IFERROR(VLOOKUP($B261,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B261="","",IFERROR(VLOOKUP($B261,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E261" s="62" t="str">
         <x:f>IF($D261="","",IF($D261="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F261" s="53" t="str">
-        <x:f>IF($B261="","",IFERROR(VLOOKUP($B261,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B261="","",IFERROR(VLOOKUP($B261,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B261),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G261" s="65" t="str">
         <x:f>IF($F261="","",IFERROR(VLOOKUP($F261,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15107,13 +15122,13 @@
       <x:c r="B262" s="33"/>
       <x:c r="C262" s="59"/>
       <x:c r="D262" s="52" t="str">
-        <x:f>IF($B262="","",IFERROR(VLOOKUP($B262,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B262="","",IFERROR(VLOOKUP($B262,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E262" s="62" t="str">
         <x:f>IF($D262="","",IF($D262="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F262" s="53" t="str">
-        <x:f>IF($B262="","",IFERROR(VLOOKUP($B262,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B262="","",IFERROR(VLOOKUP($B262,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B262),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G262" s="65" t="str">
         <x:f>IF($F262="","",IFERROR(VLOOKUP($F262,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15161,13 +15176,13 @@
       <x:c r="B263" s="33"/>
       <x:c r="C263" s="59"/>
       <x:c r="D263" s="52" t="str">
-        <x:f>IF($B263="","",IFERROR(VLOOKUP($B263,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B263="","",IFERROR(VLOOKUP($B263,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E263" s="62" t="str">
         <x:f>IF($D263="","",IF($D263="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F263" s="53" t="str">
-        <x:f>IF($B263="","",IFERROR(VLOOKUP($B263,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B263="","",IFERROR(VLOOKUP($B263,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B263),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G263" s="65" t="str">
         <x:f>IF($F263="","",IFERROR(VLOOKUP($F263,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15215,13 +15230,13 @@
       <x:c r="B264" s="33"/>
       <x:c r="C264" s="59"/>
       <x:c r="D264" s="52" t="str">
-        <x:f>IF($B264="","",IFERROR(VLOOKUP($B264,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B264="","",IFERROR(VLOOKUP($B264,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E264" s="62" t="str">
         <x:f>IF($D264="","",IF($D264="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F264" s="53" t="str">
-        <x:f>IF($B264="","",IFERROR(VLOOKUP($B264,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B264="","",IFERROR(VLOOKUP($B264,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B264),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G264" s="65" t="str">
         <x:f>IF($F264="","",IFERROR(VLOOKUP($F264,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15269,13 +15284,13 @@
       <x:c r="B265" s="33"/>
       <x:c r="C265" s="59"/>
       <x:c r="D265" s="52" t="str">
-        <x:f>IF($B265="","",IFERROR(VLOOKUP($B265,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B265="","",IFERROR(VLOOKUP($B265,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E265" s="62" t="str">
         <x:f>IF($D265="","",IF($D265="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F265" s="53" t="str">
-        <x:f>IF($B265="","",IFERROR(VLOOKUP($B265,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B265="","",IFERROR(VLOOKUP($B265,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B265),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G265" s="65" t="str">
         <x:f>IF($F265="","",IFERROR(VLOOKUP($F265,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15323,13 +15338,13 @@
       <x:c r="B266" s="33"/>
       <x:c r="C266" s="59"/>
       <x:c r="D266" s="52" t="str">
-        <x:f>IF($B266="","",IFERROR(VLOOKUP($B266,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B266="","",IFERROR(VLOOKUP($B266,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E266" s="62" t="str">
         <x:f>IF($D266="","",IF($D266="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F266" s="53" t="str">
-        <x:f>IF($B266="","",IFERROR(VLOOKUP($B266,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B266="","",IFERROR(VLOOKUP($B266,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B266),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G266" s="65" t="str">
         <x:f>IF($F266="","",IFERROR(VLOOKUP($F266,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15377,13 +15392,13 @@
       <x:c r="B267" s="33"/>
       <x:c r="C267" s="59"/>
       <x:c r="D267" s="52" t="str">
-        <x:f>IF($B267="","",IFERROR(VLOOKUP($B267,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B267="","",IFERROR(VLOOKUP($B267,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E267" s="62" t="str">
         <x:f>IF($D267="","",IF($D267="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F267" s="53" t="str">
-        <x:f>IF($B267="","",IFERROR(VLOOKUP($B267,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B267="","",IFERROR(VLOOKUP($B267,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B267),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G267" s="65" t="str">
         <x:f>IF($F267="","",IFERROR(VLOOKUP($F267,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15431,13 +15446,13 @@
       <x:c r="B268" s="33"/>
       <x:c r="C268" s="59"/>
       <x:c r="D268" s="52" t="str">
-        <x:f>IF($B268="","",IFERROR(VLOOKUP($B268,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B268="","",IFERROR(VLOOKUP($B268,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E268" s="62" t="str">
         <x:f>IF($D268="","",IF($D268="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F268" s="53" t="str">
-        <x:f>IF($B268="","",IFERROR(VLOOKUP($B268,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B268="","",IFERROR(VLOOKUP($B268,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B268),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G268" s="65" t="str">
         <x:f>IF($F268="","",IFERROR(VLOOKUP($F268,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15485,13 +15500,13 @@
       <x:c r="B269" s="33"/>
       <x:c r="C269" s="59"/>
       <x:c r="D269" s="52" t="str">
-        <x:f>IF($B269="","",IFERROR(VLOOKUP($B269,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B269="","",IFERROR(VLOOKUP($B269,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E269" s="62" t="str">
         <x:f>IF($D269="","",IF($D269="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F269" s="53" t="str">
-        <x:f>IF($B269="","",IFERROR(VLOOKUP($B269,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B269="","",IFERROR(VLOOKUP($B269,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B269),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G269" s="65" t="str">
         <x:f>IF($F269="","",IFERROR(VLOOKUP($F269,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15539,13 +15554,13 @@
       <x:c r="B270" s="33"/>
       <x:c r="C270" s="59"/>
       <x:c r="D270" s="52" t="str">
-        <x:f>IF($B270="","",IFERROR(VLOOKUP($B270,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B270="","",IFERROR(VLOOKUP($B270,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E270" s="62" t="str">
         <x:f>IF($D270="","",IF($D270="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F270" s="53" t="str">
-        <x:f>IF($B270="","",IFERROR(VLOOKUP($B270,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B270="","",IFERROR(VLOOKUP($B270,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B270),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G270" s="65" t="str">
         <x:f>IF($F270="","",IFERROR(VLOOKUP($F270,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15593,13 +15608,13 @@
       <x:c r="B271" s="33"/>
       <x:c r="C271" s="59"/>
       <x:c r="D271" s="52" t="str">
-        <x:f>IF($B271="","",IFERROR(VLOOKUP($B271,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B271="","",IFERROR(VLOOKUP($B271,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E271" s="62" t="str">
         <x:f>IF($D271="","",IF($D271="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F271" s="53" t="str">
-        <x:f>IF($B271="","",IFERROR(VLOOKUP($B271,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B271="","",IFERROR(VLOOKUP($B271,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B271),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G271" s="65" t="str">
         <x:f>IF($F271="","",IFERROR(VLOOKUP($F271,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15647,13 +15662,13 @@
       <x:c r="B272" s="33"/>
       <x:c r="C272" s="59"/>
       <x:c r="D272" s="52" t="str">
-        <x:f>IF($B272="","",IFERROR(VLOOKUP($B272,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B272="","",IFERROR(VLOOKUP($B272,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E272" s="62" t="str">
         <x:f>IF($D272="","",IF($D272="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F272" s="53" t="str">
-        <x:f>IF($B272="","",IFERROR(VLOOKUP($B272,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B272="","",IFERROR(VLOOKUP($B272,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B272),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G272" s="65" t="str">
         <x:f>IF($F272="","",IFERROR(VLOOKUP($F272,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15701,13 +15716,13 @@
       <x:c r="B273" s="33"/>
       <x:c r="C273" s="59"/>
       <x:c r="D273" s="52" t="str">
-        <x:f>IF($B273="","",IFERROR(VLOOKUP($B273,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B273="","",IFERROR(VLOOKUP($B273,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E273" s="62" t="str">
         <x:f>IF($D273="","",IF($D273="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F273" s="53" t="str">
-        <x:f>IF($B273="","",IFERROR(VLOOKUP($B273,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B273="","",IFERROR(VLOOKUP($B273,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B273),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G273" s="65" t="str">
         <x:f>IF($F273="","",IFERROR(VLOOKUP($F273,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15755,13 +15770,13 @@
       <x:c r="B274" s="33"/>
       <x:c r="C274" s="59"/>
       <x:c r="D274" s="52" t="str">
-        <x:f>IF($B274="","",IFERROR(VLOOKUP($B274,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B274="","",IFERROR(VLOOKUP($B274,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E274" s="62" t="str">
         <x:f>IF($D274="","",IF($D274="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F274" s="53" t="str">
-        <x:f>IF($B274="","",IFERROR(VLOOKUP($B274,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B274="","",IFERROR(VLOOKUP($B274,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B274),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G274" s="65" t="str">
         <x:f>IF($F274="","",IFERROR(VLOOKUP($F274,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15809,13 +15824,13 @@
       <x:c r="B275" s="33"/>
       <x:c r="C275" s="59"/>
       <x:c r="D275" s="52" t="str">
-        <x:f>IF($B275="","",IFERROR(VLOOKUP($B275,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B275="","",IFERROR(VLOOKUP($B275,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E275" s="62" t="str">
         <x:f>IF($D275="","",IF($D275="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F275" s="53" t="str">
-        <x:f>IF($B275="","",IFERROR(VLOOKUP($B275,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B275="","",IFERROR(VLOOKUP($B275,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B275),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G275" s="65" t="str">
         <x:f>IF($F275="","",IFERROR(VLOOKUP($F275,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15863,13 +15878,13 @@
       <x:c r="B276" s="33"/>
       <x:c r="C276" s="59"/>
       <x:c r="D276" s="52" t="str">
-        <x:f>IF($B276="","",IFERROR(VLOOKUP($B276,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B276="","",IFERROR(VLOOKUP($B276,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E276" s="62" t="str">
         <x:f>IF($D276="","",IF($D276="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F276" s="53" t="str">
-        <x:f>IF($B276="","",IFERROR(VLOOKUP($B276,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B276="","",IFERROR(VLOOKUP($B276,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B276),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G276" s="65" t="str">
         <x:f>IF($F276="","",IFERROR(VLOOKUP($F276,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15917,13 +15932,13 @@
       <x:c r="B277" s="33"/>
       <x:c r="C277" s="59"/>
       <x:c r="D277" s="52" t="str">
-        <x:f>IF($B277="","",IFERROR(VLOOKUP($B277,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B277="","",IFERROR(VLOOKUP($B277,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E277" s="62" t="str">
         <x:f>IF($D277="","",IF($D277="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F277" s="53" t="str">
-        <x:f>IF($B277="","",IFERROR(VLOOKUP($B277,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B277="","",IFERROR(VLOOKUP($B277,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B277),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G277" s="65" t="str">
         <x:f>IF($F277="","",IFERROR(VLOOKUP($F277,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -15971,13 +15986,13 @@
       <x:c r="B278" s="33"/>
       <x:c r="C278" s="59"/>
       <x:c r="D278" s="52" t="str">
-        <x:f>IF($B278="","",IFERROR(VLOOKUP($B278,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B278="","",IFERROR(VLOOKUP($B278,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E278" s="62" t="str">
         <x:f>IF($D278="","",IF($D278="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F278" s="53" t="str">
-        <x:f>IF($B278="","",IFERROR(VLOOKUP($B278,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B278="","",IFERROR(VLOOKUP($B278,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B278),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G278" s="65" t="str">
         <x:f>IF($F278="","",IFERROR(VLOOKUP($F278,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16025,13 +16040,13 @@
       <x:c r="B279" s="33"/>
       <x:c r="C279" s="59"/>
       <x:c r="D279" s="52" t="str">
-        <x:f>IF($B279="","",IFERROR(VLOOKUP($B279,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B279="","",IFERROR(VLOOKUP($B279,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E279" s="62" t="str">
         <x:f>IF($D279="","",IF($D279="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F279" s="53" t="str">
-        <x:f>IF($B279="","",IFERROR(VLOOKUP($B279,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B279="","",IFERROR(VLOOKUP($B279,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B279),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G279" s="65" t="str">
         <x:f>IF($F279="","",IFERROR(VLOOKUP($F279,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16079,13 +16094,13 @@
       <x:c r="B280" s="33"/>
       <x:c r="C280" s="59"/>
       <x:c r="D280" s="52" t="str">
-        <x:f>IF($B280="","",IFERROR(VLOOKUP($B280,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B280="","",IFERROR(VLOOKUP($B280,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E280" s="62" t="str">
         <x:f>IF($D280="","",IF($D280="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F280" s="53" t="str">
-        <x:f>IF($B280="","",IFERROR(VLOOKUP($B280,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B280="","",IFERROR(VLOOKUP($B280,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B280),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G280" s="65" t="str">
         <x:f>IF($F280="","",IFERROR(VLOOKUP($F280,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16133,13 +16148,13 @@
       <x:c r="B281" s="33"/>
       <x:c r="C281" s="59"/>
       <x:c r="D281" s="52" t="str">
-        <x:f>IF($B281="","",IFERROR(VLOOKUP($B281,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B281="","",IFERROR(VLOOKUP($B281,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E281" s="62" t="str">
         <x:f>IF($D281="","",IF($D281="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F281" s="53" t="str">
-        <x:f>IF($B281="","",IFERROR(VLOOKUP($B281,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B281="","",IFERROR(VLOOKUP($B281,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B281),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G281" s="65" t="str">
         <x:f>IF($F281="","",IFERROR(VLOOKUP($F281,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16187,13 +16202,13 @@
       <x:c r="B282" s="33"/>
       <x:c r="C282" s="59"/>
       <x:c r="D282" s="52" t="str">
-        <x:f>IF($B282="","",IFERROR(VLOOKUP($B282,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B282="","",IFERROR(VLOOKUP($B282,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E282" s="62" t="str">
         <x:f>IF($D282="","",IF($D282="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F282" s="53" t="str">
-        <x:f>IF($B282="","",IFERROR(VLOOKUP($B282,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B282="","",IFERROR(VLOOKUP($B282,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B282),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G282" s="65" t="str">
         <x:f>IF($F282="","",IFERROR(VLOOKUP($F282,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16241,13 +16256,13 @@
       <x:c r="B283" s="33"/>
       <x:c r="C283" s="59"/>
       <x:c r="D283" s="52" t="str">
-        <x:f>IF($B283="","",IFERROR(VLOOKUP($B283,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B283="","",IFERROR(VLOOKUP($B283,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E283" s="62" t="str">
         <x:f>IF($D283="","",IF($D283="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F283" s="53" t="str">
-        <x:f>IF($B283="","",IFERROR(VLOOKUP($B283,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B283="","",IFERROR(VLOOKUP($B283,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B283),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G283" s="65" t="str">
         <x:f>IF($F283="","",IFERROR(VLOOKUP($F283,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16295,13 +16310,13 @@
       <x:c r="B284" s="33"/>
       <x:c r="C284" s="59"/>
       <x:c r="D284" s="52" t="str">
-        <x:f>IF($B284="","",IFERROR(VLOOKUP($B284,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B284="","",IFERROR(VLOOKUP($B284,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E284" s="62" t="str">
         <x:f>IF($D284="","",IF($D284="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F284" s="53" t="str">
-        <x:f>IF($B284="","",IFERROR(VLOOKUP($B284,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B284="","",IFERROR(VLOOKUP($B284,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B284),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G284" s="65" t="str">
         <x:f>IF($F284="","",IFERROR(VLOOKUP($F284,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16349,13 +16364,13 @@
       <x:c r="B285" s="33"/>
       <x:c r="C285" s="59"/>
       <x:c r="D285" s="52" t="str">
-        <x:f>IF($B285="","",IFERROR(VLOOKUP($B285,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B285="","",IFERROR(VLOOKUP($B285,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E285" s="62" t="str">
         <x:f>IF($D285="","",IF($D285="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F285" s="53" t="str">
-        <x:f>IF($B285="","",IFERROR(VLOOKUP($B285,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B285="","",IFERROR(VLOOKUP($B285,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B285),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G285" s="65" t="str">
         <x:f>IF($F285="","",IFERROR(VLOOKUP($F285,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16403,13 +16418,13 @@
       <x:c r="B286" s="33"/>
       <x:c r="C286" s="59"/>
       <x:c r="D286" s="52" t="str">
-        <x:f>IF($B286="","",IFERROR(VLOOKUP($B286,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B286="","",IFERROR(VLOOKUP($B286,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E286" s="62" t="str">
         <x:f>IF($D286="","",IF($D286="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F286" s="53" t="str">
-        <x:f>IF($B286="","",IFERROR(VLOOKUP($B286,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B286="","",IFERROR(VLOOKUP($B286,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B286),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G286" s="65" t="str">
         <x:f>IF($F286="","",IFERROR(VLOOKUP($F286,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16457,13 +16472,13 @@
       <x:c r="B287" s="33"/>
       <x:c r="C287" s="59"/>
       <x:c r="D287" s="52" t="str">
-        <x:f>IF($B287="","",IFERROR(VLOOKUP($B287,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B287="","",IFERROR(VLOOKUP($B287,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E287" s="62" t="str">
         <x:f>IF($D287="","",IF($D287="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F287" s="53" t="str">
-        <x:f>IF($B287="","",IFERROR(VLOOKUP($B287,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B287="","",IFERROR(VLOOKUP($B287,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B287),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G287" s="65" t="str">
         <x:f>IF($F287="","",IFERROR(VLOOKUP($F287,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16511,13 +16526,13 @@
       <x:c r="B288" s="33"/>
       <x:c r="C288" s="59"/>
       <x:c r="D288" s="52" t="str">
-        <x:f>IF($B288="","",IFERROR(VLOOKUP($B288,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B288="","",IFERROR(VLOOKUP($B288,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E288" s="62" t="str">
         <x:f>IF($D288="","",IF($D288="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F288" s="53" t="str">
-        <x:f>IF($B288="","",IFERROR(VLOOKUP($B288,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B288="","",IFERROR(VLOOKUP($B288,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B288),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G288" s="65" t="str">
         <x:f>IF($F288="","",IFERROR(VLOOKUP($F288,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16565,13 +16580,13 @@
       <x:c r="B289" s="33"/>
       <x:c r="C289" s="59"/>
       <x:c r="D289" s="52" t="str">
-        <x:f>IF($B289="","",IFERROR(VLOOKUP($B289,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B289="","",IFERROR(VLOOKUP($B289,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E289" s="62" t="str">
         <x:f>IF($D289="","",IF($D289="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F289" s="53" t="str">
-        <x:f>IF($B289="","",IFERROR(VLOOKUP($B289,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B289="","",IFERROR(VLOOKUP($B289,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B289),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G289" s="65" t="str">
         <x:f>IF($F289="","",IFERROR(VLOOKUP($F289,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16619,13 +16634,13 @@
       <x:c r="B290" s="33"/>
       <x:c r="C290" s="59"/>
       <x:c r="D290" s="52" t="str">
-        <x:f>IF($B290="","",IFERROR(VLOOKUP($B290,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B290="","",IFERROR(VLOOKUP($B290,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E290" s="62" t="str">
         <x:f>IF($D290="","",IF($D290="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F290" s="53" t="str">
-        <x:f>IF($B290="","",IFERROR(VLOOKUP($B290,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B290="","",IFERROR(VLOOKUP($B290,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B290),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G290" s="65" t="str">
         <x:f>IF($F290="","",IFERROR(VLOOKUP($F290,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16673,13 +16688,13 @@
       <x:c r="B291" s="33"/>
       <x:c r="C291" s="59"/>
       <x:c r="D291" s="52" t="str">
-        <x:f>IF($B291="","",IFERROR(VLOOKUP($B291,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B291="","",IFERROR(VLOOKUP($B291,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E291" s="62" t="str">
         <x:f>IF($D291="","",IF($D291="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F291" s="53" t="str">
-        <x:f>IF($B291="","",IFERROR(VLOOKUP($B291,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B291="","",IFERROR(VLOOKUP($B291,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B291),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G291" s="65" t="str">
         <x:f>IF($F291="","",IFERROR(VLOOKUP($F291,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16727,13 +16742,13 @@
       <x:c r="B292" s="33"/>
       <x:c r="C292" s="59"/>
       <x:c r="D292" s="52" t="str">
-        <x:f>IF($B292="","",IFERROR(VLOOKUP($B292,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B292="","",IFERROR(VLOOKUP($B292,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E292" s="62" t="str">
         <x:f>IF($D292="","",IF($D292="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F292" s="53" t="str">
-        <x:f>IF($B292="","",IFERROR(VLOOKUP($B292,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B292="","",IFERROR(VLOOKUP($B292,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B292),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G292" s="65" t="str">
         <x:f>IF($F292="","",IFERROR(VLOOKUP($F292,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16781,13 +16796,13 @@
       <x:c r="B293" s="33"/>
       <x:c r="C293" s="59"/>
       <x:c r="D293" s="52" t="str">
-        <x:f>IF($B293="","",IFERROR(VLOOKUP($B293,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B293="","",IFERROR(VLOOKUP($B293,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E293" s="62" t="str">
         <x:f>IF($D293="","",IF($D293="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F293" s="53" t="str">
-        <x:f>IF($B293="","",IFERROR(VLOOKUP($B293,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B293="","",IFERROR(VLOOKUP($B293,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B293),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G293" s="65" t="str">
         <x:f>IF($F293="","",IFERROR(VLOOKUP($F293,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16835,13 +16850,13 @@
       <x:c r="B294" s="33"/>
       <x:c r="C294" s="59"/>
       <x:c r="D294" s="52" t="str">
-        <x:f>IF($B294="","",IFERROR(VLOOKUP($B294,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B294="","",IFERROR(VLOOKUP($B294,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E294" s="62" t="str">
         <x:f>IF($D294="","",IF($D294="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F294" s="53" t="str">
-        <x:f>IF($B294="","",IFERROR(VLOOKUP($B294,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B294="","",IFERROR(VLOOKUP($B294,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B294),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G294" s="65" t="str">
         <x:f>IF($F294="","",IFERROR(VLOOKUP($F294,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16889,13 +16904,13 @@
       <x:c r="B295" s="33"/>
       <x:c r="C295" s="59"/>
       <x:c r="D295" s="52" t="str">
-        <x:f>IF($B295="","",IFERROR(VLOOKUP($B295,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B295="","",IFERROR(VLOOKUP($B295,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E295" s="62" t="str">
         <x:f>IF($D295="","",IF($D295="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F295" s="53" t="str">
-        <x:f>IF($B295="","",IFERROR(VLOOKUP($B295,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B295="","",IFERROR(VLOOKUP($B295,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B295),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G295" s="65" t="str">
         <x:f>IF($F295="","",IFERROR(VLOOKUP($F295,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16943,13 +16958,13 @@
       <x:c r="B296" s="33"/>
       <x:c r="C296" s="59"/>
       <x:c r="D296" s="52" t="str">
-        <x:f>IF($B296="","",IFERROR(VLOOKUP($B296,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B296="","",IFERROR(VLOOKUP($B296,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E296" s="62" t="str">
         <x:f>IF($D296="","",IF($D296="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F296" s="53" t="str">
-        <x:f>IF($B296="","",IFERROR(VLOOKUP($B296,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B296="","",IFERROR(VLOOKUP($B296,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B296),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G296" s="65" t="str">
         <x:f>IF($F296="","",IFERROR(VLOOKUP($F296,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -16997,13 +17012,13 @@
       <x:c r="B297" s="33"/>
       <x:c r="C297" s="59"/>
       <x:c r="D297" s="52" t="str">
-        <x:f>IF($B297="","",IFERROR(VLOOKUP($B297,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B297="","",IFERROR(VLOOKUP($B297,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E297" s="62" t="str">
         <x:f>IF($D297="","",IF($D297="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F297" s="53" t="str">
-        <x:f>IF($B297="","",IFERROR(VLOOKUP($B297,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B297="","",IFERROR(VLOOKUP($B297,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B297),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G297" s="65" t="str">
         <x:f>IF($F297="","",IFERROR(VLOOKUP($F297,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17051,13 +17066,13 @@
       <x:c r="B298" s="33"/>
       <x:c r="C298" s="59"/>
       <x:c r="D298" s="52" t="str">
-        <x:f>IF($B298="","",IFERROR(VLOOKUP($B298,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B298="","",IFERROR(VLOOKUP($B298,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E298" s="62" t="str">
         <x:f>IF($D298="","",IF($D298="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F298" s="53" t="str">
-        <x:f>IF($B298="","",IFERROR(VLOOKUP($B298,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B298="","",IFERROR(VLOOKUP($B298,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B298),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G298" s="65" t="str">
         <x:f>IF($F298="","",IFERROR(VLOOKUP($F298,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17105,13 +17120,13 @@
       <x:c r="B299" s="33"/>
       <x:c r="C299" s="59"/>
       <x:c r="D299" s="52" t="str">
-        <x:f>IF($B299="","",IFERROR(VLOOKUP($B299,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B299="","",IFERROR(VLOOKUP($B299,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E299" s="62" t="str">
         <x:f>IF($D299="","",IF($D299="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F299" s="53" t="str">
-        <x:f>IF($B299="","",IFERROR(VLOOKUP($B299,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B299="","",IFERROR(VLOOKUP($B299,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B299),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G299" s="65" t="str">
         <x:f>IF($F299="","",IFERROR(VLOOKUP($F299,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17159,13 +17174,13 @@
       <x:c r="B300" s="33"/>
       <x:c r="C300" s="59"/>
       <x:c r="D300" s="52" t="str">
-        <x:f>IF($B300="","",IFERROR(VLOOKUP($B300,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B300="","",IFERROR(VLOOKUP($B300,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E300" s="62" t="str">
         <x:f>IF($D300="","",IF($D300="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F300" s="53" t="str">
-        <x:f>IF($B300="","",IFERROR(VLOOKUP($B300,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B300="","",IFERROR(VLOOKUP($B300,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B300),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G300" s="65" t="str">
         <x:f>IF($F300="","",IFERROR(VLOOKUP($F300,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17213,13 +17228,13 @@
       <x:c r="B301" s="33"/>
       <x:c r="C301" s="59"/>
       <x:c r="D301" s="52" t="str">
-        <x:f>IF($B301="","",IFERROR(VLOOKUP($B301,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B301="","",IFERROR(VLOOKUP($B301,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E301" s="62" t="str">
         <x:f>IF($D301="","",IF($D301="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F301" s="53" t="str">
-        <x:f>IF($B301="","",IFERROR(VLOOKUP($B301,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B301="","",IFERROR(VLOOKUP($B301,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B301),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G301" s="65" t="str">
         <x:f>IF($F301="","",IFERROR(VLOOKUP($F301,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17267,13 +17282,13 @@
       <x:c r="B302" s="33"/>
       <x:c r="C302" s="59"/>
       <x:c r="D302" s="52" t="str">
-        <x:f>IF($B302="","",IFERROR(VLOOKUP($B302,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B302="","",IFERROR(VLOOKUP($B302,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E302" s="62" t="str">
         <x:f>IF($D302="","",IF($D302="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F302" s="53" t="str">
-        <x:f>IF($B302="","",IFERROR(VLOOKUP($B302,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B302="","",IFERROR(VLOOKUP($B302,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B302),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G302" s="65" t="str">
         <x:f>IF($F302="","",IFERROR(VLOOKUP($F302,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17321,13 +17336,13 @@
       <x:c r="B303" s="33"/>
       <x:c r="C303" s="59"/>
       <x:c r="D303" s="52" t="str">
-        <x:f>IF($B303="","",IFERROR(VLOOKUP($B303,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B303="","",IFERROR(VLOOKUP($B303,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E303" s="62" t="str">
         <x:f>IF($D303="","",IF($D303="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F303" s="53" t="str">
-        <x:f>IF($B303="","",IFERROR(VLOOKUP($B303,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B303="","",IFERROR(VLOOKUP($B303,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B303),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G303" s="65" t="str">
         <x:f>IF($F303="","",IFERROR(VLOOKUP($F303,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17375,13 +17390,13 @@
       <x:c r="B304" s="33"/>
       <x:c r="C304" s="59"/>
       <x:c r="D304" s="52" t="str">
-        <x:f>IF($B304="","",IFERROR(VLOOKUP($B304,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B304="","",IFERROR(VLOOKUP($B304,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E304" s="62" t="str">
         <x:f>IF($D304="","",IF($D304="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F304" s="53" t="str">
-        <x:f>IF($B304="","",IFERROR(VLOOKUP($B304,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B304="","",IFERROR(VLOOKUP($B304,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B304),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G304" s="65" t="str">
         <x:f>IF($F304="","",IFERROR(VLOOKUP($F304,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17429,13 +17444,13 @@
       <x:c r="B305" s="33"/>
       <x:c r="C305" s="59"/>
       <x:c r="D305" s="52" t="str">
-        <x:f>IF($B305="","",IFERROR(VLOOKUP($B305,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B305="","",IFERROR(VLOOKUP($B305,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E305" s="62" t="str">
         <x:f>IF($D305="","",IF($D305="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F305" s="53" t="str">
-        <x:f>IF($B305="","",IFERROR(VLOOKUP($B305,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B305="","",IFERROR(VLOOKUP($B305,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B305),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G305" s="65" t="str">
         <x:f>IF($F305="","",IFERROR(VLOOKUP($F305,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17483,13 +17498,13 @@
       <x:c r="B306" s="33"/>
       <x:c r="C306" s="59"/>
       <x:c r="D306" s="52" t="str">
-        <x:f>IF($B306="","",IFERROR(VLOOKUP($B306,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B306="","",IFERROR(VLOOKUP($B306,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E306" s="62" t="str">
         <x:f>IF($D306="","",IF($D306="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F306" s="53" t="str">
-        <x:f>IF($B306="","",IFERROR(VLOOKUP($B306,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B306="","",IFERROR(VLOOKUP($B306,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B306),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G306" s="65" t="str">
         <x:f>IF($F306="","",IFERROR(VLOOKUP($F306,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17537,13 +17552,13 @@
       <x:c r="B307" s="33"/>
       <x:c r="C307" s="59"/>
       <x:c r="D307" s="52" t="str">
-        <x:f>IF($B307="","",IFERROR(VLOOKUP($B307,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B307="","",IFERROR(VLOOKUP($B307,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E307" s="62" t="str">
         <x:f>IF($D307="","",IF($D307="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F307" s="53" t="str">
-        <x:f>IF($B307="","",IFERROR(VLOOKUP($B307,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B307="","",IFERROR(VLOOKUP($B307,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B307),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G307" s="65" t="str">
         <x:f>IF($F307="","",IFERROR(VLOOKUP($F307,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17591,13 +17606,13 @@
       <x:c r="B308" s="33"/>
       <x:c r="C308" s="59"/>
       <x:c r="D308" s="52" t="str">
-        <x:f>IF($B308="","",IFERROR(VLOOKUP($B308,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B308="","",IFERROR(VLOOKUP($B308,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E308" s="62" t="str">
         <x:f>IF($D308="","",IF($D308="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F308" s="53" t="str">
-        <x:f>IF($B308="","",IFERROR(VLOOKUP($B308,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B308="","",IFERROR(VLOOKUP($B308,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B308),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G308" s="65" t="str">
         <x:f>IF($F308="","",IFERROR(VLOOKUP($F308,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17645,13 +17660,13 @@
       <x:c r="B309" s="33"/>
       <x:c r="C309" s="59"/>
       <x:c r="D309" s="52" t="str">
-        <x:f>IF($B309="","",IFERROR(VLOOKUP($B309,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B309="","",IFERROR(VLOOKUP($B309,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E309" s="62" t="str">
         <x:f>IF($D309="","",IF($D309="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F309" s="53" t="str">
-        <x:f>IF($B309="","",IFERROR(VLOOKUP($B309,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B309="","",IFERROR(VLOOKUP($B309,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B309),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G309" s="65" t="str">
         <x:f>IF($F309="","",IFERROR(VLOOKUP($F309,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17699,13 +17714,13 @@
       <x:c r="B310" s="33"/>
       <x:c r="C310" s="59"/>
       <x:c r="D310" s="52" t="str">
-        <x:f>IF($B310="","",IFERROR(VLOOKUP($B310,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B310="","",IFERROR(VLOOKUP($B310,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E310" s="62" t="str">
         <x:f>IF($D310="","",IF($D310="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F310" s="53" t="str">
-        <x:f>IF($B310="","",IFERROR(VLOOKUP($B310,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B310="","",IFERROR(VLOOKUP($B310,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B310),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G310" s="65" t="str">
         <x:f>IF($F310="","",IFERROR(VLOOKUP($F310,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17753,13 +17768,13 @@
       <x:c r="B311" s="33"/>
       <x:c r="C311" s="59"/>
       <x:c r="D311" s="52" t="str">
-        <x:f>IF($B311="","",IFERROR(VLOOKUP($B311,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B311="","",IFERROR(VLOOKUP($B311,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E311" s="62" t="str">
         <x:f>IF($D311="","",IF($D311="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F311" s="53" t="str">
-        <x:f>IF($B311="","",IFERROR(VLOOKUP($B311,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B311="","",IFERROR(VLOOKUP($B311,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B311),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G311" s="65" t="str">
         <x:f>IF($F311="","",IFERROR(VLOOKUP($F311,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17807,13 +17822,13 @@
       <x:c r="B312" s="33"/>
       <x:c r="C312" s="59"/>
       <x:c r="D312" s="52" t="str">
-        <x:f>IF($B312="","",IFERROR(VLOOKUP($B312,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B312="","",IFERROR(VLOOKUP($B312,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E312" s="62" t="str">
         <x:f>IF($D312="","",IF($D312="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F312" s="53" t="str">
-        <x:f>IF($B312="","",IFERROR(VLOOKUP($B312,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B312="","",IFERROR(VLOOKUP($B312,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B312),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G312" s="65" t="str">
         <x:f>IF($F312="","",IFERROR(VLOOKUP($F312,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17861,13 +17876,13 @@
       <x:c r="B313" s="33"/>
       <x:c r="C313" s="59"/>
       <x:c r="D313" s="52" t="str">
-        <x:f>IF($B313="","",IFERROR(VLOOKUP($B313,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B313="","",IFERROR(VLOOKUP($B313,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E313" s="62" t="str">
         <x:f>IF($D313="","",IF($D313="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F313" s="53" t="str">
-        <x:f>IF($B313="","",IFERROR(VLOOKUP($B313,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B313="","",IFERROR(VLOOKUP($B313,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B313),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G313" s="65" t="str">
         <x:f>IF($F313="","",IFERROR(VLOOKUP($F313,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17915,13 +17930,13 @@
       <x:c r="B314" s="33"/>
       <x:c r="C314" s="59"/>
       <x:c r="D314" s="52" t="str">
-        <x:f>IF($B314="","",IFERROR(VLOOKUP($B314,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B314="","",IFERROR(VLOOKUP($B314,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E314" s="62" t="str">
         <x:f>IF($D314="","",IF($D314="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F314" s="53" t="str">
-        <x:f>IF($B314="","",IFERROR(VLOOKUP($B314,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B314="","",IFERROR(VLOOKUP($B314,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B314),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G314" s="65" t="str">
         <x:f>IF($F314="","",IFERROR(VLOOKUP($F314,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -17969,13 +17984,13 @@
       <x:c r="B315" s="33"/>
       <x:c r="C315" s="59"/>
       <x:c r="D315" s="52" t="str">
-        <x:f>IF($B315="","",IFERROR(VLOOKUP($B315,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B315="","",IFERROR(VLOOKUP($B315,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E315" s="62" t="str">
         <x:f>IF($D315="","",IF($D315="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F315" s="53" t="str">
-        <x:f>IF($B315="","",IFERROR(VLOOKUP($B315,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B315="","",IFERROR(VLOOKUP($B315,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B315),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G315" s="65" t="str">
         <x:f>IF($F315="","",IFERROR(VLOOKUP($F315,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18023,13 +18038,13 @@
       <x:c r="B316" s="33"/>
       <x:c r="C316" s="59"/>
       <x:c r="D316" s="52" t="str">
-        <x:f>IF($B316="","",IFERROR(VLOOKUP($B316,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B316="","",IFERROR(VLOOKUP($B316,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E316" s="62" t="str">
         <x:f>IF($D316="","",IF($D316="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F316" s="53" t="str">
-        <x:f>IF($B316="","",IFERROR(VLOOKUP($B316,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B316="","",IFERROR(VLOOKUP($B316,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B316),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G316" s="65" t="str">
         <x:f>IF($F316="","",IFERROR(VLOOKUP($F316,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18077,13 +18092,13 @@
       <x:c r="B317" s="33"/>
       <x:c r="C317" s="59"/>
       <x:c r="D317" s="52" t="str">
-        <x:f>IF($B317="","",IFERROR(VLOOKUP($B317,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B317="","",IFERROR(VLOOKUP($B317,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E317" s="62" t="str">
         <x:f>IF($D317="","",IF($D317="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F317" s="53" t="str">
-        <x:f>IF($B317="","",IFERROR(VLOOKUP($B317,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B317="","",IFERROR(VLOOKUP($B317,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B317),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G317" s="65" t="str">
         <x:f>IF($F317="","",IFERROR(VLOOKUP($F317,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18131,13 +18146,13 @@
       <x:c r="B318" s="33"/>
       <x:c r="C318" s="59"/>
       <x:c r="D318" s="52" t="str">
-        <x:f>IF($B318="","",IFERROR(VLOOKUP($B318,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B318="","",IFERROR(VLOOKUP($B318,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E318" s="62" t="str">
         <x:f>IF($D318="","",IF($D318="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F318" s="53" t="str">
-        <x:f>IF($B318="","",IFERROR(VLOOKUP($B318,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B318="","",IFERROR(VLOOKUP($B318,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B318),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G318" s="65" t="str">
         <x:f>IF($F318="","",IFERROR(VLOOKUP($F318,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18185,13 +18200,13 @@
       <x:c r="B319" s="33"/>
       <x:c r="C319" s="59"/>
       <x:c r="D319" s="52" t="str">
-        <x:f>IF($B319="","",IFERROR(VLOOKUP($B319,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B319="","",IFERROR(VLOOKUP($B319,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E319" s="62" t="str">
         <x:f>IF($D319="","",IF($D319="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F319" s="53" t="str">
-        <x:f>IF($B319="","",IFERROR(VLOOKUP($B319,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B319="","",IFERROR(VLOOKUP($B319,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B319),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G319" s="65" t="str">
         <x:f>IF($F319="","",IFERROR(VLOOKUP($F319,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18239,13 +18254,13 @@
       <x:c r="B320" s="33"/>
       <x:c r="C320" s="59"/>
       <x:c r="D320" s="52" t="str">
-        <x:f>IF($B320="","",IFERROR(VLOOKUP($B320,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B320="","",IFERROR(VLOOKUP($B320,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E320" s="62" t="str">
         <x:f>IF($D320="","",IF($D320="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F320" s="53" t="str">
-        <x:f>IF($B320="","",IFERROR(VLOOKUP($B320,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B320="","",IFERROR(VLOOKUP($B320,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B320),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G320" s="65" t="str">
         <x:f>IF($F320="","",IFERROR(VLOOKUP($F320,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18293,13 +18308,13 @@
       <x:c r="B321" s="33"/>
       <x:c r="C321" s="59"/>
       <x:c r="D321" s="52" t="str">
-        <x:f>IF($B321="","",IFERROR(VLOOKUP($B321,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B321="","",IFERROR(VLOOKUP($B321,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E321" s="62" t="str">
         <x:f>IF($D321="","",IF($D321="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F321" s="53" t="str">
-        <x:f>IF($B321="","",IFERROR(VLOOKUP($B321,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B321="","",IFERROR(VLOOKUP($B321,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B321),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G321" s="65" t="str">
         <x:f>IF($F321="","",IFERROR(VLOOKUP($F321,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18347,13 +18362,13 @@
       <x:c r="B322" s="33"/>
       <x:c r="C322" s="59"/>
       <x:c r="D322" s="52" t="str">
-        <x:f>IF($B322="","",IFERROR(VLOOKUP($B322,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B322="","",IFERROR(VLOOKUP($B322,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E322" s="62" t="str">
         <x:f>IF($D322="","",IF($D322="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F322" s="53" t="str">
-        <x:f>IF($B322="","",IFERROR(VLOOKUP($B322,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B322="","",IFERROR(VLOOKUP($B322,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B322),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G322" s="65" t="str">
         <x:f>IF($F322="","",IFERROR(VLOOKUP($F322,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18401,13 +18416,13 @@
       <x:c r="B323" s="33"/>
       <x:c r="C323" s="59"/>
       <x:c r="D323" s="52" t="str">
-        <x:f>IF($B323="","",IFERROR(VLOOKUP($B323,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B323="","",IFERROR(VLOOKUP($B323,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E323" s="62" t="str">
         <x:f>IF($D323="","",IF($D323="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F323" s="53" t="str">
-        <x:f>IF($B323="","",IFERROR(VLOOKUP($B323,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B323="","",IFERROR(VLOOKUP($B323,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B323),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G323" s="65" t="str">
         <x:f>IF($F323="","",IFERROR(VLOOKUP($F323,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18455,13 +18470,13 @@
       <x:c r="B324" s="33"/>
       <x:c r="C324" s="59"/>
       <x:c r="D324" s="52" t="str">
-        <x:f>IF($B324="","",IFERROR(VLOOKUP($B324,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B324="","",IFERROR(VLOOKUP($B324,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E324" s="62" t="str">
         <x:f>IF($D324="","",IF($D324="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F324" s="53" t="str">
-        <x:f>IF($B324="","",IFERROR(VLOOKUP($B324,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B324="","",IFERROR(VLOOKUP($B324,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B324),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G324" s="65" t="str">
         <x:f>IF($F324="","",IFERROR(VLOOKUP($F324,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18509,13 +18524,13 @@
       <x:c r="B325" s="33"/>
       <x:c r="C325" s="59"/>
       <x:c r="D325" s="52" t="str">
-        <x:f>IF($B325="","",IFERROR(VLOOKUP($B325,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B325="","",IFERROR(VLOOKUP($B325,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E325" s="62" t="str">
         <x:f>IF($D325="","",IF($D325="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F325" s="53" t="str">
-        <x:f>IF($B325="","",IFERROR(VLOOKUP($B325,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B325="","",IFERROR(VLOOKUP($B325,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B325),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G325" s="65" t="str">
         <x:f>IF($F325="","",IFERROR(VLOOKUP($F325,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18563,13 +18578,13 @@
       <x:c r="B326" s="33"/>
       <x:c r="C326" s="59"/>
       <x:c r="D326" s="52" t="str">
-        <x:f>IF($B326="","",IFERROR(VLOOKUP($B326,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B326="","",IFERROR(VLOOKUP($B326,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E326" s="62" t="str">
         <x:f>IF($D326="","",IF($D326="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F326" s="53" t="str">
-        <x:f>IF($B326="","",IFERROR(VLOOKUP($B326,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B326="","",IFERROR(VLOOKUP($B326,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B326),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G326" s="65" t="str">
         <x:f>IF($F326="","",IFERROR(VLOOKUP($F326,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18617,13 +18632,13 @@
       <x:c r="B327" s="33"/>
       <x:c r="C327" s="59"/>
       <x:c r="D327" s="52" t="str">
-        <x:f>IF($B327="","",IFERROR(VLOOKUP($B327,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B327="","",IFERROR(VLOOKUP($B327,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E327" s="62" t="str">
         <x:f>IF($D327="","",IF($D327="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F327" s="53" t="str">
-        <x:f>IF($B327="","",IFERROR(VLOOKUP($B327,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B327="","",IFERROR(VLOOKUP($B327,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B327),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G327" s="65" t="str">
         <x:f>IF($F327="","",IFERROR(VLOOKUP($F327,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18671,13 +18686,13 @@
       <x:c r="B328" s="33"/>
       <x:c r="C328" s="59"/>
       <x:c r="D328" s="52" t="str">
-        <x:f>IF($B328="","",IFERROR(VLOOKUP($B328,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B328="","",IFERROR(VLOOKUP($B328,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E328" s="62" t="str">
         <x:f>IF($D328="","",IF($D328="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F328" s="53" t="str">
-        <x:f>IF($B328="","",IFERROR(VLOOKUP($B328,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B328="","",IFERROR(VLOOKUP($B328,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B328),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G328" s="65" t="str">
         <x:f>IF($F328="","",IFERROR(VLOOKUP($F328,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18725,13 +18740,13 @@
       <x:c r="B329" s="33"/>
       <x:c r="C329" s="59"/>
       <x:c r="D329" s="52" t="str">
-        <x:f>IF($B329="","",IFERROR(VLOOKUP($B329,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B329="","",IFERROR(VLOOKUP($B329,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E329" s="62" t="str">
         <x:f>IF($D329="","",IF($D329="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F329" s="53" t="str">
-        <x:f>IF($B329="","",IFERROR(VLOOKUP($B329,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B329="","",IFERROR(VLOOKUP($B329,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B329),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G329" s="65" t="str">
         <x:f>IF($F329="","",IFERROR(VLOOKUP($F329,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18779,13 +18794,13 @@
       <x:c r="B330" s="33"/>
       <x:c r="C330" s="59"/>
       <x:c r="D330" s="52" t="str">
-        <x:f>IF($B330="","",IFERROR(VLOOKUP($B330,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B330="","",IFERROR(VLOOKUP($B330,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E330" s="62" t="str">
         <x:f>IF($D330="","",IF($D330="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F330" s="53" t="str">
-        <x:f>IF($B330="","",IFERROR(VLOOKUP($B330,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B330="","",IFERROR(VLOOKUP($B330,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B330),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G330" s="65" t="str">
         <x:f>IF($F330="","",IFERROR(VLOOKUP($F330,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18833,13 +18848,13 @@
       <x:c r="B331" s="33"/>
       <x:c r="C331" s="59"/>
       <x:c r="D331" s="52" t="str">
-        <x:f>IF($B331="","",IFERROR(VLOOKUP($B331,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B331="","",IFERROR(VLOOKUP($B331,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E331" s="62" t="str">
         <x:f>IF($D331="","",IF($D331="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F331" s="53" t="str">
-        <x:f>IF($B331="","",IFERROR(VLOOKUP($B331,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B331="","",IFERROR(VLOOKUP($B331,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B331),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G331" s="65" t="str">
         <x:f>IF($F331="","",IFERROR(VLOOKUP($F331,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18887,13 +18902,13 @@
       <x:c r="B332" s="33"/>
       <x:c r="C332" s="59"/>
       <x:c r="D332" s="52" t="str">
-        <x:f>IF($B332="","",IFERROR(VLOOKUP($B332,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B332="","",IFERROR(VLOOKUP($B332,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E332" s="62" t="str">
         <x:f>IF($D332="","",IF($D332="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F332" s="53" t="str">
-        <x:f>IF($B332="","",IFERROR(VLOOKUP($B332,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B332="","",IFERROR(VLOOKUP($B332,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B332),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G332" s="65" t="str">
         <x:f>IF($F332="","",IFERROR(VLOOKUP($F332,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18941,13 +18956,13 @@
       <x:c r="B333" s="33"/>
       <x:c r="C333" s="59"/>
       <x:c r="D333" s="52" t="str">
-        <x:f>IF($B333="","",IFERROR(VLOOKUP($B333,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B333="","",IFERROR(VLOOKUP($B333,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E333" s="62" t="str">
         <x:f>IF($D333="","",IF($D333="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F333" s="53" t="str">
-        <x:f>IF($B333="","",IFERROR(VLOOKUP($B333,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B333="","",IFERROR(VLOOKUP($B333,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B333),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G333" s="65" t="str">
         <x:f>IF($F333="","",IFERROR(VLOOKUP($F333,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -18995,13 +19010,13 @@
       <x:c r="B334" s="33"/>
       <x:c r="C334" s="59"/>
       <x:c r="D334" s="52" t="str">
-        <x:f>IF($B334="","",IFERROR(VLOOKUP($B334,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B334="","",IFERROR(VLOOKUP($B334,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E334" s="62" t="str">
         <x:f>IF($D334="","",IF($D334="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F334" s="53" t="str">
-        <x:f>IF($B334="","",IFERROR(VLOOKUP($B334,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B334="","",IFERROR(VLOOKUP($B334,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B334),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G334" s="65" t="str">
         <x:f>IF($F334="","",IFERROR(VLOOKUP($F334,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19049,13 +19064,13 @@
       <x:c r="B335" s="33"/>
       <x:c r="C335" s="59"/>
       <x:c r="D335" s="52" t="str">
-        <x:f>IF($B335="","",IFERROR(VLOOKUP($B335,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B335="","",IFERROR(VLOOKUP($B335,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E335" s="62" t="str">
         <x:f>IF($D335="","",IF($D335="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F335" s="53" t="str">
-        <x:f>IF($B335="","",IFERROR(VLOOKUP($B335,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B335="","",IFERROR(VLOOKUP($B335,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B335),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G335" s="65" t="str">
         <x:f>IF($F335="","",IFERROR(VLOOKUP($F335,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19103,13 +19118,13 @@
       <x:c r="B336" s="33"/>
       <x:c r="C336" s="59"/>
       <x:c r="D336" s="52" t="str">
-        <x:f>IF($B336="","",IFERROR(VLOOKUP($B336,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B336="","",IFERROR(VLOOKUP($B336,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E336" s="62" t="str">
         <x:f>IF($D336="","",IF($D336="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F336" s="53" t="str">
-        <x:f>IF($B336="","",IFERROR(VLOOKUP($B336,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B336="","",IFERROR(VLOOKUP($B336,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B336),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G336" s="65" t="str">
         <x:f>IF($F336="","",IFERROR(VLOOKUP($F336,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19157,13 +19172,13 @@
       <x:c r="B337" s="33"/>
       <x:c r="C337" s="59"/>
       <x:c r="D337" s="52" t="str">
-        <x:f>IF($B337="","",IFERROR(VLOOKUP($B337,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B337="","",IFERROR(VLOOKUP($B337,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E337" s="62" t="str">
         <x:f>IF($D337="","",IF($D337="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F337" s="53" t="str">
-        <x:f>IF($B337="","",IFERROR(VLOOKUP($B337,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B337="","",IFERROR(VLOOKUP($B337,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B337),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G337" s="65" t="str">
         <x:f>IF($F337="","",IFERROR(VLOOKUP($F337,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19211,13 +19226,13 @@
       <x:c r="B338" s="33"/>
       <x:c r="C338" s="59"/>
       <x:c r="D338" s="52" t="str">
-        <x:f>IF($B338="","",IFERROR(VLOOKUP($B338,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B338="","",IFERROR(VLOOKUP($B338,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E338" s="62" t="str">
         <x:f>IF($D338="","",IF($D338="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F338" s="53" t="str">
-        <x:f>IF($B338="","",IFERROR(VLOOKUP($B338,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B338="","",IFERROR(VLOOKUP($B338,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B338),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G338" s="65" t="str">
         <x:f>IF($F338="","",IFERROR(VLOOKUP($F338,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19265,13 +19280,13 @@
       <x:c r="B339" s="33"/>
       <x:c r="C339" s="59"/>
       <x:c r="D339" s="52" t="str">
-        <x:f>IF($B339="","",IFERROR(VLOOKUP($B339,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B339="","",IFERROR(VLOOKUP($B339,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E339" s="62" t="str">
         <x:f>IF($D339="","",IF($D339="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F339" s="53" t="str">
-        <x:f>IF($B339="","",IFERROR(VLOOKUP($B339,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B339="","",IFERROR(VLOOKUP($B339,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B339),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G339" s="65" t="str">
         <x:f>IF($F339="","",IFERROR(VLOOKUP($F339,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19319,13 +19334,13 @@
       <x:c r="B340" s="33"/>
       <x:c r="C340" s="59"/>
       <x:c r="D340" s="52" t="str">
-        <x:f>IF($B340="","",IFERROR(VLOOKUP($B340,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B340="","",IFERROR(VLOOKUP($B340,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E340" s="62" t="str">
         <x:f>IF($D340="","",IF($D340="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F340" s="53" t="str">
-        <x:f>IF($B340="","",IFERROR(VLOOKUP($B340,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B340="","",IFERROR(VLOOKUP($B340,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B340),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G340" s="65" t="str">
         <x:f>IF($F340="","",IFERROR(VLOOKUP($F340,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19373,13 +19388,13 @@
       <x:c r="B341" s="33"/>
       <x:c r="C341" s="59"/>
       <x:c r="D341" s="52" t="str">
-        <x:f>IF($B341="","",IFERROR(VLOOKUP($B341,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B341="","",IFERROR(VLOOKUP($B341,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E341" s="62" t="str">
         <x:f>IF($D341="","",IF($D341="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F341" s="53" t="str">
-        <x:f>IF($B341="","",IFERROR(VLOOKUP($B341,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B341="","",IFERROR(VLOOKUP($B341,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B341),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G341" s="65" t="str">
         <x:f>IF($F341="","",IFERROR(VLOOKUP($F341,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19427,13 +19442,13 @@
       <x:c r="B342" s="33"/>
       <x:c r="C342" s="59"/>
       <x:c r="D342" s="52" t="str">
-        <x:f>IF($B342="","",IFERROR(VLOOKUP($B342,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B342="","",IFERROR(VLOOKUP($B342,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E342" s="62" t="str">
         <x:f>IF($D342="","",IF($D342="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F342" s="53" t="str">
-        <x:f>IF($B342="","",IFERROR(VLOOKUP($B342,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B342="","",IFERROR(VLOOKUP($B342,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B342),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G342" s="65" t="str">
         <x:f>IF($F342="","",IFERROR(VLOOKUP($F342,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19481,13 +19496,13 @@
       <x:c r="B343" s="33"/>
       <x:c r="C343" s="59"/>
       <x:c r="D343" s="52" t="str">
-        <x:f>IF($B343="","",IFERROR(VLOOKUP($B343,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B343="","",IFERROR(VLOOKUP($B343,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E343" s="62" t="str">
         <x:f>IF($D343="","",IF($D343="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F343" s="53" t="str">
-        <x:f>IF($B343="","",IFERROR(VLOOKUP($B343,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B343="","",IFERROR(VLOOKUP($B343,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B343),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G343" s="65" t="str">
         <x:f>IF($F343="","",IFERROR(VLOOKUP($F343,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19535,13 +19550,13 @@
       <x:c r="B344" s="33"/>
       <x:c r="C344" s="59"/>
       <x:c r="D344" s="52" t="str">
-        <x:f>IF($B344="","",IFERROR(VLOOKUP($B344,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B344="","",IFERROR(VLOOKUP($B344,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E344" s="62" t="str">
         <x:f>IF($D344="","",IF($D344="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F344" s="53" t="str">
-        <x:f>IF($B344="","",IFERROR(VLOOKUP($B344,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B344="","",IFERROR(VLOOKUP($B344,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B344),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G344" s="65" t="str">
         <x:f>IF($F344="","",IFERROR(VLOOKUP($F344,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19589,13 +19604,13 @@
       <x:c r="B345" s="33"/>
       <x:c r="C345" s="59"/>
       <x:c r="D345" s="52" t="str">
-        <x:f>IF($B345="","",IFERROR(VLOOKUP($B345,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B345="","",IFERROR(VLOOKUP($B345,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E345" s="62" t="str">
         <x:f>IF($D345="","",IF($D345="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F345" s="53" t="str">
-        <x:f>IF($B345="","",IFERROR(VLOOKUP($B345,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B345="","",IFERROR(VLOOKUP($B345,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B345),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G345" s="65" t="str">
         <x:f>IF($F345="","",IFERROR(VLOOKUP($F345,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19643,13 +19658,13 @@
       <x:c r="B346" s="33"/>
       <x:c r="C346" s="59"/>
       <x:c r="D346" s="52" t="str">
-        <x:f>IF($B346="","",IFERROR(VLOOKUP($B346,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B346="","",IFERROR(VLOOKUP($B346,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E346" s="62" t="str">
         <x:f>IF($D346="","",IF($D346="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F346" s="53" t="str">
-        <x:f>IF($B346="","",IFERROR(VLOOKUP($B346,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B346="","",IFERROR(VLOOKUP($B346,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B346),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G346" s="65" t="str">
         <x:f>IF($F346="","",IFERROR(VLOOKUP($F346,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19697,13 +19712,13 @@
       <x:c r="B347" s="33"/>
       <x:c r="C347" s="59"/>
       <x:c r="D347" s="52" t="str">
-        <x:f>IF($B347="","",IFERROR(VLOOKUP($B347,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B347="","",IFERROR(VLOOKUP($B347,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E347" s="62" t="str">
         <x:f>IF($D347="","",IF($D347="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F347" s="53" t="str">
-        <x:f>IF($B347="","",IFERROR(VLOOKUP($B347,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B347="","",IFERROR(VLOOKUP($B347,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B347),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G347" s="65" t="str">
         <x:f>IF($F347="","",IFERROR(VLOOKUP($F347,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19751,13 +19766,13 @@
       <x:c r="B348" s="33"/>
       <x:c r="C348" s="59"/>
       <x:c r="D348" s="52" t="str">
-        <x:f>IF($B348="","",IFERROR(VLOOKUP($B348,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B348="","",IFERROR(VLOOKUP($B348,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E348" s="62" t="str">
         <x:f>IF($D348="","",IF($D348="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F348" s="53" t="str">
-        <x:f>IF($B348="","",IFERROR(VLOOKUP($B348,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B348="","",IFERROR(VLOOKUP($B348,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B348),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G348" s="65" t="str">
         <x:f>IF($F348="","",IFERROR(VLOOKUP($F348,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19805,13 +19820,13 @@
       <x:c r="B349" s="33"/>
       <x:c r="C349" s="59"/>
       <x:c r="D349" s="52" t="str">
-        <x:f>IF($B349="","",IFERROR(VLOOKUP($B349,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B349="","",IFERROR(VLOOKUP($B349,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E349" s="62" t="str">
         <x:f>IF($D349="","",IF($D349="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F349" s="53" t="str">
-        <x:f>IF($B349="","",IFERROR(VLOOKUP($B349,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B349="","",IFERROR(VLOOKUP($B349,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B349),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G349" s="65" t="str">
         <x:f>IF($F349="","",IFERROR(VLOOKUP($F349,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19859,13 +19874,13 @@
       <x:c r="B350" s="33"/>
       <x:c r="C350" s="59"/>
       <x:c r="D350" s="52" t="str">
-        <x:f>IF($B350="","",IFERROR(VLOOKUP($B350,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B350="","",IFERROR(VLOOKUP($B350,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E350" s="62" t="str">
         <x:f>IF($D350="","",IF($D350="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F350" s="53" t="str">
-        <x:f>IF($B350="","",IFERROR(VLOOKUP($B350,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B350="","",IFERROR(VLOOKUP($B350,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B350),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G350" s="65" t="str">
         <x:f>IF($F350="","",IFERROR(VLOOKUP($F350,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19913,13 +19928,13 @@
       <x:c r="B351" s="33"/>
       <x:c r="C351" s="59"/>
       <x:c r="D351" s="52" t="str">
-        <x:f>IF($B351="","",IFERROR(VLOOKUP($B351,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B351="","",IFERROR(VLOOKUP($B351,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E351" s="62" t="str">
         <x:f>IF($D351="","",IF($D351="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F351" s="53" t="str">
-        <x:f>IF($B351="","",IFERROR(VLOOKUP($B351,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B351="","",IFERROR(VLOOKUP($B351,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B351),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G351" s="65" t="str">
         <x:f>IF($F351="","",IFERROR(VLOOKUP($F351,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -19967,13 +19982,13 @@
       <x:c r="B352" s="33"/>
       <x:c r="C352" s="59"/>
       <x:c r="D352" s="52" t="str">
-        <x:f>IF($B352="","",IFERROR(VLOOKUP($B352,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B352="","",IFERROR(VLOOKUP($B352,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E352" s="62" t="str">
         <x:f>IF($D352="","",IF($D352="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F352" s="53" t="str">
-        <x:f>IF($B352="","",IFERROR(VLOOKUP($B352,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B352="","",IFERROR(VLOOKUP($B352,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B352),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G352" s="65" t="str">
         <x:f>IF($F352="","",IFERROR(VLOOKUP($F352,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -20021,13 +20036,13 @@
       <x:c r="B353" s="33"/>
       <x:c r="C353" s="59"/>
       <x:c r="D353" s="52" t="str">
-        <x:f>IF($B353="","",IFERROR(VLOOKUP($B353,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B353="","",IFERROR(VLOOKUP($B353,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E353" s="62" t="str">
         <x:f>IF($D353="","",IF($D353="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F353" s="53" t="str">
-        <x:f>IF($B353="","",IFERROR(VLOOKUP($B353,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B353="","",IFERROR(VLOOKUP($B353,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B353),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G353" s="65" t="str">
         <x:f>IF($F353="","",IFERROR(VLOOKUP($F353,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -20075,13 +20090,13 @@
       <x:c r="B354" s="36"/>
       <x:c r="C354" s="60"/>
       <x:c r="D354" s="55" t="str">
-        <x:f>IF($B354="","",IFERROR(VLOOKUP($B354,'Data'!$A$2:$C$113,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," ")))))),"PS","GS")))</x:f>
+        <x:f>IF($B354="","",IFERROR(VLOOKUP($B354,'Data'!$A$2:$C$119,3,FALSE),IF(OR(RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))),2)="P1",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))),2)="P2",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))),2)="P3",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))),2)="P4",RIGHT(UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))),2)="PS",ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," ")))))),"PS","GS")))</x:f>
       </x:c>
       <x:c r="E354" s="63" t="str">
         <x:f>IF($D354="","",IF($D354="PS",'Data'!$O$5,'Data'!$O$4))</x:f>
       </x:c>
       <x:c r="F354" s="56" t="str">
-        <x:f>IF($B354="","",IFERROR(VLOOKUP($B354,'Data'!$A$2:$B$113,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
+        <x:f>IF($B354="","",IFERROR(VLOOKUP($B354,'Data'!$A$2:$B$119,2,FALSE),IF(ISNUMBER(SEARCH("INDUSTRIAL HYGIENIST",UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))))),IF(OR(ISNUMBER(SEARCH("P2",UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," "))))),ISNUMBER(SEARCH(" II "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," ")))&amp;" ")),ISNUMBER(SEARCH(" 2 "," "&amp;UPPER(TRIM(SUBSTITUTE(CLEAN($B354),CHAR(160)," ")))&amp;" "))),"H","G"),"")))</x:f>
       </x:c>
       <x:c r="G354" s="66" t="str">
         <x:f>IF($F354="","",IFERROR(VLOOKUP($F354,'Data'!$D$2:$G$14,3,FALSE),""))</x:f>
@@ -21010,7 +21025,7 @@
   </x:conditionalFormatting>
   <x:dataValidations count="2">
     <x:dataValidation type="list" allowBlank="1" showDropDown="0" sqref="B5:B354">
-      <x:formula1>$U$2:$U$113</x:formula1>
+      <x:formula1>$U$2:$U$119</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="decimal" operator="greaterThan" sqref="C5:C354">
       <x:formula1>0</x:formula1>
@@ -22555,34 +22570,73 @@
       </x:c>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" s="92"/>
-      <x:c r="B114" s="92"/>
-      <x:c r="C114"/>
+      <x:c r="A114" s="92" t="str">
+        <x:v>CQ engineer  Site Engineering P1-G midpoint   (CQ=Commissioning&amp;Qualification)
+1 stap boven mid</x:v>
+      </x:c>
+      <x:c r="B114" s="92" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>PS</x:v>
+      </x:c>
     </x:row>
     <x:row r="115">
-      <x:c r="A115"/>
-      <x:c r="B115"/>
-      <x:c r="C115"/>
+      <x:c r="A115" t="str">
+        <x:v>CQ engineer Site Engineering P1-F midpoint   (CQ=Commissioning&amp;Qualification)</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>PS</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
-      <x:c r="A116"/>
-      <x:c r="B116"/>
-      <x:c r="C116"/>
+      <x:c r="A116" t="str">
+        <x:v>CQ engineer Site Engineering P1-G Tussen midpoint en max.   (CQ=Commissioning&amp;Qualification)</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>PS</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
-      <x:c r="A117"/>
-      <x:c r="B117"/>
-      <x:c r="C117"/>
+      <x:c r="A117" t="str">
+        <x:v>SPOC=Programma-manager Site Engineering  P3-J  Tussen midpoint en max.
+2 stappen boven mid 1 stap  onder max</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>J</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>PS</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
-      <x:c r="A118"/>
-      <x:c r="B118"/>
-      <x:c r="C118"/>
+      <x:c r="A118" t="str">
+        <x:v>Projectmanager Site Engineering P2-H Tussen midpoint en max.
+2 stappen boven mid 1 stap onder max</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>PS</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
-      <x:c r="A119"/>
-      <x:c r="B119"/>
-      <x:c r="C119"/>
+      <x:c r="A119" t="str">
+        <x:v>Civil engineer Site Engineering P1-G midpoint 1 stap boven</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>PS</x:v>
+      </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120"/>
